--- a/data/EjemploDominios.xlsx
+++ b/data/EjemploDominios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giova\Documents\GB\MisCursos\Muestreo2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EB88EF9-5F6F-4F62-B32A-51E6B31BEA04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F37F4F6-C852-4AE8-ABFF-09818D300B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{42CC5FC2-8CC7-43C2-B7FE-203DEB835DFD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{42CC5FC2-8CC7-43C2-B7FE-203DEB835DFD}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="35">
   <si>
     <t>ID</t>
   </si>
@@ -115,12 +115,48 @@
   <si>
     <t>Gasto mensual en COP destinado a otros</t>
   </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>Fex</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Total*D1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suma </t>
+  </si>
+  <si>
+    <t>S^2_y</t>
+  </si>
+  <si>
+    <t>FCP</t>
+  </si>
+  <si>
+    <t>Var</t>
+  </si>
+  <si>
+    <t>CVE</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -134,8 +170,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -145,6 +202,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -244,10 +331,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -260,9 +348,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -594,10 +694,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{177A18EF-237E-4601-8DAA-1F2B06E0B3DF}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:BJ16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="4.7265625" customWidth="1"/>
+    <col min="3" max="8" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.7265625" customWidth="1"/>
+    <col min="11" max="11" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.36328125" customWidth="1"/>
+    <col min="13" max="13" width="6.26953125" customWidth="1"/>
+    <col min="14" max="14" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="19" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -622,8 +734,218 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1" s="13" t="str">
+        <f>C1&amp;"*D1"</f>
+        <v>P2*D1</v>
+      </c>
+      <c r="O1" s="13" t="str">
+        <f>D1&amp;"*D1"</f>
+        <v>P3*D1</v>
+      </c>
+      <c r="P1" s="13" t="str">
+        <f>E1&amp;"*D1"</f>
+        <v>P4*D1</v>
+      </c>
+      <c r="Q1" s="13" t="str">
+        <f>F1&amp;"*D1"</f>
+        <v>P5*D1</v>
+      </c>
+      <c r="R1" s="13" t="str">
+        <f>G1&amp;"*D1"</f>
+        <v>P6*D1</v>
+      </c>
+      <c r="S1" s="13" t="str">
+        <f>H1&amp;"*D1"</f>
+        <v>P7*D1</v>
+      </c>
+      <c r="T1" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="U1" s="12" t="str">
+        <f>N1&amp;"*Fex"</f>
+        <v>P2*D1*Fex</v>
+      </c>
+      <c r="V1" s="12" t="str">
+        <f t="shared" ref="V1:AA1" si="0">O1&amp;"*Fex"</f>
+        <v>P3*D1*Fex</v>
+      </c>
+      <c r="W1" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>P4*D1*Fex</v>
+      </c>
+      <c r="X1" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>P5*D1*Fex</v>
+      </c>
+      <c r="Y1" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>P6*D1*Fex</v>
+      </c>
+      <c r="Z1" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>P7*D1*Fex</v>
+      </c>
+      <c r="AA1" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Total*D1*Fex</v>
+      </c>
+      <c r="AB1" s="13" t="str">
+        <f>C1&amp;"*D2"</f>
+        <v>P2*D2</v>
+      </c>
+      <c r="AC1" s="13" t="str">
+        <f t="shared" ref="AC1:AI1" si="1">D1&amp;"*D2"</f>
+        <v>P3*D2</v>
+      </c>
+      <c r="AD1" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>P4*D2</v>
+      </c>
+      <c r="AE1" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>P5*D2</v>
+      </c>
+      <c r="AF1" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>P6*D2</v>
+      </c>
+      <c r="AG1" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>P7*D2</v>
+      </c>
+      <c r="AH1" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>Total*D2</v>
+      </c>
+      <c r="AI1" s="14" t="str">
+        <f>AB1&amp;"*Fex"</f>
+        <v>P2*D2*Fex</v>
+      </c>
+      <c r="AJ1" s="14" t="str">
+        <f t="shared" ref="AJ1:AO1" si="2">AC1&amp;"*Fex"</f>
+        <v>P3*D2*Fex</v>
+      </c>
+      <c r="AK1" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v>P4*D2*Fex</v>
+      </c>
+      <c r="AL1" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v>P5*D2*Fex</v>
+      </c>
+      <c r="AM1" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v>P6*D2*Fex</v>
+      </c>
+      <c r="AN1" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v>P7*D2*Fex</v>
+      </c>
+      <c r="AO1" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v>Total*D2*Fex</v>
+      </c>
+      <c r="AP1" s="15" t="str">
+        <f>C1&amp;"*D3"</f>
+        <v>P2*D3</v>
+      </c>
+      <c r="AQ1" s="15" t="str">
+        <f t="shared" ref="AQ1:AU1" si="3">D1&amp;"*D3"</f>
+        <v>P3*D3</v>
+      </c>
+      <c r="AR1" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>P4*D3</v>
+      </c>
+      <c r="AS1" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>P5*D3</v>
+      </c>
+      <c r="AT1" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>P6*D3</v>
+      </c>
+      <c r="AU1" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>P7*D3</v>
+      </c>
+      <c r="AV1" s="15" t="str">
+        <f>I1&amp;"*D3"</f>
+        <v>Total*D3</v>
+      </c>
+      <c r="AW1" s="14" t="str">
+        <f>AP1&amp;"*Fex"</f>
+        <v>P2*D3*Fex</v>
+      </c>
+      <c r="AX1" s="14" t="str">
+        <f t="shared" ref="AX1:BC1" si="4">AQ1&amp;"*Fex"</f>
+        <v>P3*D3*Fex</v>
+      </c>
+      <c r="AY1" s="14" t="str">
+        <f t="shared" si="4"/>
+        <v>P4*D3*Fex</v>
+      </c>
+      <c r="AZ1" s="14" t="str">
+        <f t="shared" si="4"/>
+        <v>P5*D3*Fex</v>
+      </c>
+      <c r="BA1" s="14" t="str">
+        <f t="shared" si="4"/>
+        <v>P6*D3*Fex</v>
+      </c>
+      <c r="BB1" s="14" t="str">
+        <f t="shared" si="4"/>
+        <v>P7*D3*Fex</v>
+      </c>
+      <c r="BC1" s="14" t="str">
+        <f t="shared" si="4"/>
+        <v>Total*D3*Fex</v>
+      </c>
+      <c r="BD1" s="18" t="str">
+        <f>C1&amp;"*Fex"</f>
+        <v>P2*Fex</v>
+      </c>
+      <c r="BE1" s="18" t="str">
+        <f t="shared" ref="BE1:BJ1" si="5">D1&amp;"*Fex"</f>
+        <v>P3*Fex</v>
+      </c>
+      <c r="BF1" s="18" t="str">
+        <f t="shared" si="5"/>
+        <v>P4*Fex</v>
+      </c>
+      <c r="BG1" s="18" t="str">
+        <f t="shared" si="5"/>
+        <v>P5*Fex</v>
+      </c>
+      <c r="BH1" s="18" t="str">
+        <f t="shared" si="5"/>
+        <v>P6*Fex</v>
+      </c>
+      <c r="BI1" s="18" t="str">
+        <f t="shared" si="5"/>
+        <v>P7*Fex</v>
+      </c>
+      <c r="BJ1" s="18" t="str">
+        <f t="shared" si="5"/>
+        <v>Total*Fex</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:62" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -648,8 +970,224 @@
       <c r="H2" s="5">
         <v>36</v>
       </c>
+      <c r="I2" s="11">
+        <f>SUM(C2:H2)</f>
+        <v>615</v>
+      </c>
+      <c r="J2" s="11">
+        <f>35/10</f>
+        <v>3.5</v>
+      </c>
+      <c r="K2">
+        <f>IF($B2=1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <f>IF($B2=2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <f>IF($B2=3,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <f>C2*$K2</f>
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <f>D2*$K2</f>
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <f>E2*$K2</f>
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <f>F2*$K2</f>
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <f>G2*$K2</f>
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <f>I2*$K2</f>
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <f>I2*$K2</f>
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <f>N2*$J2</f>
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <f t="shared" ref="V2:AA11" si="6">O2*$J2</f>
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <f>C2*$L2</f>
+        <v>224</v>
+      </c>
+      <c r="AC2">
+        <f t="shared" ref="AC2:AH2" si="7">D2*$L2</f>
+        <v>68</v>
+      </c>
+      <c r="AD2">
+        <f t="shared" si="7"/>
+        <v>187</v>
+      </c>
+      <c r="AE2">
+        <f t="shared" si="7"/>
+        <v>36</v>
+      </c>
+      <c r="AF2">
+        <f t="shared" si="7"/>
+        <v>64</v>
+      </c>
+      <c r="AG2">
+        <f t="shared" si="7"/>
+        <v>36</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" si="7"/>
+        <v>615</v>
+      </c>
+      <c r="AI2">
+        <f>AB2*$J2</f>
+        <v>784</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" ref="AJ2:AO2" si="8">AC2*$J2</f>
+        <v>238</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="8"/>
+        <v>654.5</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="8"/>
+        <v>126</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="8"/>
+        <v>224</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="8"/>
+        <v>126</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="8"/>
+        <v>2152.5</v>
+      </c>
+      <c r="AP2">
+        <f>C2*$M2</f>
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" ref="AQ2:AV2" si="9">D2*$M2</f>
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <f>AP2*$J2</f>
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" ref="AX2:BC2" si="10">AQ2*$J2</f>
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BA2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BB2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BC2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BD2">
+        <f>C2*$J2</f>
+        <v>784</v>
+      </c>
+      <c r="BE2">
+        <f t="shared" ref="BE2:BJ11" si="11">D2*$J2</f>
+        <v>238</v>
+      </c>
+      <c r="BF2">
+        <f t="shared" si="11"/>
+        <v>654.5</v>
+      </c>
+      <c r="BG2">
+        <f t="shared" si="11"/>
+        <v>126</v>
+      </c>
+      <c r="BH2">
+        <f t="shared" si="11"/>
+        <v>224</v>
+      </c>
+      <c r="BI2">
+        <f t="shared" si="11"/>
+        <v>126</v>
+      </c>
+      <c r="BJ2">
+        <f t="shared" si="11"/>
+        <v>2152.5</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:62" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -674,8 +1212,224 @@
       <c r="H3" s="5">
         <v>63</v>
       </c>
+      <c r="I3" s="11">
+        <f t="shared" ref="I3:I11" si="12">SUM(C3:H3)</f>
+        <v>628</v>
+      </c>
+      <c r="J3" s="11">
+        <f t="shared" ref="J3:J11" si="13">35/10</f>
+        <v>3.5</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K11" si="14">IF($B3=1,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <f t="shared" ref="L3:L11" si="15">IF($B3=2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <f t="shared" ref="M3:M11" si="16">IF($B3=3,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <f t="shared" ref="N3:N11" si="17">C3*$K3</f>
+        <v>112</v>
+      </c>
+      <c r="O3">
+        <f t="shared" ref="O3:O11" si="18">D3*$K3</f>
+        <v>42</v>
+      </c>
+      <c r="P3">
+        <f t="shared" ref="P3:P11" si="19">E3*$K3</f>
+        <v>126</v>
+      </c>
+      <c r="Q3">
+        <f>F3*$K3</f>
+        <v>78</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="20">G3*$K3</f>
+        <v>207</v>
+      </c>
+      <c r="S3">
+        <f t="shared" ref="S3:S11" si="21">H3*$K3</f>
+        <v>63</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T11" si="22">I3*$K3</f>
+        <v>628</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="23">N3*$J3</f>
+        <v>392</v>
+      </c>
+      <c r="V3">
+        <f t="shared" ref="V3:V11" si="24">O3*$J3</f>
+        <v>147</v>
+      </c>
+      <c r="W3">
+        <f t="shared" ref="W3:W11" si="25">P3*$J3</f>
+        <v>441</v>
+      </c>
+      <c r="X3">
+        <f t="shared" ref="X3:X11" si="26">Q3*$J3</f>
+        <v>273</v>
+      </c>
+      <c r="Y3">
+        <f t="shared" si="6"/>
+        <v>724.5</v>
+      </c>
+      <c r="Z3">
+        <f t="shared" si="6"/>
+        <v>220.5</v>
+      </c>
+      <c r="AA3">
+        <f t="shared" si="6"/>
+        <v>2198</v>
+      </c>
+      <c r="AB3">
+        <f t="shared" ref="AB3:AB11" si="27">C3*$L3</f>
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <f t="shared" ref="AC3:AC11" si="28">D3*$L3</f>
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <f t="shared" ref="AD3:AD11" si="29">E3*$L3</f>
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <f t="shared" ref="AE3:AE11" si="30">F3*$L3</f>
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <f t="shared" ref="AF3:AF11" si="31">G3*$L3</f>
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <f t="shared" ref="AG3:AG11" si="32">H3*$L3</f>
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" ref="AH3:AH11" si="33">I3*$L3</f>
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" ref="AI3:AI11" si="34">AB3*$J3</f>
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" ref="AJ3:AJ11" si="35">AC3*$J3</f>
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" ref="AK3:AK11" si="36">AD3*$J3</f>
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" ref="AL3:AL11" si="37">AE3*$J3</f>
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" ref="AM3:AM11" si="38">AF3*$J3</f>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" ref="AN3:AN11" si="39">AG3*$J3</f>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" ref="AO3:AO11" si="40">AH3*$J3</f>
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" ref="AP3:AP11" si="41">C3*$M3</f>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" ref="AQ3:AQ11" si="42">D3*$M3</f>
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" ref="AR3:AR11" si="43">E3*$M3</f>
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" ref="AS3:AS11" si="44">F3*$M3</f>
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" ref="AT3:AT11" si="45">G3*$M3</f>
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" ref="AU3:AU11" si="46">H3*$M3</f>
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" ref="AV3:AV11" si="47">I3*$M3</f>
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" ref="AW3:AW11" si="48">AP3*$J3</f>
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" ref="AX3:AX11" si="49">AQ3*$J3</f>
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" ref="AY3:AY11" si="50">AR3*$J3</f>
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" ref="AZ3:AZ11" si="51">AS3*$J3</f>
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <f t="shared" ref="BA3:BA11" si="52">AT3*$J3</f>
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <f t="shared" ref="BB3:BB11" si="53">AU3*$J3</f>
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <f t="shared" ref="BC3:BC11" si="54">AV3*$J3</f>
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <f t="shared" ref="BD3:BD11" si="55">C3*$J3</f>
+        <v>392</v>
+      </c>
+      <c r="BE3">
+        <f t="shared" si="11"/>
+        <v>147</v>
+      </c>
+      <c r="BF3">
+        <f t="shared" si="11"/>
+        <v>441</v>
+      </c>
+      <c r="BG3">
+        <f t="shared" si="11"/>
+        <v>273</v>
+      </c>
+      <c r="BH3">
+        <f t="shared" si="11"/>
+        <v>724.5</v>
+      </c>
+      <c r="BI3">
+        <f t="shared" si="11"/>
+        <v>220.5</v>
+      </c>
+      <c r="BJ3">
+        <f t="shared" si="11"/>
+        <v>2198</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:62" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -700,8 +1454,224 @@
       <c r="H4" s="5">
         <v>57</v>
       </c>
+      <c r="I4" s="11">
+        <f t="shared" si="12"/>
+        <v>840</v>
+      </c>
+      <c r="J4" s="11">
+        <f t="shared" si="13"/>
+        <v>3.5</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <f>F4*$K4</f>
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="41"/>
+        <v>227</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="42"/>
+        <v>154</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="43"/>
+        <v>78</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="44"/>
+        <v>155</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="45"/>
+        <v>169</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="46"/>
+        <v>57</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="47"/>
+        <v>840</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="48"/>
+        <v>794.5</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="49"/>
+        <v>539</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="50"/>
+        <v>273</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="51"/>
+        <v>542.5</v>
+      </c>
+      <c r="BA4">
+        <f t="shared" si="52"/>
+        <v>591.5</v>
+      </c>
+      <c r="BB4">
+        <f t="shared" si="53"/>
+        <v>199.5</v>
+      </c>
+      <c r="BC4">
+        <f t="shared" si="54"/>
+        <v>2940</v>
+      </c>
+      <c r="BD4">
+        <f t="shared" si="55"/>
+        <v>794.5</v>
+      </c>
+      <c r="BE4">
+        <f t="shared" si="11"/>
+        <v>539</v>
+      </c>
+      <c r="BF4">
+        <f t="shared" si="11"/>
+        <v>273</v>
+      </c>
+      <c r="BG4">
+        <f t="shared" si="11"/>
+        <v>542.5</v>
+      </c>
+      <c r="BH4">
+        <f t="shared" si="11"/>
+        <v>591.5</v>
+      </c>
+      <c r="BI4">
+        <f t="shared" si="11"/>
+        <v>199.5</v>
+      </c>
+      <c r="BJ4">
+        <f t="shared" si="11"/>
+        <v>2940</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:62" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -726,8 +1696,224 @@
       <c r="H5" s="5">
         <v>181</v>
       </c>
+      <c r="I5" s="11">
+        <f t="shared" si="12"/>
+        <v>780</v>
+      </c>
+      <c r="J5" s="11">
+        <f t="shared" si="13"/>
+        <v>3.5</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="17"/>
+        <v>166</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="18"/>
+        <v>143</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="19"/>
+        <v>205</v>
+      </c>
+      <c r="Q5">
+        <f>F5*$K5</f>
+        <v>67</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="20"/>
+        <v>18</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="21"/>
+        <v>181</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="22"/>
+        <v>780</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="23"/>
+        <v>581</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="24"/>
+        <v>500.5</v>
+      </c>
+      <c r="W5">
+        <f t="shared" si="25"/>
+        <v>717.5</v>
+      </c>
+      <c r="X5">
+        <f t="shared" si="26"/>
+        <v>234.5</v>
+      </c>
+      <c r="Y5">
+        <f t="shared" si="6"/>
+        <v>63</v>
+      </c>
+      <c r="Z5">
+        <f t="shared" si="6"/>
+        <v>633.5</v>
+      </c>
+      <c r="AA5">
+        <f t="shared" si="6"/>
+        <v>2730</v>
+      </c>
+      <c r="AB5">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <f t="shared" si="55"/>
+        <v>581</v>
+      </c>
+      <c r="BE5">
+        <f t="shared" si="11"/>
+        <v>500.5</v>
+      </c>
+      <c r="BF5">
+        <f t="shared" si="11"/>
+        <v>717.5</v>
+      </c>
+      <c r="BG5">
+        <f t="shared" si="11"/>
+        <v>234.5</v>
+      </c>
+      <c r="BH5">
+        <f t="shared" si="11"/>
+        <v>63</v>
+      </c>
+      <c r="BI5">
+        <f t="shared" si="11"/>
+        <v>633.5</v>
+      </c>
+      <c r="BJ5">
+        <f t="shared" si="11"/>
+        <v>2730</v>
+      </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:62" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -752,8 +1938,224 @@
       <c r="H6" s="5">
         <v>72</v>
       </c>
+      <c r="I6" s="11">
+        <f t="shared" si="12"/>
+        <v>792</v>
+      </c>
+      <c r="J6" s="11">
+        <f t="shared" si="13"/>
+        <v>3.5</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <f>F6*$K6</f>
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="41"/>
+        <v>134</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="42"/>
+        <v>149</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="43"/>
+        <v>162</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="44"/>
+        <v>231</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="45"/>
+        <v>44</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="46"/>
+        <v>72</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="47"/>
+        <v>792</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="48"/>
+        <v>469</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="49"/>
+        <v>521.5</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="50"/>
+        <v>567</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="51"/>
+        <v>808.5</v>
+      </c>
+      <c r="BA6">
+        <f t="shared" si="52"/>
+        <v>154</v>
+      </c>
+      <c r="BB6">
+        <f t="shared" si="53"/>
+        <v>252</v>
+      </c>
+      <c r="BC6">
+        <f t="shared" si="54"/>
+        <v>2772</v>
+      </c>
+      <c r="BD6">
+        <f t="shared" si="55"/>
+        <v>469</v>
+      </c>
+      <c r="BE6">
+        <f t="shared" si="11"/>
+        <v>521.5</v>
+      </c>
+      <c r="BF6">
+        <f t="shared" si="11"/>
+        <v>567</v>
+      </c>
+      <c r="BG6">
+        <f t="shared" si="11"/>
+        <v>808.5</v>
+      </c>
+      <c r="BH6">
+        <f t="shared" si="11"/>
+        <v>154</v>
+      </c>
+      <c r="BI6">
+        <f t="shared" si="11"/>
+        <v>252</v>
+      </c>
+      <c r="BJ6">
+        <f t="shared" si="11"/>
+        <v>2772</v>
+      </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:62" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -778,8 +2180,224 @@
       <c r="H7" s="5">
         <v>65</v>
       </c>
+      <c r="I7" s="11">
+        <f t="shared" si="12"/>
+        <v>640</v>
+      </c>
+      <c r="J7" s="11">
+        <f t="shared" si="13"/>
+        <v>3.5</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <f>F7*$K7</f>
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <f t="shared" si="27"/>
+        <v>109</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="28"/>
+        <v>224</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="29"/>
+        <v>138</v>
+      </c>
+      <c r="AE7">
+        <f t="shared" si="30"/>
+        <v>31</v>
+      </c>
+      <c r="AF7">
+        <f t="shared" si="31"/>
+        <v>73</v>
+      </c>
+      <c r="AG7">
+        <f t="shared" si="32"/>
+        <v>65</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="33"/>
+        <v>640</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="34"/>
+        <v>381.5</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="35"/>
+        <v>784</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="36"/>
+        <v>483</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="37"/>
+        <v>108.5</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="38"/>
+        <v>255.5</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="39"/>
+        <v>227.5</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="40"/>
+        <v>2240</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <f t="shared" si="55"/>
+        <v>381.5</v>
+      </c>
+      <c r="BE7">
+        <f t="shared" si="11"/>
+        <v>784</v>
+      </c>
+      <c r="BF7">
+        <f t="shared" si="11"/>
+        <v>483</v>
+      </c>
+      <c r="BG7">
+        <f t="shared" si="11"/>
+        <v>108.5</v>
+      </c>
+      <c r="BH7">
+        <f t="shared" si="11"/>
+        <v>255.5</v>
+      </c>
+      <c r="BI7">
+        <f t="shared" si="11"/>
+        <v>227.5</v>
+      </c>
+      <c r="BJ7">
+        <f t="shared" si="11"/>
+        <v>2240</v>
+      </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:62" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -804,8 +2422,224 @@
       <c r="H8" s="5">
         <v>242</v>
       </c>
+      <c r="I8" s="11">
+        <f t="shared" si="12"/>
+        <v>730</v>
+      </c>
+      <c r="J8" s="11">
+        <f t="shared" si="13"/>
+        <v>3.5</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <f>F8*$K8</f>
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <f t="shared" si="27"/>
+        <v>154</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="28"/>
+        <v>126</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="29"/>
+        <v>50</v>
+      </c>
+      <c r="AE8">
+        <f t="shared" si="30"/>
+        <v>115</v>
+      </c>
+      <c r="AF8">
+        <f t="shared" si="31"/>
+        <v>43</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="32"/>
+        <v>242</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="33"/>
+        <v>730</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="34"/>
+        <v>539</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="35"/>
+        <v>441</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="36"/>
+        <v>175</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="37"/>
+        <v>402.5</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="38"/>
+        <v>150.5</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="39"/>
+        <v>847</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="40"/>
+        <v>2555</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <f t="shared" si="55"/>
+        <v>539</v>
+      </c>
+      <c r="BE8">
+        <f t="shared" si="11"/>
+        <v>441</v>
+      </c>
+      <c r="BF8">
+        <f t="shared" si="11"/>
+        <v>175</v>
+      </c>
+      <c r="BG8">
+        <f t="shared" si="11"/>
+        <v>402.5</v>
+      </c>
+      <c r="BH8">
+        <f t="shared" si="11"/>
+        <v>150.5</v>
+      </c>
+      <c r="BI8">
+        <f t="shared" si="11"/>
+        <v>847</v>
+      </c>
+      <c r="BJ8">
+        <f t="shared" si="11"/>
+        <v>2555</v>
+      </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:62" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -830,8 +2664,224 @@
       <c r="H9" s="5">
         <v>32</v>
       </c>
+      <c r="I9" s="11">
+        <f t="shared" si="12"/>
+        <v>796</v>
+      </c>
+      <c r="J9" s="11">
+        <f t="shared" si="13"/>
+        <v>3.5</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <f>F9*$K9</f>
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <f t="shared" si="41"/>
+        <v>190</v>
+      </c>
+      <c r="AQ9">
+        <f t="shared" si="42"/>
+        <v>161</v>
+      </c>
+      <c r="AR9">
+        <f t="shared" si="43"/>
+        <v>158</v>
+      </c>
+      <c r="AS9">
+        <f t="shared" si="44"/>
+        <v>172</v>
+      </c>
+      <c r="AT9">
+        <f t="shared" si="45"/>
+        <v>83</v>
+      </c>
+      <c r="AU9">
+        <f t="shared" si="46"/>
+        <v>32</v>
+      </c>
+      <c r="AV9">
+        <f t="shared" si="47"/>
+        <v>796</v>
+      </c>
+      <c r="AW9">
+        <f t="shared" si="48"/>
+        <v>665</v>
+      </c>
+      <c r="AX9">
+        <f t="shared" si="49"/>
+        <v>563.5</v>
+      </c>
+      <c r="AY9">
+        <f t="shared" si="50"/>
+        <v>553</v>
+      </c>
+      <c r="AZ9">
+        <f t="shared" si="51"/>
+        <v>602</v>
+      </c>
+      <c r="BA9">
+        <f t="shared" si="52"/>
+        <v>290.5</v>
+      </c>
+      <c r="BB9">
+        <f t="shared" si="53"/>
+        <v>112</v>
+      </c>
+      <c r="BC9">
+        <f t="shared" si="54"/>
+        <v>2786</v>
+      </c>
+      <c r="BD9">
+        <f t="shared" si="55"/>
+        <v>665</v>
+      </c>
+      <c r="BE9">
+        <f t="shared" si="11"/>
+        <v>563.5</v>
+      </c>
+      <c r="BF9">
+        <f t="shared" si="11"/>
+        <v>553</v>
+      </c>
+      <c r="BG9">
+        <f t="shared" si="11"/>
+        <v>602</v>
+      </c>
+      <c r="BH9">
+        <f t="shared" si="11"/>
+        <v>290.5</v>
+      </c>
+      <c r="BI9">
+        <f t="shared" si="11"/>
+        <v>112</v>
+      </c>
+      <c r="BJ9">
+        <f t="shared" si="11"/>
+        <v>2786</v>
+      </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:62" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -856,8 +2906,224 @@
       <c r="H10" s="5">
         <v>23</v>
       </c>
+      <c r="I10" s="11">
+        <f t="shared" si="12"/>
+        <v>399</v>
+      </c>
+      <c r="J10" s="11">
+        <f t="shared" si="13"/>
+        <v>3.5</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <f>F10*$K10</f>
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <f t="shared" si="41"/>
+        <v>33</v>
+      </c>
+      <c r="AQ10">
+        <f t="shared" si="42"/>
+        <v>4</v>
+      </c>
+      <c r="AR10">
+        <f t="shared" si="43"/>
+        <v>10</v>
+      </c>
+      <c r="AS10">
+        <f t="shared" si="44"/>
+        <v>232</v>
+      </c>
+      <c r="AT10">
+        <f t="shared" si="45"/>
+        <v>97</v>
+      </c>
+      <c r="AU10">
+        <f t="shared" si="46"/>
+        <v>23</v>
+      </c>
+      <c r="AV10">
+        <f t="shared" si="47"/>
+        <v>399</v>
+      </c>
+      <c r="AW10">
+        <f t="shared" si="48"/>
+        <v>115.5</v>
+      </c>
+      <c r="AX10">
+        <f t="shared" si="49"/>
+        <v>14</v>
+      </c>
+      <c r="AY10">
+        <f t="shared" si="50"/>
+        <v>35</v>
+      </c>
+      <c r="AZ10">
+        <f t="shared" si="51"/>
+        <v>812</v>
+      </c>
+      <c r="BA10">
+        <f t="shared" si="52"/>
+        <v>339.5</v>
+      </c>
+      <c r="BB10">
+        <f t="shared" si="53"/>
+        <v>80.5</v>
+      </c>
+      <c r="BC10">
+        <f t="shared" si="54"/>
+        <v>1396.5</v>
+      </c>
+      <c r="BD10">
+        <f t="shared" si="55"/>
+        <v>115.5</v>
+      </c>
+      <c r="BE10">
+        <f t="shared" si="11"/>
+        <v>14</v>
+      </c>
+      <c r="BF10">
+        <f t="shared" si="11"/>
+        <v>35</v>
+      </c>
+      <c r="BG10">
+        <f t="shared" si="11"/>
+        <v>812</v>
+      </c>
+      <c r="BH10">
+        <f t="shared" si="11"/>
+        <v>339.5</v>
+      </c>
+      <c r="BI10">
+        <f t="shared" si="11"/>
+        <v>80.5</v>
+      </c>
+      <c r="BJ10">
+        <f t="shared" si="11"/>
+        <v>1396.5</v>
+      </c>
     </row>
-    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="6">
         <v>10</v>
       </c>
@@ -881,6 +3147,708 @@
       </c>
       <c r="H11" s="8">
         <v>61</v>
+      </c>
+      <c r="I11" s="11">
+        <f t="shared" si="12"/>
+        <v>840</v>
+      </c>
+      <c r="J11" s="11">
+        <f t="shared" si="13"/>
+        <v>3.5</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <f>F11*$K11</f>
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <f t="shared" si="41"/>
+        <v>244</v>
+      </c>
+      <c r="AQ11">
+        <f t="shared" si="42"/>
+        <v>81</v>
+      </c>
+      <c r="AR11">
+        <f t="shared" si="43"/>
+        <v>153</v>
+      </c>
+      <c r="AS11">
+        <f t="shared" si="44"/>
+        <v>126</v>
+      </c>
+      <c r="AT11">
+        <f t="shared" si="45"/>
+        <v>175</v>
+      </c>
+      <c r="AU11">
+        <f t="shared" si="46"/>
+        <v>61</v>
+      </c>
+      <c r="AV11">
+        <f t="shared" si="47"/>
+        <v>840</v>
+      </c>
+      <c r="AW11">
+        <f t="shared" si="48"/>
+        <v>854</v>
+      </c>
+      <c r="AX11">
+        <f t="shared" si="49"/>
+        <v>283.5</v>
+      </c>
+      <c r="AY11">
+        <f t="shared" si="50"/>
+        <v>535.5</v>
+      </c>
+      <c r="AZ11">
+        <f t="shared" si="51"/>
+        <v>441</v>
+      </c>
+      <c r="BA11">
+        <f t="shared" si="52"/>
+        <v>612.5</v>
+      </c>
+      <c r="BB11">
+        <f t="shared" si="53"/>
+        <v>213.5</v>
+      </c>
+      <c r="BC11">
+        <f t="shared" si="54"/>
+        <v>2940</v>
+      </c>
+      <c r="BD11">
+        <f t="shared" si="55"/>
+        <v>854</v>
+      </c>
+      <c r="BE11">
+        <f t="shared" si="11"/>
+        <v>283.5</v>
+      </c>
+      <c r="BF11">
+        <f t="shared" si="11"/>
+        <v>535.5</v>
+      </c>
+      <c r="BG11">
+        <f t="shared" si="11"/>
+        <v>441</v>
+      </c>
+      <c r="BH11">
+        <f t="shared" si="11"/>
+        <v>612.5</v>
+      </c>
+      <c r="BI11">
+        <f t="shared" si="11"/>
+        <v>213.5</v>
+      </c>
+      <c r="BJ11">
+        <f t="shared" si="11"/>
+        <v>2940</v>
+      </c>
+    </row>
+    <row r="12" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="M12" t="s">
+        <v>30</v>
+      </c>
+      <c r="U12">
+        <f>SUM(U2:U11)</f>
+        <v>973</v>
+      </c>
+      <c r="V12">
+        <f t="shared" ref="V12:AA12" si="56">SUM(V1:V11)</f>
+        <v>647.5</v>
+      </c>
+      <c r="W12">
+        <f t="shared" si="56"/>
+        <v>1158.5</v>
+      </c>
+      <c r="X12">
+        <f t="shared" si="56"/>
+        <v>507.5</v>
+      </c>
+      <c r="Y12">
+        <f t="shared" si="56"/>
+        <v>787.5</v>
+      </c>
+      <c r="Z12">
+        <f t="shared" si="56"/>
+        <v>854</v>
+      </c>
+      <c r="AA12" s="16">
+        <f t="shared" si="56"/>
+        <v>4928</v>
+      </c>
+      <c r="AI12" s="16">
+        <f>SUM(AI1:AI11)</f>
+        <v>1704.5</v>
+      </c>
+      <c r="AJ12">
+        <f t="shared" ref="AJ12:AO12" si="57">SUM(AJ1:AJ11)</f>
+        <v>1463</v>
+      </c>
+      <c r="AK12">
+        <f t="shared" si="57"/>
+        <v>1312.5</v>
+      </c>
+      <c r="AL12">
+        <f t="shared" si="57"/>
+        <v>637</v>
+      </c>
+      <c r="AM12">
+        <f t="shared" si="57"/>
+        <v>630</v>
+      </c>
+      <c r="AN12">
+        <f t="shared" si="57"/>
+        <v>1200.5</v>
+      </c>
+      <c r="AO12" s="16">
+        <f t="shared" si="57"/>
+        <v>6947.5</v>
+      </c>
+      <c r="AW12">
+        <f>SUM(AW1:AW11)</f>
+        <v>2898</v>
+      </c>
+      <c r="AX12">
+        <f t="shared" ref="AX12:BC12" si="58">SUM(AX1:AX11)</f>
+        <v>1921.5</v>
+      </c>
+      <c r="AY12">
+        <f t="shared" si="58"/>
+        <v>1963.5</v>
+      </c>
+      <c r="AZ12">
+        <f t="shared" si="58"/>
+        <v>3206</v>
+      </c>
+      <c r="BA12">
+        <f t="shared" si="58"/>
+        <v>1988</v>
+      </c>
+      <c r="BB12">
+        <f t="shared" si="58"/>
+        <v>857.5</v>
+      </c>
+      <c r="BC12" s="16">
+        <f t="shared" si="58"/>
+        <v>12834.5</v>
+      </c>
+      <c r="BD12" s="19">
+        <f t="shared" ref="BD12" si="59">SUM(BD1:BD11)</f>
+        <v>5575.5</v>
+      </c>
+      <c r="BE12" s="19">
+        <f t="shared" ref="BE12" si="60">SUM(BE1:BE11)</f>
+        <v>4032</v>
+      </c>
+      <c r="BF12" s="19">
+        <f t="shared" ref="BF12" si="61">SUM(BF1:BF11)</f>
+        <v>4434.5</v>
+      </c>
+      <c r="BG12" s="19">
+        <f t="shared" ref="BG12" si="62">SUM(BG1:BG11)</f>
+        <v>4350.5</v>
+      </c>
+      <c r="BH12" s="19">
+        <f t="shared" ref="BH12" si="63">SUM(BH1:BH11)</f>
+        <v>3405.5</v>
+      </c>
+      <c r="BI12" s="19">
+        <f t="shared" ref="BI12" si="64">SUM(BI1:BI11)</f>
+        <v>2912</v>
+      </c>
+      <c r="BJ12" s="16">
+        <f t="shared" ref="BJ12" si="65">SUM(BJ1:BJ11)</f>
+        <v>24710</v>
+      </c>
+    </row>
+    <row r="13" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="20">
+        <f>_xlfn.VAR.S(C2:C11)</f>
+        <v>4257.5666666666675</v>
+      </c>
+      <c r="D13" s="20">
+        <f t="shared" ref="D13:I13" si="66">_xlfn.VAR.S(D2:D11)</f>
+        <v>4288.1777777777788</v>
+      </c>
+      <c r="E13" s="20">
+        <f t="shared" si="66"/>
+        <v>3854.0111111111119</v>
+      </c>
+      <c r="F13" s="20">
+        <f t="shared" si="66"/>
+        <v>5357.7888888888892</v>
+      </c>
+      <c r="G13" s="20">
+        <f t="shared" si="66"/>
+        <v>4132.6777777777788</v>
+      </c>
+      <c r="H13" s="20">
+        <f t="shared" si="66"/>
+        <v>5033.2888888888892</v>
+      </c>
+      <c r="I13" s="20">
+        <f t="shared" si="66"/>
+        <v>18936.666666666668</v>
+      </c>
+      <c r="M13" t="s">
+        <v>31</v>
+      </c>
+      <c r="N13">
+        <f>_xlfn.VAR.S(N2:N11)</f>
+        <v>3596.8444444444444</v>
+      </c>
+      <c r="O13">
+        <f t="shared" ref="O13:T13" si="67">_xlfn.VAR.S(O2:O11)</f>
+        <v>2087.8333333333335</v>
+      </c>
+      <c r="P13">
+        <f t="shared" si="67"/>
+        <v>5216.1000000000004</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="67"/>
+        <v>941.16666666666663</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="67"/>
+        <v>4234.5</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="67"/>
+        <v>3419.6000000000004</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="67"/>
+        <v>89393.066666666666</v>
+      </c>
+      <c r="AB13">
+        <f>_xlfn.VAR.S(AB2:AB11)</f>
+        <v>6895.1222222222223</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" ref="AC13:AH13" si="68">_xlfn.VAR.S(AC2:AC11)</f>
+        <v>5911.5111111111109</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" si="68"/>
+        <v>4716.7222222222226</v>
+      </c>
+      <c r="AE13">
+        <f t="shared" si="68"/>
+        <v>1352.1777777777779</v>
+      </c>
+      <c r="AF13">
+        <f t="shared" si="68"/>
+        <v>892.66666666666663</v>
+      </c>
+      <c r="AG13">
+        <f t="shared" si="68"/>
+        <v>5813.344444444444</v>
+      </c>
+      <c r="AH13">
+        <f t="shared" si="68"/>
+        <v>102966.94444444444</v>
+      </c>
+      <c r="AP13">
+        <f>_xlfn.VAR.S(AP2:AP11)</f>
+        <v>10850.177777777779</v>
+      </c>
+      <c r="AQ13">
+        <f t="shared" ref="AQ13:AV13" si="69">_xlfn.VAR.S(AQ2:AQ11)</f>
+        <v>5363.8777777777777</v>
+      </c>
+      <c r="AR13">
+        <f t="shared" si="69"/>
+        <v>5480.9888888888891</v>
+      </c>
+      <c r="AS13">
+        <f>_xlfn.VAR.S(AS2:AS11)</f>
+        <v>10307.155555555555</v>
+      </c>
+      <c r="AT13">
+        <f t="shared" si="69"/>
+        <v>5017.5111111111109</v>
+      </c>
+      <c r="AU13">
+        <f t="shared" si="69"/>
+        <v>856.05555555555554</v>
+      </c>
+      <c r="AV13">
+        <f t="shared" si="69"/>
+        <v>165176.90000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="20">
+        <f>$M$15*C13</f>
+        <v>372537.08333333343</v>
+      </c>
+      <c r="D14" s="20">
+        <f t="shared" ref="D14" si="70">$M$15*D13</f>
+        <v>375215.55555555562</v>
+      </c>
+      <c r="E14" s="20">
+        <f t="shared" ref="E14" si="71">$M$15*E13</f>
+        <v>337225.97222222231</v>
+      </c>
+      <c r="F14" s="20">
+        <f t="shared" ref="F14" si="72">$M$15*F13</f>
+        <v>468806.52777777781</v>
+      </c>
+      <c r="G14" s="20">
+        <f t="shared" ref="G14" si="73">$M$15*G13</f>
+        <v>361609.30555555562</v>
+      </c>
+      <c r="H14" s="20">
+        <f t="shared" ref="H14" si="74">$M$15*H13</f>
+        <v>440412.77777777781</v>
+      </c>
+      <c r="I14" s="20">
+        <f t="shared" ref="I14" si="75">$M$15*I13</f>
+        <v>1656958.3333333335</v>
+      </c>
+      <c r="M14" t="s">
+        <v>33</v>
+      </c>
+      <c r="N14">
+        <f>$M$15*N13</f>
+        <v>314723.88888888888</v>
+      </c>
+      <c r="O14">
+        <f t="shared" ref="O14:T14" si="76">$M$15*O13</f>
+        <v>182685.41666666669</v>
+      </c>
+      <c r="P14">
+        <f t="shared" si="76"/>
+        <v>456408.75000000006</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="76"/>
+        <v>82352.083333333328</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="76"/>
+        <v>370518.75</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="76"/>
+        <v>299215.00000000006</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="76"/>
+        <v>7821893.333333333</v>
+      </c>
+      <c r="AB14">
+        <f>$M$15*AB13</f>
+        <v>603323.1944444445</v>
+      </c>
+      <c r="AC14">
+        <f t="shared" ref="AC14" si="77">$M$15*AC13</f>
+        <v>517257.22222222219</v>
+      </c>
+      <c r="AD14">
+        <f t="shared" ref="AD14" si="78">$M$15*AD13</f>
+        <v>412713.1944444445</v>
+      </c>
+      <c r="AE14">
+        <f t="shared" ref="AE14" si="79">$M$15*AE13</f>
+        <v>118315.55555555556</v>
+      </c>
+      <c r="AF14">
+        <f t="shared" ref="AF14" si="80">$M$15*AF13</f>
+        <v>78108.333333333328</v>
+      </c>
+      <c r="AG14">
+        <f t="shared" ref="AG14" si="81">$M$15*AG13</f>
+        <v>508667.63888888888</v>
+      </c>
+      <c r="AH14">
+        <f t="shared" ref="AH14" si="82">$M$15*AH13</f>
+        <v>9009607.6388888881</v>
+      </c>
+      <c r="AP14">
+        <f>$M$15*AP13</f>
+        <v>949390.55555555562</v>
+      </c>
+      <c r="AQ14">
+        <f t="shared" ref="AQ14" si="83">$M$15*AQ13</f>
+        <v>469339.30555555556</v>
+      </c>
+      <c r="AR14">
+        <f t="shared" ref="AR14" si="84">$M$15*AR13</f>
+        <v>479586.52777777781</v>
+      </c>
+      <c r="AS14">
+        <f t="shared" ref="AS14" si="85">$M$15*AS13</f>
+        <v>901876.11111111112</v>
+      </c>
+      <c r="AT14">
+        <f t="shared" ref="AT14" si="86">$M$15*AT13</f>
+        <v>439032.22222222219</v>
+      </c>
+      <c r="AU14">
+        <f t="shared" ref="AU14" si="87">$M$15*AU13</f>
+        <v>74904.861111111109</v>
+      </c>
+      <c r="AV14">
+        <f t="shared" ref="AV14" si="88">$M$15*AV13</f>
+        <v>14452978.750000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="L15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15" s="16">
+        <f>(35^2)/10*(1-(10/35))</f>
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="17">
+        <f>SQRT(C14)/BD12</f>
+        <v>0.10947146621487054</v>
+      </c>
+      <c r="D16" s="17">
+        <f t="shared" ref="D16:I16" si="89">SQRT(D14)/BE12</f>
+        <v>0.15192172886539346</v>
+      </c>
+      <c r="E16" s="17">
+        <f t="shared" si="89"/>
+        <v>0.13095311951267588</v>
+      </c>
+      <c r="F16" s="17">
+        <f t="shared" si="89"/>
+        <v>0.15738293936075731</v>
+      </c>
+      <c r="G16" s="17">
+        <f t="shared" si="89"/>
+        <v>0.17657894363220863</v>
+      </c>
+      <c r="H16" s="17">
+        <f t="shared" si="89"/>
+        <v>0.22789698766793456</v>
+      </c>
+      <c r="I16" s="17">
+        <f t="shared" si="89"/>
+        <v>5.2093441354391638E-2</v>
+      </c>
+      <c r="M16" t="s">
+        <v>34</v>
+      </c>
+      <c r="N16" s="17">
+        <f>SQRT(N14)/U12</f>
+        <v>0.57656996378352732</v>
+      </c>
+      <c r="O16" s="17">
+        <f t="shared" ref="O16:T16" si="90">SQRT(O14)/V12</f>
+        <v>0.66010370033529941</v>
+      </c>
+      <c r="P16" s="17">
+        <f t="shared" si="90"/>
+        <v>0.58315089003649156</v>
+      </c>
+      <c r="Q16" s="17">
+        <f t="shared" si="90"/>
+        <v>0.56545916638805438</v>
+      </c>
+      <c r="R16" s="17">
+        <f t="shared" si="90"/>
+        <v>0.77295557275972693</v>
+      </c>
+      <c r="S16" s="17">
+        <f t="shared" si="90"/>
+        <v>0.6405216445353632</v>
+      </c>
+      <c r="T16" s="17">
+        <f t="shared" si="90"/>
+        <v>0.56752532419697355</v>
+      </c>
+      <c r="AB16" s="17">
+        <f>SQRT(AB14)/AI12</f>
+        <v>0.45569892635228015</v>
+      </c>
+      <c r="AC16" s="17">
+        <f t="shared" ref="AC16" si="91">SQRT(AC14)/AJ12</f>
+        <v>0.49159669615942952</v>
+      </c>
+      <c r="AD16" s="17">
+        <f t="shared" ref="AD16" si="92">SQRT(AD14)/AK12</f>
+        <v>0.48946863172853905</v>
+      </c>
+      <c r="AE16" s="17">
+        <f t="shared" ref="AE16" si="93">SQRT(AE14)/AL12</f>
+        <v>0.53998474561090493</v>
+      </c>
+      <c r="AF16" s="17">
+        <f t="shared" ref="AF16" si="94">SQRT(AF14)/AM12</f>
+        <v>0.44361695453573219</v>
+      </c>
+      <c r="AG16" s="17">
+        <f t="shared" ref="AG16" si="95">SQRT(AG14)/AN12</f>
+        <v>0.59409362218949024</v>
+      </c>
+      <c r="AH16" s="17">
+        <f t="shared" ref="AH16" si="96">SQRT(AH14)/AO12</f>
+        <v>0.43204042404176263</v>
+      </c>
+      <c r="AP16" s="17">
+        <f>SQRT(AP14)/AW12</f>
+        <v>0.33622040922029806</v>
+      </c>
+      <c r="AQ16" s="17">
+        <f t="shared" ref="AQ16" si="97">SQRT(AQ14)/AX12</f>
+        <v>0.35653574271736921</v>
+      </c>
+      <c r="AR16" s="17">
+        <f t="shared" ref="AR16" si="98">SQRT(AR14)/AY12</f>
+        <v>0.35269766277888442</v>
+      </c>
+      <c r="AS16" s="17">
+        <f t="shared" ref="AS16" si="99">SQRT(AS14)/AZ12</f>
+        <v>0.29621696215186122</v>
+      </c>
+      <c r="AT16" s="17">
+        <f t="shared" ref="AT16" si="100">SQRT(AT14)/BA12</f>
+        <v>0.33329731718027883</v>
+      </c>
+      <c r="AU16" s="17">
+        <f t="shared" ref="AU16" si="101">SQRT(AU14)/BB12</f>
+        <v>0.31916912487545152</v>
+      </c>
+      <c r="AV16" s="17">
+        <f>SQRT(AV14)/BC12</f>
+        <v>0.29621000792443913</v>
       </c>
     </row>
   </sheetData>

--- a/data/EjemploDominios.xlsx
+++ b/data/EjemploDominios.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giova\Documents\GB\MisCursos\Muestreo2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F37F4F6-C852-4AE8-ABFF-09818D300B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8729624E-DB31-44DA-98A0-768ABEE15F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{42CC5FC2-8CC7-43C2-B7FE-203DEB835DFD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{42CC5FC2-8CC7-43C2-B7FE-203DEB835DFD}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="Diccionario" sheetId="2" r:id="rId2"/>
+    <sheet name="MAS" sheetId="1" r:id="rId1"/>
+    <sheet name="BER" sheetId="3" r:id="rId2"/>
+    <sheet name="Cuadro" sheetId="4" r:id="rId3"/>
+    <sheet name="Deff" sheetId="5" r:id="rId4"/>
+    <sheet name="Diccionario" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="49">
   <si>
     <t>ID</t>
   </si>
@@ -148,6 +151,48 @@
   <si>
     <t>CVE</t>
   </si>
+  <si>
+    <t>S_y^2</t>
+  </si>
+  <si>
+    <t>Estrategia MAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vivienda </t>
+  </si>
+  <si>
+    <t>Alimentación</t>
+  </si>
+  <si>
+    <t>Educación</t>
+  </si>
+  <si>
+    <t>Transporte</t>
+  </si>
+  <si>
+    <t>Esparcimiento</t>
+  </si>
+  <si>
+    <t>Otros</t>
+  </si>
+  <si>
+    <t>&lt;2 SMMLV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-4 SMMLV </t>
+  </si>
+  <si>
+    <t>&gt;4 SMMLV</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>VAR MAS</t>
+  </si>
+  <si>
+    <t>VAR BER</t>
+  </si>
 </sst>
 </file>
 
@@ -156,7 +201,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,6 +232,15 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -348,8 +402,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -357,8 +410,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -694,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{177A18EF-237E-4601-8DAA-1F2B06E0B3DF}">
-  <dimension ref="A1:BJ16"/>
+  <dimension ref="A1:BJ17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="4.7265625" customWidth="1"/>
@@ -749,199 +805,199 @@
       <c r="M1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="N1" s="13" t="str">
-        <f>C1&amp;"*D1"</f>
+      <c r="N1" s="12" t="str">
+        <f t="shared" ref="N1:S1" si="0">C1&amp;"*D1"</f>
         <v>P2*D1</v>
       </c>
-      <c r="O1" s="13" t="str">
-        <f>D1&amp;"*D1"</f>
+      <c r="O1" s="12" t="str">
+        <f t="shared" si="0"/>
         <v>P3*D1</v>
       </c>
-      <c r="P1" s="13" t="str">
-        <f>E1&amp;"*D1"</f>
+      <c r="P1" s="12" t="str">
+        <f t="shared" si="0"/>
         <v>P4*D1</v>
       </c>
-      <c r="Q1" s="13" t="str">
-        <f>F1&amp;"*D1"</f>
+      <c r="Q1" s="12" t="str">
+        <f t="shared" si="0"/>
         <v>P5*D1</v>
       </c>
-      <c r="R1" s="13" t="str">
-        <f>G1&amp;"*D1"</f>
+      <c r="R1" s="12" t="str">
+        <f t="shared" si="0"/>
         <v>P6*D1</v>
       </c>
-      <c r="S1" s="13" t="str">
-        <f>H1&amp;"*D1"</f>
+      <c r="S1" s="12" t="str">
+        <f t="shared" si="0"/>
         <v>P7*D1</v>
       </c>
-      <c r="T1" s="13" t="s">
+      <c r="T1" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="U1" s="12" t="str">
+      <c r="U1" s="11" t="str">
         <f>N1&amp;"*Fex"</f>
         <v>P2*D1*Fex</v>
       </c>
-      <c r="V1" s="12" t="str">
-        <f t="shared" ref="V1:AA1" si="0">O1&amp;"*Fex"</f>
+      <c r="V1" s="11" t="str">
+        <f t="shared" ref="V1:AA1" si="1">O1&amp;"*Fex"</f>
         <v>P3*D1*Fex</v>
       </c>
-      <c r="W1" s="12" t="str">
-        <f t="shared" si="0"/>
+      <c r="W1" s="11" t="str">
+        <f t="shared" si="1"/>
         <v>P4*D1*Fex</v>
       </c>
-      <c r="X1" s="12" t="str">
-        <f t="shared" si="0"/>
+      <c r="X1" s="11" t="str">
+        <f t="shared" si="1"/>
         <v>P5*D1*Fex</v>
       </c>
-      <c r="Y1" s="12" t="str">
-        <f t="shared" si="0"/>
+      <c r="Y1" s="11" t="str">
+        <f t="shared" si="1"/>
         <v>P6*D1*Fex</v>
       </c>
-      <c r="Z1" s="12" t="str">
-        <f t="shared" si="0"/>
+      <c r="Z1" s="11" t="str">
+        <f t="shared" si="1"/>
         <v>P7*D1*Fex</v>
       </c>
-      <c r="AA1" s="12" t="str">
-        <f t="shared" si="0"/>
+      <c r="AA1" s="11" t="str">
+        <f t="shared" si="1"/>
         <v>Total*D1*Fex</v>
       </c>
-      <c r="AB1" s="13" t="str">
+      <c r="AB1" s="12" t="str">
         <f>C1&amp;"*D2"</f>
         <v>P2*D2</v>
       </c>
-      <c r="AC1" s="13" t="str">
-        <f t="shared" ref="AC1:AI1" si="1">D1&amp;"*D2"</f>
+      <c r="AC1" s="12" t="str">
+        <f t="shared" ref="AC1:AH1" si="2">D1&amp;"*D2"</f>
         <v>P3*D2</v>
       </c>
-      <c r="AD1" s="13" t="str">
-        <f t="shared" si="1"/>
+      <c r="AD1" s="12" t="str">
+        <f t="shared" si="2"/>
         <v>P4*D2</v>
       </c>
-      <c r="AE1" s="13" t="str">
-        <f t="shared" si="1"/>
+      <c r="AE1" s="12" t="str">
+        <f t="shared" si="2"/>
         <v>P5*D2</v>
       </c>
-      <c r="AF1" s="13" t="str">
-        <f t="shared" si="1"/>
+      <c r="AF1" s="12" t="str">
+        <f t="shared" si="2"/>
         <v>P6*D2</v>
       </c>
-      <c r="AG1" s="13" t="str">
-        <f t="shared" si="1"/>
+      <c r="AG1" s="12" t="str">
+        <f t="shared" si="2"/>
         <v>P7*D2</v>
       </c>
-      <c r="AH1" s="13" t="str">
-        <f t="shared" si="1"/>
+      <c r="AH1" s="12" t="str">
+        <f t="shared" si="2"/>
         <v>Total*D2</v>
       </c>
-      <c r="AI1" s="14" t="str">
+      <c r="AI1" s="13" t="str">
         <f>AB1&amp;"*Fex"</f>
         <v>P2*D2*Fex</v>
       </c>
-      <c r="AJ1" s="14" t="str">
-        <f t="shared" ref="AJ1:AO1" si="2">AC1&amp;"*Fex"</f>
+      <c r="AJ1" s="13" t="str">
+        <f t="shared" ref="AJ1:AO1" si="3">AC1&amp;"*Fex"</f>
         <v>P3*D2*Fex</v>
       </c>
-      <c r="AK1" s="14" t="str">
-        <f t="shared" si="2"/>
+      <c r="AK1" s="13" t="str">
+        <f t="shared" si="3"/>
         <v>P4*D2*Fex</v>
       </c>
-      <c r="AL1" s="14" t="str">
-        <f t="shared" si="2"/>
+      <c r="AL1" s="13" t="str">
+        <f t="shared" si="3"/>
         <v>P5*D2*Fex</v>
       </c>
-      <c r="AM1" s="14" t="str">
-        <f t="shared" si="2"/>
+      <c r="AM1" s="13" t="str">
+        <f t="shared" si="3"/>
         <v>P6*D2*Fex</v>
       </c>
-      <c r="AN1" s="14" t="str">
-        <f t="shared" si="2"/>
+      <c r="AN1" s="13" t="str">
+        <f t="shared" si="3"/>
         <v>P7*D2*Fex</v>
       </c>
-      <c r="AO1" s="14" t="str">
-        <f t="shared" si="2"/>
+      <c r="AO1" s="13" t="str">
+        <f t="shared" si="3"/>
         <v>Total*D2*Fex</v>
       </c>
-      <c r="AP1" s="15" t="str">
+      <c r="AP1" s="14" t="str">
         <f>C1&amp;"*D3"</f>
         <v>P2*D3</v>
       </c>
-      <c r="AQ1" s="15" t="str">
-        <f t="shared" ref="AQ1:AU1" si="3">D1&amp;"*D3"</f>
+      <c r="AQ1" s="14" t="str">
+        <f t="shared" ref="AQ1:AU1" si="4">D1&amp;"*D3"</f>
         <v>P3*D3</v>
       </c>
-      <c r="AR1" s="15" t="str">
-        <f t="shared" si="3"/>
+      <c r="AR1" s="14" t="str">
+        <f t="shared" si="4"/>
         <v>P4*D3</v>
       </c>
-      <c r="AS1" s="15" t="str">
-        <f t="shared" si="3"/>
+      <c r="AS1" s="14" t="str">
+        <f t="shared" si="4"/>
         <v>P5*D3</v>
       </c>
-      <c r="AT1" s="15" t="str">
-        <f t="shared" si="3"/>
+      <c r="AT1" s="14" t="str">
+        <f t="shared" si="4"/>
         <v>P6*D3</v>
       </c>
-      <c r="AU1" s="15" t="str">
-        <f t="shared" si="3"/>
+      <c r="AU1" s="14" t="str">
+        <f t="shared" si="4"/>
         <v>P7*D3</v>
       </c>
-      <c r="AV1" s="15" t="str">
+      <c r="AV1" s="14" t="str">
         <f>I1&amp;"*D3"</f>
         <v>Total*D3</v>
       </c>
-      <c r="AW1" s="14" t="str">
+      <c r="AW1" s="13" t="str">
         <f>AP1&amp;"*Fex"</f>
         <v>P2*D3*Fex</v>
       </c>
-      <c r="AX1" s="14" t="str">
-        <f t="shared" ref="AX1:BC1" si="4">AQ1&amp;"*Fex"</f>
+      <c r="AX1" s="13" t="str">
+        <f t="shared" ref="AX1:BC1" si="5">AQ1&amp;"*Fex"</f>
         <v>P3*D3*Fex</v>
       </c>
-      <c r="AY1" s="14" t="str">
-        <f t="shared" si="4"/>
+      <c r="AY1" s="13" t="str">
+        <f t="shared" si="5"/>
         <v>P4*D3*Fex</v>
       </c>
-      <c r="AZ1" s="14" t="str">
-        <f t="shared" si="4"/>
+      <c r="AZ1" s="13" t="str">
+        <f t="shared" si="5"/>
         <v>P5*D3*Fex</v>
       </c>
-      <c r="BA1" s="14" t="str">
-        <f t="shared" si="4"/>
+      <c r="BA1" s="13" t="str">
+        <f t="shared" si="5"/>
         <v>P6*D3*Fex</v>
       </c>
-      <c r="BB1" s="14" t="str">
-        <f t="shared" si="4"/>
+      <c r="BB1" s="13" t="str">
+        <f t="shared" si="5"/>
         <v>P7*D3*Fex</v>
       </c>
-      <c r="BC1" s="14" t="str">
-        <f t="shared" si="4"/>
+      <c r="BC1" s="13" t="str">
+        <f t="shared" si="5"/>
         <v>Total*D3*Fex</v>
       </c>
-      <c r="BD1" s="18" t="str">
+      <c r="BD1" s="17" t="str">
         <f>C1&amp;"*Fex"</f>
         <v>P2*Fex</v>
       </c>
-      <c r="BE1" s="18" t="str">
-        <f t="shared" ref="BE1:BJ1" si="5">D1&amp;"*Fex"</f>
+      <c r="BE1" s="17" t="str">
+        <f t="shared" ref="BE1:BJ1" si="6">D1&amp;"*Fex"</f>
         <v>P3*Fex</v>
       </c>
-      <c r="BF1" s="18" t="str">
-        <f t="shared" si="5"/>
+      <c r="BF1" s="17" t="str">
+        <f t="shared" si="6"/>
         <v>P4*Fex</v>
       </c>
-      <c r="BG1" s="18" t="str">
-        <f t="shared" si="5"/>
+      <c r="BG1" s="17" t="str">
+        <f t="shared" si="6"/>
         <v>P5*Fex</v>
       </c>
-      <c r="BH1" s="18" t="str">
-        <f t="shared" si="5"/>
+      <c r="BH1" s="17" t="str">
+        <f t="shared" si="6"/>
         <v>P6*Fex</v>
       </c>
-      <c r="BI1" s="18" t="str">
-        <f t="shared" si="5"/>
+      <c r="BI1" s="17" t="str">
+        <f t="shared" si="6"/>
         <v>P7*Fex</v>
       </c>
-      <c r="BJ1" s="18" t="str">
-        <f t="shared" si="5"/>
+      <c r="BJ1" s="17" t="str">
+        <f t="shared" si="6"/>
         <v>Total*Fex</v>
       </c>
     </row>
@@ -970,11 +1026,11 @@
       <c r="H2" s="5">
         <v>36</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2">
         <f>SUM(C2:H2)</f>
         <v>615</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2">
         <f>35/10</f>
         <v>3.5</v>
       </c>
@@ -1023,27 +1079,27 @@
         <v>0</v>
       </c>
       <c r="V2">
-        <f t="shared" ref="V2:AA11" si="6">O2*$J2</f>
+        <f t="shared" ref="V2:AA11" si="7">O2*$J2</f>
         <v>0</v>
       </c>
       <c r="W2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="X2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Y2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AA2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AB2">
@@ -1051,27 +1107,27 @@
         <v>224</v>
       </c>
       <c r="AC2">
-        <f t="shared" ref="AC2:AH2" si="7">D2*$L2</f>
+        <f t="shared" ref="AC2:AH2" si="8">D2*$L2</f>
         <v>68</v>
       </c>
       <c r="AD2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>187</v>
       </c>
       <c r="AE2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>36</v>
       </c>
       <c r="AF2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>64</v>
       </c>
       <c r="AG2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>36</v>
       </c>
       <c r="AH2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>615</v>
       </c>
       <c r="AI2">
@@ -1079,27 +1135,27 @@
         <v>784</v>
       </c>
       <c r="AJ2">
-        <f t="shared" ref="AJ2:AO2" si="8">AC2*$J2</f>
+        <f t="shared" ref="AJ2:AO2" si="9">AC2*$J2</f>
         <v>238</v>
       </c>
       <c r="AK2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>654.5</v>
       </c>
       <c r="AL2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>126</v>
       </c>
       <c r="AM2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>224</v>
       </c>
       <c r="AN2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>126</v>
       </c>
       <c r="AO2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2152.5</v>
       </c>
       <c r="AP2">
@@ -1107,27 +1163,27 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <f t="shared" ref="AQ2:AV2" si="9">D2*$M2</f>
+        <f t="shared" ref="AQ2:AV2" si="10">D2*$M2</f>
         <v>0</v>
       </c>
       <c r="AR2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AS2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AT2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AU2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AV2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AW2">
@@ -1135,27 +1191,27 @@
         <v>0</v>
       </c>
       <c r="AX2">
-        <f t="shared" ref="AX2:BC2" si="10">AQ2*$J2</f>
+        <f t="shared" ref="AX2:BC2" si="11">AQ2*$J2</f>
         <v>0</v>
       </c>
       <c r="AY2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AZ2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BA2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BB2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BC2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="BD2">
@@ -1163,27 +1219,27 @@
         <v>784</v>
       </c>
       <c r="BE2">
-        <f t="shared" ref="BE2:BJ11" si="11">D2*$J2</f>
+        <f t="shared" ref="BE2:BJ11" si="12">D2*$J2</f>
         <v>238</v>
       </c>
       <c r="BF2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>654.5</v>
       </c>
       <c r="BG2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>126</v>
       </c>
       <c r="BH2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>224</v>
       </c>
       <c r="BI2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>126</v>
       </c>
       <c r="BJ2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2152.5</v>
       </c>
     </row>
@@ -1212,220 +1268,220 @@
       <c r="H3" s="5">
         <v>63</v>
       </c>
-      <c r="I3" s="11">
-        <f t="shared" ref="I3:I11" si="12">SUM(C3:H3)</f>
+      <c r="I3">
+        <f t="shared" ref="I3:I11" si="13">SUM(C3:H3)</f>
         <v>628</v>
       </c>
-      <c r="J3" s="11">
-        <f t="shared" ref="J3:J11" si="13">35/10</f>
+      <c r="J3">
+        <f t="shared" ref="J3:J11" si="14">35/10</f>
         <v>3.5</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K11" si="14">IF($B3=1,1,0)</f>
+        <f t="shared" ref="K3:K11" si="15">IF($B3=1,1,0)</f>
         <v>1</v>
       </c>
       <c r="L3">
-        <f t="shared" ref="L3:L11" si="15">IF($B3=2,1,0)</f>
+        <f t="shared" ref="L3:L11" si="16">IF($B3=2,1,0)</f>
         <v>0</v>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:M11" si="16">IF($B3=3,1,0)</f>
+        <f t="shared" ref="M3:M11" si="17">IF($B3=3,1,0)</f>
         <v>0</v>
       </c>
       <c r="N3">
-        <f t="shared" ref="N3:N11" si="17">C3*$K3</f>
+        <f t="shared" ref="N3:N11" si="18">C3*$K3</f>
         <v>112</v>
       </c>
       <c r="O3">
-        <f t="shared" ref="O3:O11" si="18">D3*$K3</f>
+        <f t="shared" ref="O3:O11" si="19">D3*$K3</f>
         <v>42</v>
       </c>
       <c r="P3">
-        <f t="shared" ref="P3:P11" si="19">E3*$K3</f>
+        <f t="shared" ref="P3:P11" si="20">E3*$K3</f>
         <v>126</v>
       </c>
       <c r="Q3">
-        <f>F3*$K3</f>
+        <f t="shared" ref="Q3:Q11" si="21">F3*$K3</f>
         <v>78</v>
       </c>
       <c r="R3">
-        <f t="shared" ref="R3:R11" si="20">G3*$K3</f>
+        <f t="shared" ref="R3:R11" si="22">G3*$K3</f>
         <v>207</v>
       </c>
       <c r="S3">
-        <f t="shared" ref="S3:S11" si="21">H3*$K3</f>
+        <f t="shared" ref="S3:S11" si="23">H3*$K3</f>
         <v>63</v>
       </c>
       <c r="T3">
-        <f t="shared" ref="T3:T11" si="22">I3*$K3</f>
+        <f t="shared" ref="T3:T11" si="24">I3*$K3</f>
         <v>628</v>
       </c>
       <c r="U3">
-        <f t="shared" ref="U3:U11" si="23">N3*$J3</f>
+        <f t="shared" ref="U3:U11" si="25">N3*$J3</f>
         <v>392</v>
       </c>
       <c r="V3">
-        <f t="shared" ref="V3:V11" si="24">O3*$J3</f>
+        <f t="shared" ref="V3:V11" si="26">O3*$J3</f>
         <v>147</v>
       </c>
       <c r="W3">
-        <f t="shared" ref="W3:W11" si="25">P3*$J3</f>
+        <f t="shared" ref="W3:W11" si="27">P3*$J3</f>
         <v>441</v>
       </c>
       <c r="X3">
-        <f t="shared" ref="X3:X11" si="26">Q3*$J3</f>
+        <f t="shared" ref="X3:X11" si="28">Q3*$J3</f>
         <v>273</v>
       </c>
       <c r="Y3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>724.5</v>
       </c>
       <c r="Z3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>220.5</v>
       </c>
       <c r="AA3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2198</v>
       </c>
       <c r="AB3">
-        <f t="shared" ref="AB3:AB11" si="27">C3*$L3</f>
+        <f t="shared" ref="AB3:AB11" si="29">C3*$L3</f>
         <v>0</v>
       </c>
       <c r="AC3">
-        <f t="shared" ref="AC3:AC11" si="28">D3*$L3</f>
+        <f t="shared" ref="AC3:AC11" si="30">D3*$L3</f>
         <v>0</v>
       </c>
       <c r="AD3">
-        <f t="shared" ref="AD3:AD11" si="29">E3*$L3</f>
+        <f t="shared" ref="AD3:AD11" si="31">E3*$L3</f>
         <v>0</v>
       </c>
       <c r="AE3">
-        <f t="shared" ref="AE3:AE11" si="30">F3*$L3</f>
+        <f t="shared" ref="AE3:AE11" si="32">F3*$L3</f>
         <v>0</v>
       </c>
       <c r="AF3">
-        <f t="shared" ref="AF3:AF11" si="31">G3*$L3</f>
+        <f t="shared" ref="AF3:AF11" si="33">G3*$L3</f>
         <v>0</v>
       </c>
       <c r="AG3">
-        <f t="shared" ref="AG3:AG11" si="32">H3*$L3</f>
+        <f t="shared" ref="AG3:AG11" si="34">H3*$L3</f>
         <v>0</v>
       </c>
       <c r="AH3">
-        <f t="shared" ref="AH3:AH11" si="33">I3*$L3</f>
+        <f t="shared" ref="AH3:AH11" si="35">I3*$L3</f>
         <v>0</v>
       </c>
       <c r="AI3">
-        <f t="shared" ref="AI3:AI11" si="34">AB3*$J3</f>
+        <f t="shared" ref="AI3:AI11" si="36">AB3*$J3</f>
         <v>0</v>
       </c>
       <c r="AJ3">
-        <f t="shared" ref="AJ3:AJ11" si="35">AC3*$J3</f>
+        <f t="shared" ref="AJ3:AJ11" si="37">AC3*$J3</f>
         <v>0</v>
       </c>
       <c r="AK3">
-        <f t="shared" ref="AK3:AK11" si="36">AD3*$J3</f>
+        <f t="shared" ref="AK3:AK11" si="38">AD3*$J3</f>
         <v>0</v>
       </c>
       <c r="AL3">
-        <f t="shared" ref="AL3:AL11" si="37">AE3*$J3</f>
+        <f t="shared" ref="AL3:AL11" si="39">AE3*$J3</f>
         <v>0</v>
       </c>
       <c r="AM3">
-        <f t="shared" ref="AM3:AM11" si="38">AF3*$J3</f>
+        <f t="shared" ref="AM3:AM11" si="40">AF3*$J3</f>
         <v>0</v>
       </c>
       <c r="AN3">
-        <f t="shared" ref="AN3:AN11" si="39">AG3*$J3</f>
+        <f t="shared" ref="AN3:AN11" si="41">AG3*$J3</f>
         <v>0</v>
       </c>
       <c r="AO3">
-        <f t="shared" ref="AO3:AO11" si="40">AH3*$J3</f>
+        <f t="shared" ref="AO3:AO11" si="42">AH3*$J3</f>
         <v>0</v>
       </c>
       <c r="AP3">
-        <f t="shared" ref="AP3:AP11" si="41">C3*$M3</f>
+        <f t="shared" ref="AP3:AP11" si="43">C3*$M3</f>
         <v>0</v>
       </c>
       <c r="AQ3">
-        <f t="shared" ref="AQ3:AQ11" si="42">D3*$M3</f>
+        <f t="shared" ref="AQ3:AQ11" si="44">D3*$M3</f>
         <v>0</v>
       </c>
       <c r="AR3">
-        <f t="shared" ref="AR3:AR11" si="43">E3*$M3</f>
+        <f t="shared" ref="AR3:AR11" si="45">E3*$M3</f>
         <v>0</v>
       </c>
       <c r="AS3">
-        <f t="shared" ref="AS3:AS11" si="44">F3*$M3</f>
+        <f t="shared" ref="AS3:AS11" si="46">F3*$M3</f>
         <v>0</v>
       </c>
       <c r="AT3">
-        <f t="shared" ref="AT3:AT11" si="45">G3*$M3</f>
+        <f t="shared" ref="AT3:AT11" si="47">G3*$M3</f>
         <v>0</v>
       </c>
       <c r="AU3">
-        <f t="shared" ref="AU3:AU11" si="46">H3*$M3</f>
+        <f t="shared" ref="AU3:AU11" si="48">H3*$M3</f>
         <v>0</v>
       </c>
       <c r="AV3">
-        <f t="shared" ref="AV3:AV11" si="47">I3*$M3</f>
+        <f t="shared" ref="AV3:AV11" si="49">I3*$M3</f>
         <v>0</v>
       </c>
       <c r="AW3">
-        <f t="shared" ref="AW3:AW11" si="48">AP3*$J3</f>
+        <f t="shared" ref="AW3:AW11" si="50">AP3*$J3</f>
         <v>0</v>
       </c>
       <c r="AX3">
-        <f t="shared" ref="AX3:AX11" si="49">AQ3*$J3</f>
+        <f t="shared" ref="AX3:AX11" si="51">AQ3*$J3</f>
         <v>0</v>
       </c>
       <c r="AY3">
-        <f t="shared" ref="AY3:AY11" si="50">AR3*$J3</f>
+        <f t="shared" ref="AY3:AY11" si="52">AR3*$J3</f>
         <v>0</v>
       </c>
       <c r="AZ3">
-        <f t="shared" ref="AZ3:AZ11" si="51">AS3*$J3</f>
+        <f t="shared" ref="AZ3:AZ11" si="53">AS3*$J3</f>
         <v>0</v>
       </c>
       <c r="BA3">
-        <f t="shared" ref="BA3:BA11" si="52">AT3*$J3</f>
+        <f t="shared" ref="BA3:BA11" si="54">AT3*$J3</f>
         <v>0</v>
       </c>
       <c r="BB3">
-        <f t="shared" ref="BB3:BB11" si="53">AU3*$J3</f>
+        <f t="shared" ref="BB3:BB11" si="55">AU3*$J3</f>
         <v>0</v>
       </c>
       <c r="BC3">
-        <f t="shared" ref="BC3:BC11" si="54">AV3*$J3</f>
+        <f t="shared" ref="BC3:BC11" si="56">AV3*$J3</f>
         <v>0</v>
       </c>
       <c r="BD3">
-        <f t="shared" ref="BD3:BD11" si="55">C3*$J3</f>
+        <f t="shared" ref="BD3:BD11" si="57">C3*$J3</f>
         <v>392</v>
       </c>
       <c r="BE3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>147</v>
       </c>
       <c r="BF3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>441</v>
       </c>
       <c r="BG3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>273</v>
       </c>
       <c r="BH3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>724.5</v>
       </c>
       <c r="BI3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>220.5</v>
       </c>
       <c r="BJ3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2198</v>
       </c>
     </row>
@@ -1454,220 +1510,220 @@
       <c r="H4" s="5">
         <v>57</v>
       </c>
-      <c r="I4" s="11">
-        <f t="shared" si="12"/>
+      <c r="I4">
+        <f t="shared" si="13"/>
         <v>840</v>
       </c>
-      <c r="J4" s="11">
-        <f t="shared" si="13"/>
+      <c r="J4">
+        <f t="shared" si="14"/>
         <v>3.5</v>
       </c>
       <c r="K4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="N4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="O4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q4">
-        <f>F4*$K4</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="R4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="S4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="T4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="U4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="V4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="W4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="X4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="Y4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AA4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AB4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AC4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AD4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AF4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AG4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AH4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AI4">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AJ4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AK4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AL4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AM4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AN4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AO4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AP4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>227</v>
       </c>
       <c r="AQ4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>154</v>
       </c>
       <c r="AR4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>78</v>
       </c>
       <c r="AS4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>155</v>
       </c>
       <c r="AT4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>169</v>
       </c>
       <c r="AU4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>57</v>
       </c>
       <c r="AV4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>840</v>
       </c>
       <c r="AW4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>794.5</v>
       </c>
       <c r="AX4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>539</v>
       </c>
       <c r="AY4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>273</v>
       </c>
       <c r="AZ4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>542.5</v>
       </c>
       <c r="BA4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>591.5</v>
       </c>
       <c r="BB4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>199.5</v>
       </c>
       <c r="BC4">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>2940</v>
       </c>
       <c r="BD4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>794.5</v>
       </c>
       <c r="BE4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>539</v>
       </c>
       <c r="BF4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>273</v>
       </c>
       <c r="BG4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>542.5</v>
       </c>
       <c r="BH4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>591.5</v>
       </c>
       <c r="BI4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>199.5</v>
       </c>
       <c r="BJ4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2940</v>
       </c>
     </row>
@@ -1696,220 +1752,220 @@
       <c r="H5" s="5">
         <v>181</v>
       </c>
-      <c r="I5" s="11">
-        <f t="shared" si="12"/>
+      <c r="I5">
+        <f t="shared" si="13"/>
         <v>780</v>
       </c>
-      <c r="J5" s="11">
-        <f t="shared" si="13"/>
+      <c r="J5">
+        <f t="shared" si="14"/>
         <v>3.5</v>
       </c>
       <c r="K5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="L5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>166</v>
       </c>
       <c r="O5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>143</v>
       </c>
       <c r="P5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>205</v>
       </c>
       <c r="Q5">
-        <f>F5*$K5</f>
+        <f t="shared" si="21"/>
         <v>67</v>
       </c>
       <c r="R5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>18</v>
       </c>
       <c r="S5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>181</v>
       </c>
       <c r="T5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>780</v>
       </c>
       <c r="U5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>581</v>
       </c>
       <c r="V5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>500.5</v>
       </c>
       <c r="W5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>717.5</v>
       </c>
       <c r="X5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>234.5</v>
       </c>
       <c r="Y5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>63</v>
       </c>
       <c r="Z5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>633.5</v>
       </c>
       <c r="AA5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2730</v>
       </c>
       <c r="AB5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AC5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AD5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AF5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AG5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AH5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AI5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AJ5">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AK5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AL5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AM5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AN5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AO5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AP5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AQ5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="AR5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AS5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="AT5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AU5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="AV5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AW5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="AX5">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="AY5">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="AZ5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="BA5">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="BB5">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="BC5">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="BD5">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>581</v>
       </c>
       <c r="BE5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>500.5</v>
       </c>
       <c r="BF5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>717.5</v>
       </c>
       <c r="BG5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>234.5</v>
       </c>
       <c r="BH5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>63</v>
       </c>
       <c r="BI5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>633.5</v>
       </c>
       <c r="BJ5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2730</v>
       </c>
     </row>
@@ -1938,220 +1994,220 @@
       <c r="H6" s="5">
         <v>72</v>
       </c>
-      <c r="I6" s="11">
-        <f t="shared" si="12"/>
+      <c r="I6">
+        <f t="shared" si="13"/>
         <v>792</v>
       </c>
-      <c r="J6" s="11">
-        <f t="shared" si="13"/>
+      <c r="J6">
+        <f t="shared" si="14"/>
         <v>3.5</v>
       </c>
       <c r="K6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="N6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="O6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q6">
-        <f>F6*$K6</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="R6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="S6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="T6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="U6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="V6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="W6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="X6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="Y6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AA6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AB6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AC6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AD6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AF6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AG6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AH6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AI6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AJ6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AK6">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AL6">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AM6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AN6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AO6">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AP6">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>134</v>
       </c>
       <c r="AQ6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>149</v>
       </c>
       <c r="AR6">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>162</v>
       </c>
       <c r="AS6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>231</v>
       </c>
       <c r="AT6">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>44</v>
       </c>
       <c r="AU6">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>72</v>
       </c>
       <c r="AV6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>792</v>
       </c>
       <c r="AW6">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>469</v>
       </c>
       <c r="AX6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>521.5</v>
       </c>
       <c r="AY6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>567</v>
       </c>
       <c r="AZ6">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>808.5</v>
       </c>
       <c r="BA6">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>154</v>
       </c>
       <c r="BB6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>252</v>
       </c>
       <c r="BC6">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>2772</v>
       </c>
       <c r="BD6">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>469</v>
       </c>
       <c r="BE6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>521.5</v>
       </c>
       <c r="BF6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>567</v>
       </c>
       <c r="BG6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>808.5</v>
       </c>
       <c r="BH6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>154</v>
       </c>
       <c r="BI6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>252</v>
       </c>
       <c r="BJ6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2772</v>
       </c>
     </row>
@@ -2180,220 +2236,220 @@
       <c r="H7" s="5">
         <v>65</v>
       </c>
-      <c r="I7" s="11">
-        <f t="shared" si="12"/>
+      <c r="I7">
+        <f t="shared" si="13"/>
         <v>640</v>
       </c>
-      <c r="J7" s="11">
-        <f t="shared" si="13"/>
+      <c r="J7">
+        <f t="shared" si="14"/>
         <v>3.5</v>
       </c>
       <c r="K7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="M7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="O7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q7">
-        <f>F7*$K7</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="R7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="S7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="T7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="U7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="V7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="W7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="X7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="Y7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AA7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AB7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>109</v>
       </c>
       <c r="AC7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>224</v>
       </c>
       <c r="AD7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>138</v>
       </c>
       <c r="AE7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>31</v>
       </c>
       <c r="AF7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>73</v>
       </c>
       <c r="AG7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>65</v>
       </c>
       <c r="AH7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>640</v>
       </c>
       <c r="AI7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>381.5</v>
       </c>
       <c r="AJ7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>784</v>
       </c>
       <c r="AK7">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>483</v>
       </c>
       <c r="AL7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>108.5</v>
       </c>
       <c r="AM7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>255.5</v>
       </c>
       <c r="AN7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>227.5</v>
       </c>
       <c r="AO7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>2240</v>
       </c>
       <c r="AP7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AQ7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="AR7">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AS7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="AT7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AU7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="AV7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AW7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="AX7">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="AY7">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="AZ7">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="BA7">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="BB7">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="BC7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="BD7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>381.5</v>
       </c>
       <c r="BE7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>784</v>
       </c>
       <c r="BF7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>483</v>
       </c>
       <c r="BG7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>108.5</v>
       </c>
       <c r="BH7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>255.5</v>
       </c>
       <c r="BI7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>227.5</v>
       </c>
       <c r="BJ7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2240</v>
       </c>
     </row>
@@ -2422,220 +2478,220 @@
       <c r="H8" s="5">
         <v>242</v>
       </c>
-      <c r="I8" s="11">
-        <f t="shared" si="12"/>
+      <c r="I8">
+        <f t="shared" si="13"/>
         <v>730</v>
       </c>
-      <c r="J8" s="11">
-        <f t="shared" si="13"/>
+      <c r="J8">
+        <f t="shared" si="14"/>
         <v>3.5</v>
       </c>
       <c r="K8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="M8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="O8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q8">
-        <f>F8*$K8</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="R8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="S8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="T8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="U8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="V8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="W8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="X8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="Y8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AA8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AB8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>154</v>
       </c>
       <c r="AC8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>126</v>
       </c>
       <c r="AD8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>50</v>
       </c>
       <c r="AE8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>115</v>
       </c>
       <c r="AF8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>43</v>
       </c>
       <c r="AG8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>242</v>
       </c>
       <c r="AH8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>730</v>
       </c>
       <c r="AI8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>539</v>
       </c>
       <c r="AJ8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>441</v>
       </c>
       <c r="AK8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>175</v>
       </c>
       <c r="AL8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>402.5</v>
       </c>
       <c r="AM8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>150.5</v>
       </c>
       <c r="AN8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>847</v>
       </c>
       <c r="AO8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>2555</v>
       </c>
       <c r="AP8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="AQ8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="AR8">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AS8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="AT8">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AU8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="AV8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AW8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="AX8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="AY8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="AZ8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="BA8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="BB8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="BC8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="BD8">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>539</v>
       </c>
       <c r="BE8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>441</v>
       </c>
       <c r="BF8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>175</v>
       </c>
       <c r="BG8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>402.5</v>
       </c>
       <c r="BH8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>150.5</v>
       </c>
       <c r="BI8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>847</v>
       </c>
       <c r="BJ8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2555</v>
       </c>
     </row>
@@ -2664,220 +2720,220 @@
       <c r="H9" s="5">
         <v>32</v>
       </c>
-      <c r="I9" s="11">
-        <f t="shared" si="12"/>
+      <c r="I9">
+        <f t="shared" si="13"/>
         <v>796</v>
       </c>
-      <c r="J9" s="11">
-        <f t="shared" si="13"/>
+      <c r="J9">
+        <f t="shared" si="14"/>
         <v>3.5</v>
       </c>
       <c r="K9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="N9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="O9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q9">
-        <f>F9*$K9</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="R9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="S9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="T9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="U9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="V9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="W9">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="X9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="Y9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AA9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AB9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AC9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AD9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AF9">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AG9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AH9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AI9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AJ9">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AK9">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AL9">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AM9">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AN9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AO9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AP9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>190</v>
       </c>
       <c r="AQ9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>161</v>
       </c>
       <c r="AR9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>158</v>
       </c>
       <c r="AS9">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>172</v>
       </c>
       <c r="AT9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>83</v>
       </c>
       <c r="AU9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>32</v>
       </c>
       <c r="AV9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>796</v>
       </c>
       <c r="AW9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>665</v>
       </c>
       <c r="AX9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>563.5</v>
       </c>
       <c r="AY9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>553</v>
       </c>
       <c r="AZ9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>602</v>
       </c>
       <c r="BA9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>290.5</v>
       </c>
       <c r="BB9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>112</v>
       </c>
       <c r="BC9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>2786</v>
       </c>
       <c r="BD9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>665</v>
       </c>
       <c r="BE9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>563.5</v>
       </c>
       <c r="BF9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>553</v>
       </c>
       <c r="BG9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>602</v>
       </c>
       <c r="BH9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>290.5</v>
       </c>
       <c r="BI9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>112</v>
       </c>
       <c r="BJ9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2786</v>
       </c>
     </row>
@@ -2906,220 +2962,220 @@
       <c r="H10" s="5">
         <v>23</v>
       </c>
-      <c r="I10" s="11">
-        <f t="shared" si="12"/>
+      <c r="I10">
+        <f t="shared" si="13"/>
         <v>399</v>
       </c>
-      <c r="J10" s="11">
-        <f t="shared" si="13"/>
+      <c r="J10">
+        <f t="shared" si="14"/>
         <v>3.5</v>
       </c>
       <c r="K10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="N10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="O10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q10">
-        <f>F10*$K10</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="R10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="S10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="T10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="U10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="V10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="W10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="X10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="Y10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AA10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AB10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AC10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AD10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AF10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AG10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AH10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AI10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AJ10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AK10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AL10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AM10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AN10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AO10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AP10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>33</v>
       </c>
       <c r="AQ10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>4</v>
       </c>
       <c r="AR10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>10</v>
       </c>
       <c r="AS10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>232</v>
       </c>
       <c r="AT10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>97</v>
       </c>
       <c r="AU10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>23</v>
       </c>
       <c r="AV10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>399</v>
       </c>
       <c r="AW10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>115.5</v>
       </c>
       <c r="AX10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>14</v>
       </c>
       <c r="AY10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>35</v>
       </c>
       <c r="AZ10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>812</v>
       </c>
       <c r="BA10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>339.5</v>
       </c>
       <c r="BB10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>80.5</v>
       </c>
       <c r="BC10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>1396.5</v>
       </c>
       <c r="BD10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>115.5</v>
       </c>
       <c r="BE10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
       <c r="BF10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>35</v>
       </c>
       <c r="BG10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>812</v>
       </c>
       <c r="BH10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>339.5</v>
       </c>
       <c r="BI10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>80.5</v>
       </c>
       <c r="BJ10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1396.5</v>
       </c>
     </row>
@@ -3148,220 +3204,220 @@
       <c r="H11" s="8">
         <v>61</v>
       </c>
-      <c r="I11" s="11">
-        <f t="shared" si="12"/>
+      <c r="I11">
+        <f t="shared" si="13"/>
         <v>840</v>
       </c>
-      <c r="J11" s="11">
-        <f t="shared" si="13"/>
+      <c r="J11">
+        <f t="shared" si="14"/>
         <v>3.5</v>
       </c>
       <c r="K11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="N11">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="O11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q11">
-        <f>F11*$K11</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="R11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="S11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="T11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="U11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="V11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="W11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="X11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="Y11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AA11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AB11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AC11">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AD11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AF11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AG11">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AH11">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AI11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AJ11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AK11">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="AL11">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AM11">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AN11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AO11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AP11">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>244</v>
       </c>
       <c r="AQ11">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>81</v>
       </c>
       <c r="AR11">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>153</v>
       </c>
       <c r="AS11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>126</v>
       </c>
       <c r="AT11">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>175</v>
       </c>
       <c r="AU11">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>61</v>
       </c>
       <c r="AV11">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>840</v>
       </c>
       <c r="AW11">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>854</v>
       </c>
       <c r="AX11">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>283.5</v>
       </c>
       <c r="AY11">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>535.5</v>
       </c>
       <c r="AZ11">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>441</v>
       </c>
       <c r="BA11">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>612.5</v>
       </c>
       <c r="BB11">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>213.5</v>
       </c>
       <c r="BC11">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>2940</v>
       </c>
       <c r="BD11">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>854</v>
       </c>
       <c r="BE11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>283.5</v>
       </c>
       <c r="BF11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>535.5</v>
       </c>
       <c r="BG11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>441</v>
       </c>
       <c r="BH11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>612.5</v>
       </c>
       <c r="BI11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>213.5</v>
       </c>
       <c r="BJ11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2940</v>
       </c>
     </row>
@@ -3374,55 +3430,55 @@
         <v>973</v>
       </c>
       <c r="V12">
-        <f t="shared" ref="V12:AA12" si="56">SUM(V1:V11)</f>
+        <f t="shared" ref="V12:AA12" si="58">SUM(V1:V11)</f>
         <v>647.5</v>
       </c>
       <c r="W12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>1158.5</v>
       </c>
       <c r="X12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>507.5</v>
       </c>
       <c r="Y12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>787.5</v>
       </c>
       <c r="Z12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>854</v>
       </c>
-      <c r="AA12" s="16">
-        <f t="shared" si="56"/>
+      <c r="AA12" s="15">
+        <f t="shared" si="58"/>
         <v>4928</v>
       </c>
-      <c r="AI12" s="16">
+      <c r="AI12" s="15">
         <f>SUM(AI1:AI11)</f>
         <v>1704.5</v>
       </c>
       <c r="AJ12">
-        <f t="shared" ref="AJ12:AO12" si="57">SUM(AJ1:AJ11)</f>
+        <f t="shared" ref="AJ12:AO12" si="59">SUM(AJ1:AJ11)</f>
         <v>1463</v>
       </c>
       <c r="AK12">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>1312.5</v>
       </c>
       <c r="AL12">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>637</v>
       </c>
       <c r="AM12">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>630</v>
       </c>
       <c r="AN12">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>1200.5</v>
       </c>
-      <c r="AO12" s="16">
-        <f t="shared" si="57"/>
+      <c r="AO12" s="15">
+        <f t="shared" si="59"/>
         <v>6947.5</v>
       </c>
       <c r="AW12">
@@ -3430,91 +3486,91 @@
         <v>2898</v>
       </c>
       <c r="AX12">
-        <f t="shared" ref="AX12:BC12" si="58">SUM(AX1:AX11)</f>
+        <f t="shared" ref="AX12:BC12" si="60">SUM(AX1:AX11)</f>
         <v>1921.5</v>
       </c>
       <c r="AY12">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>1963.5</v>
       </c>
       <c r="AZ12">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>3206</v>
       </c>
       <c r="BA12">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>1988</v>
       </c>
       <c r="BB12">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>857.5</v>
       </c>
-      <c r="BC12" s="16">
-        <f t="shared" si="58"/>
+      <c r="BC12" s="15">
+        <f t="shared" si="60"/>
         <v>12834.5</v>
       </c>
-      <c r="BD12" s="19">
-        <f t="shared" ref="BD12" si="59">SUM(BD1:BD11)</f>
+      <c r="BD12">
+        <f t="shared" ref="BD12" si="61">SUM(BD1:BD11)</f>
         <v>5575.5</v>
       </c>
-      <c r="BE12" s="19">
-        <f t="shared" ref="BE12" si="60">SUM(BE1:BE11)</f>
+      <c r="BE12">
+        <f t="shared" ref="BE12" si="62">SUM(BE1:BE11)</f>
         <v>4032</v>
       </c>
-      <c r="BF12" s="19">
-        <f t="shared" ref="BF12" si="61">SUM(BF1:BF11)</f>
+      <c r="BF12">
+        <f t="shared" ref="BF12" si="63">SUM(BF1:BF11)</f>
         <v>4434.5</v>
       </c>
-      <c r="BG12" s="19">
-        <f t="shared" ref="BG12" si="62">SUM(BG1:BG11)</f>
+      <c r="BG12">
+        <f t="shared" ref="BG12" si="64">SUM(BG1:BG11)</f>
         <v>4350.5</v>
       </c>
-      <c r="BH12" s="19">
-        <f t="shared" ref="BH12" si="63">SUM(BH1:BH11)</f>
+      <c r="BH12">
+        <f t="shared" ref="BH12" si="65">SUM(BH1:BH11)</f>
         <v>3405.5</v>
       </c>
-      <c r="BI12" s="19">
-        <f t="shared" ref="BI12" si="64">SUM(BI1:BI11)</f>
+      <c r="BI12">
+        <f t="shared" ref="BI12" si="66">SUM(BI1:BI11)</f>
         <v>2912</v>
       </c>
-      <c r="BJ12" s="16">
-        <f t="shared" ref="BJ12" si="65">SUM(BJ1:BJ11)</f>
+      <c r="BJ12" s="15">
+        <f t="shared" ref="BJ12" si="67">SUM(BJ1:BJ11)</f>
         <v>24710</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="B13" t="s">
+      <c r="B13" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="18">
         <f>_xlfn.VAR.S(C2:C11)</f>
         <v>4257.5666666666675</v>
       </c>
-      <c r="D13" s="20">
-        <f t="shared" ref="D13:I13" si="66">_xlfn.VAR.S(D2:D11)</f>
+      <c r="D13" s="18">
+        <f t="shared" ref="D13:I13" si="68">_xlfn.VAR.S(D2:D11)</f>
         <v>4288.1777777777788</v>
       </c>
-      <c r="E13" s="20">
-        <f t="shared" si="66"/>
+      <c r="E13" s="18">
+        <f t="shared" si="68"/>
         <v>3854.0111111111119</v>
       </c>
-      <c r="F13" s="20">
-        <f t="shared" si="66"/>
+      <c r="F13" s="18">
+        <f t="shared" si="68"/>
         <v>5357.7888888888892</v>
       </c>
-      <c r="G13" s="20">
-        <f t="shared" si="66"/>
+      <c r="G13" s="18">
+        <f t="shared" si="68"/>
         <v>4132.6777777777788</v>
       </c>
-      <c r="H13" s="20">
-        <f t="shared" si="66"/>
+      <c r="H13" s="18">
+        <f t="shared" si="68"/>
         <v>5033.2888888888892</v>
       </c>
-      <c r="I13" s="20">
-        <f t="shared" si="66"/>
+      <c r="I13" s="18">
+        <f t="shared" si="68"/>
         <v>18936.666666666668</v>
       </c>
-      <c r="M13" t="s">
+      <c r="M13" s="19" t="s">
         <v>31</v>
       </c>
       <c r="N13">
@@ -3522,27 +3578,27 @@
         <v>3596.8444444444444</v>
       </c>
       <c r="O13">
-        <f t="shared" ref="O13:T13" si="67">_xlfn.VAR.S(O2:O11)</f>
+        <f t="shared" ref="O13:T13" si="69">_xlfn.VAR.S(O2:O11)</f>
         <v>2087.8333333333335</v>
       </c>
       <c r="P13">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>5216.1000000000004</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>941.16666666666663</v>
       </c>
       <c r="R13">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>4234.5</v>
       </c>
       <c r="S13">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>3419.6000000000004</v>
       </c>
       <c r="T13">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>89393.066666666666</v>
       </c>
       <c r="AB13">
@@ -3550,27 +3606,27 @@
         <v>6895.1222222222223</v>
       </c>
       <c r="AC13">
-        <f t="shared" ref="AC13:AH13" si="68">_xlfn.VAR.S(AC2:AC11)</f>
+        <f t="shared" ref="AC13:AH13" si="70">_xlfn.VAR.S(AC2:AC11)</f>
         <v>5911.5111111111109</v>
       </c>
       <c r="AD13">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>4716.7222222222226</v>
       </c>
       <c r="AE13">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>1352.1777777777779</v>
       </c>
       <c r="AF13">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>892.66666666666663</v>
       </c>
       <c r="AG13">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>5813.344444444444</v>
       </c>
       <c r="AH13">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>102966.94444444444</v>
       </c>
       <c r="AP13">
@@ -3578,11 +3634,11 @@
         <v>10850.177777777779</v>
       </c>
       <c r="AQ13">
-        <f t="shared" ref="AQ13:AV13" si="69">_xlfn.VAR.S(AQ2:AQ11)</f>
+        <f t="shared" ref="AQ13:AV13" si="71">_xlfn.VAR.S(AQ2:AQ11)</f>
         <v>5363.8777777777777</v>
       </c>
       <c r="AR13">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>5480.9888888888891</v>
       </c>
       <c r="AS13">
@@ -3590,51 +3646,51 @@
         <v>10307.155555555555</v>
       </c>
       <c r="AT13">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>5017.5111111111109</v>
       </c>
       <c r="AU13">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>856.05555555555554</v>
       </c>
       <c r="AV13">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>165176.90000000002</v>
       </c>
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="B14" t="s">
+      <c r="B14" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="18">
         <f>$M$15*C13</f>
         <v>372537.08333333343</v>
       </c>
-      <c r="D14" s="20">
-        <f t="shared" ref="D14" si="70">$M$15*D13</f>
+      <c r="D14" s="18">
+        <f t="shared" ref="D14" si="72">$M$15*D13</f>
         <v>375215.55555555562</v>
       </c>
-      <c r="E14" s="20">
-        <f t="shared" ref="E14" si="71">$M$15*E13</f>
+      <c r="E14" s="18">
+        <f t="shared" ref="E14" si="73">$M$15*E13</f>
         <v>337225.97222222231</v>
       </c>
-      <c r="F14" s="20">
-        <f t="shared" ref="F14" si="72">$M$15*F13</f>
+      <c r="F14" s="18">
+        <f t="shared" ref="F14" si="74">$M$15*F13</f>
         <v>468806.52777777781</v>
       </c>
-      <c r="G14" s="20">
-        <f t="shared" ref="G14" si="73">$M$15*G13</f>
+      <c r="G14" s="18">
+        <f t="shared" ref="G14" si="75">$M$15*G13</f>
         <v>361609.30555555562</v>
       </c>
-      <c r="H14" s="20">
-        <f t="shared" ref="H14" si="74">$M$15*H13</f>
+      <c r="H14" s="18">
+        <f t="shared" ref="H14" si="76">$M$15*H13</f>
         <v>440412.77777777781</v>
       </c>
-      <c r="I14" s="20">
-        <f t="shared" ref="I14" si="75">$M$15*I13</f>
+      <c r="I14" s="18">
+        <f t="shared" ref="I14" si="77">$M$15*I13</f>
         <v>1656958.3333333335</v>
       </c>
-      <c r="M14" t="s">
+      <c r="M14" s="19" t="s">
         <v>33</v>
       </c>
       <c r="N14">
@@ -3642,27 +3698,27 @@
         <v>314723.88888888888</v>
       </c>
       <c r="O14">
-        <f t="shared" ref="O14:T14" si="76">$M$15*O13</f>
+        <f t="shared" ref="O14:T14" si="78">$M$15*O13</f>
         <v>182685.41666666669</v>
       </c>
       <c r="P14">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>456408.75000000006</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>82352.083333333328</v>
       </c>
       <c r="R14">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>370518.75</v>
       </c>
       <c r="S14">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>299215.00000000006</v>
       </c>
       <c r="T14">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>7821893.333333333</v>
       </c>
       <c r="AB14">
@@ -3670,27 +3726,27 @@
         <v>603323.1944444445</v>
       </c>
       <c r="AC14">
-        <f t="shared" ref="AC14" si="77">$M$15*AC13</f>
+        <f t="shared" ref="AC14" si="79">$M$15*AC13</f>
         <v>517257.22222222219</v>
       </c>
       <c r="AD14">
-        <f t="shared" ref="AD14" si="78">$M$15*AD13</f>
+        <f t="shared" ref="AD14" si="80">$M$15*AD13</f>
         <v>412713.1944444445</v>
       </c>
       <c r="AE14">
-        <f t="shared" ref="AE14" si="79">$M$15*AE13</f>
+        <f t="shared" ref="AE14" si="81">$M$15*AE13</f>
         <v>118315.55555555556</v>
       </c>
       <c r="AF14">
-        <f t="shared" ref="AF14" si="80">$M$15*AF13</f>
+        <f t="shared" ref="AF14" si="82">$M$15*AF13</f>
         <v>78108.333333333328</v>
       </c>
       <c r="AG14">
-        <f t="shared" ref="AG14" si="81">$M$15*AG13</f>
+        <f t="shared" ref="AG14" si="83">$M$15*AG13</f>
         <v>508667.63888888888</v>
       </c>
       <c r="AH14">
-        <f t="shared" ref="AH14" si="82">$M$15*AH13</f>
+        <f t="shared" ref="AH14" si="84">$M$15*AH13</f>
         <v>9009607.6388888881</v>
       </c>
       <c r="AP14">
@@ -3698,157 +3754,164 @@
         <v>949390.55555555562</v>
       </c>
       <c r="AQ14">
-        <f t="shared" ref="AQ14" si="83">$M$15*AQ13</f>
+        <f t="shared" ref="AQ14" si="85">$M$15*AQ13</f>
         <v>469339.30555555556</v>
       </c>
       <c r="AR14">
-        <f t="shared" ref="AR14" si="84">$M$15*AR13</f>
+        <f t="shared" ref="AR14" si="86">$M$15*AR13</f>
         <v>479586.52777777781</v>
       </c>
       <c r="AS14">
-        <f t="shared" ref="AS14" si="85">$M$15*AS13</f>
+        <f t="shared" ref="AS14" si="87">$M$15*AS13</f>
         <v>901876.11111111112</v>
       </c>
       <c r="AT14">
-        <f t="shared" ref="AT14" si="86">$M$15*AT13</f>
+        <f t="shared" ref="AT14" si="88">$M$15*AT13</f>
         <v>439032.22222222219</v>
       </c>
       <c r="AU14">
-        <f t="shared" ref="AU14" si="87">$M$15*AU13</f>
+        <f t="shared" ref="AU14" si="89">$M$15*AU13</f>
         <v>74904.861111111109</v>
       </c>
       <c r="AV14">
-        <f t="shared" ref="AV14" si="88">$M$15*AV13</f>
+        <f t="shared" ref="AV14" si="90">$M$15*AV13</f>
         <v>14452978.750000002</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="L15" t="s">
+      <c r="B15" s="19"/>
+      <c r="L15" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="M15" s="16">
+      <c r="M15" s="15">
         <f>(35^2)/10*(1-(10/35))</f>
         <v>87.5</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="B16" t="s">
+      <c r="B16" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="16">
         <f>SQRT(C14)/BD12</f>
         <v>0.10947146621487054</v>
       </c>
-      <c r="D16" s="17">
-        <f t="shared" ref="D16:I16" si="89">SQRT(D14)/BE12</f>
+      <c r="D16" s="16">
+        <f t="shared" ref="D16:I16" si="91">SQRT(D14)/BE12</f>
         <v>0.15192172886539346</v>
       </c>
-      <c r="E16" s="17">
-        <f t="shared" si="89"/>
+      <c r="E16" s="16">
+        <f t="shared" si="91"/>
         <v>0.13095311951267588</v>
       </c>
-      <c r="F16" s="17">
-        <f t="shared" si="89"/>
+      <c r="F16" s="16">
+        <f t="shared" si="91"/>
         <v>0.15738293936075731</v>
       </c>
-      <c r="G16" s="17">
-        <f t="shared" si="89"/>
+      <c r="G16" s="16">
+        <f t="shared" si="91"/>
         <v>0.17657894363220863</v>
       </c>
-      <c r="H16" s="17">
-        <f t="shared" si="89"/>
+      <c r="H16" s="16">
+        <f t="shared" si="91"/>
         <v>0.22789698766793456</v>
       </c>
-      <c r="I16" s="17">
-        <f t="shared" si="89"/>
+      <c r="I16" s="16">
+        <f t="shared" si="91"/>
         <v>5.2093441354391638E-2</v>
       </c>
-      <c r="M16" t="s">
+      <c r="M16" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="N16" s="17">
+      <c r="N16" s="16">
         <f>SQRT(N14)/U12</f>
         <v>0.57656996378352732</v>
       </c>
-      <c r="O16" s="17">
-        <f t="shared" ref="O16:T16" si="90">SQRT(O14)/V12</f>
+      <c r="O16" s="16">
+        <f t="shared" ref="O16:T16" si="92">SQRT(O14)/V12</f>
         <v>0.66010370033529941</v>
       </c>
-      <c r="P16" s="17">
-        <f t="shared" si="90"/>
+      <c r="P16" s="16">
+        <f t="shared" si="92"/>
         <v>0.58315089003649156</v>
       </c>
-      <c r="Q16" s="17">
-        <f t="shared" si="90"/>
+      <c r="Q16" s="16">
+        <f t="shared" si="92"/>
         <v>0.56545916638805438</v>
       </c>
-      <c r="R16" s="17">
-        <f t="shared" si="90"/>
+      <c r="R16" s="16">
+        <f t="shared" si="92"/>
         <v>0.77295557275972693</v>
       </c>
-      <c r="S16" s="17">
-        <f t="shared" si="90"/>
+      <c r="S16" s="16">
+        <f t="shared" si="92"/>
         <v>0.6405216445353632</v>
       </c>
-      <c r="T16" s="17">
-        <f t="shared" si="90"/>
+      <c r="T16" s="16">
+        <f t="shared" si="92"/>
         <v>0.56752532419697355</v>
       </c>
-      <c r="AB16" s="17">
+      <c r="AB16" s="16">
         <f>SQRT(AB14)/AI12</f>
         <v>0.45569892635228015</v>
       </c>
-      <c r="AC16" s="17">
-        <f t="shared" ref="AC16" si="91">SQRT(AC14)/AJ12</f>
+      <c r="AC16" s="16">
+        <f t="shared" ref="AC16" si="93">SQRT(AC14)/AJ12</f>
         <v>0.49159669615942952</v>
       </c>
-      <c r="AD16" s="17">
-        <f t="shared" ref="AD16" si="92">SQRT(AD14)/AK12</f>
+      <c r="AD16" s="16">
+        <f t="shared" ref="AD16" si="94">SQRT(AD14)/AK12</f>
         <v>0.48946863172853905</v>
       </c>
-      <c r="AE16" s="17">
-        <f t="shared" ref="AE16" si="93">SQRT(AE14)/AL12</f>
+      <c r="AE16" s="16">
+        <f t="shared" ref="AE16" si="95">SQRT(AE14)/AL12</f>
         <v>0.53998474561090493</v>
       </c>
-      <c r="AF16" s="17">
-        <f t="shared" ref="AF16" si="94">SQRT(AF14)/AM12</f>
+      <c r="AF16" s="16">
+        <f t="shared" ref="AF16" si="96">SQRT(AF14)/AM12</f>
         <v>0.44361695453573219</v>
       </c>
-      <c r="AG16" s="17">
-        <f t="shared" ref="AG16" si="95">SQRT(AG14)/AN12</f>
+      <c r="AG16" s="16">
+        <f t="shared" ref="AG16" si="97">SQRT(AG14)/AN12</f>
         <v>0.59409362218949024</v>
       </c>
-      <c r="AH16" s="17">
-        <f t="shared" ref="AH16" si="96">SQRT(AH14)/AO12</f>
+      <c r="AH16" s="16">
+        <f t="shared" ref="AH16" si="98">SQRT(AH14)/AO12</f>
         <v>0.43204042404176263</v>
       </c>
-      <c r="AP16" s="17">
+      <c r="AP16" s="16">
         <f>SQRT(AP14)/AW12</f>
         <v>0.33622040922029806</v>
       </c>
-      <c r="AQ16" s="17">
-        <f t="shared" ref="AQ16" si="97">SQRT(AQ14)/AX12</f>
+      <c r="AQ16" s="16">
+        <f t="shared" ref="AQ16" si="99">SQRT(AQ14)/AX12</f>
         <v>0.35653574271736921</v>
       </c>
-      <c r="AR16" s="17">
-        <f t="shared" ref="AR16" si="98">SQRT(AR14)/AY12</f>
+      <c r="AR16" s="16">
+        <f t="shared" ref="AR16" si="100">SQRT(AR14)/AY12</f>
         <v>0.35269766277888442</v>
       </c>
-      <c r="AS16" s="17">
-        <f t="shared" ref="AS16" si="99">SQRT(AS14)/AZ12</f>
+      <c r="AS16" s="16">
+        <f t="shared" ref="AS16" si="101">SQRT(AS14)/AZ12</f>
         <v>0.29621696215186122</v>
       </c>
-      <c r="AT16" s="17">
-        <f t="shared" ref="AT16" si="100">SQRT(AT14)/BA12</f>
+      <c r="AT16" s="16">
+        <f t="shared" ref="AT16" si="102">SQRT(AT14)/BA12</f>
         <v>0.33329731718027883</v>
       </c>
-      <c r="AU16" s="17">
-        <f t="shared" ref="AU16" si="101">SQRT(AU14)/BB12</f>
+      <c r="AU16" s="16">
+        <f t="shared" ref="AU16" si="103">SQRT(AU14)/BB12</f>
         <v>0.31916912487545152</v>
       </c>
-      <c r="AV16" s="17">
+      <c r="AV16" s="16">
         <f>SQRT(AV14)/BC12</f>
         <v>0.29621000792443913</v>
+      </c>
+    </row>
+    <row r="17" spans="14:14" x14ac:dyDescent="0.35">
+      <c r="N17">
+        <f>SUMSQ(N1:N11)</f>
+        <v>40100</v>
       </c>
     </row>
   </sheetData>
@@ -3857,6 +3920,3490 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BA35F26-9DCE-42B2-9A0A-CB6EA4720C8F}">
+  <dimension ref="A1:BJ16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="4.7265625" customWidth="1"/>
+    <col min="3" max="8" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.7265625" customWidth="1"/>
+    <col min="11" max="11" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.36328125" customWidth="1"/>
+    <col min="13" max="13" width="6.26953125" customWidth="1"/>
+    <col min="14" max="14" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1" s="12" t="str">
+        <f t="shared" ref="N1:S1" si="0">C1&amp;"*D1"</f>
+        <v>P2*D1</v>
+      </c>
+      <c r="O1" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>P3*D1</v>
+      </c>
+      <c r="P1" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>P4*D1</v>
+      </c>
+      <c r="Q1" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>P5*D1</v>
+      </c>
+      <c r="R1" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>P6*D1</v>
+      </c>
+      <c r="S1" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>P7*D1</v>
+      </c>
+      <c r="T1" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="U1" s="11" t="str">
+        <f>N1&amp;"*Fex"</f>
+        <v>P2*D1*Fex</v>
+      </c>
+      <c r="V1" s="11" t="str">
+        <f t="shared" ref="V1:AA1" si="1">O1&amp;"*Fex"</f>
+        <v>P3*D1*Fex</v>
+      </c>
+      <c r="W1" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>P4*D1*Fex</v>
+      </c>
+      <c r="X1" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>P5*D1*Fex</v>
+      </c>
+      <c r="Y1" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>P6*D1*Fex</v>
+      </c>
+      <c r="Z1" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>P7*D1*Fex</v>
+      </c>
+      <c r="AA1" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>Total*D1*Fex</v>
+      </c>
+      <c r="AB1" s="12" t="str">
+        <f>C1&amp;"*D2"</f>
+        <v>P2*D2</v>
+      </c>
+      <c r="AC1" s="12" t="str">
+        <f t="shared" ref="AC1:AH1" si="2">D1&amp;"*D2"</f>
+        <v>P3*D2</v>
+      </c>
+      <c r="AD1" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v>P4*D2</v>
+      </c>
+      <c r="AE1" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v>P5*D2</v>
+      </c>
+      <c r="AF1" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v>P6*D2</v>
+      </c>
+      <c r="AG1" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v>P7*D2</v>
+      </c>
+      <c r="AH1" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v>Total*D2</v>
+      </c>
+      <c r="AI1" s="13" t="str">
+        <f>AB1&amp;"*Fex"</f>
+        <v>P2*D2*Fex</v>
+      </c>
+      <c r="AJ1" s="13" t="str">
+        <f t="shared" ref="AJ1:AO1" si="3">AC1&amp;"*Fex"</f>
+        <v>P3*D2*Fex</v>
+      </c>
+      <c r="AK1" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>P4*D2*Fex</v>
+      </c>
+      <c r="AL1" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>P5*D2*Fex</v>
+      </c>
+      <c r="AM1" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>P6*D2*Fex</v>
+      </c>
+      <c r="AN1" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>P7*D2*Fex</v>
+      </c>
+      <c r="AO1" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>Total*D2*Fex</v>
+      </c>
+      <c r="AP1" s="14" t="str">
+        <f>C1&amp;"*D3"</f>
+        <v>P2*D3</v>
+      </c>
+      <c r="AQ1" s="14" t="str">
+        <f t="shared" ref="AQ1:AU1" si="4">D1&amp;"*D3"</f>
+        <v>P3*D3</v>
+      </c>
+      <c r="AR1" s="14" t="str">
+        <f t="shared" si="4"/>
+        <v>P4*D3</v>
+      </c>
+      <c r="AS1" s="14" t="str">
+        <f t="shared" si="4"/>
+        <v>P5*D3</v>
+      </c>
+      <c r="AT1" s="14" t="str">
+        <f t="shared" si="4"/>
+        <v>P6*D3</v>
+      </c>
+      <c r="AU1" s="14" t="str">
+        <f t="shared" si="4"/>
+        <v>P7*D3</v>
+      </c>
+      <c r="AV1" s="14" t="str">
+        <f>I1&amp;"*D3"</f>
+        <v>Total*D3</v>
+      </c>
+      <c r="AW1" s="13" t="str">
+        <f>AP1&amp;"*Fex"</f>
+        <v>P2*D3*Fex</v>
+      </c>
+      <c r="AX1" s="13" t="str">
+        <f t="shared" ref="AX1:BC1" si="5">AQ1&amp;"*Fex"</f>
+        <v>P3*D3*Fex</v>
+      </c>
+      <c r="AY1" s="13" t="str">
+        <f t="shared" si="5"/>
+        <v>P4*D3*Fex</v>
+      </c>
+      <c r="AZ1" s="13" t="str">
+        <f t="shared" si="5"/>
+        <v>P5*D3*Fex</v>
+      </c>
+      <c r="BA1" s="13" t="str">
+        <f t="shared" si="5"/>
+        <v>P6*D3*Fex</v>
+      </c>
+      <c r="BB1" s="13" t="str">
+        <f t="shared" si="5"/>
+        <v>P7*D3*Fex</v>
+      </c>
+      <c r="BC1" s="13" t="str">
+        <f t="shared" si="5"/>
+        <v>Total*D3*Fex</v>
+      </c>
+      <c r="BD1" s="17" t="str">
+        <f>C1&amp;"*Fex"</f>
+        <v>P2*Fex</v>
+      </c>
+      <c r="BE1" s="17" t="str">
+        <f t="shared" ref="BE1:BJ1" si="6">D1&amp;"*Fex"</f>
+        <v>P3*Fex</v>
+      </c>
+      <c r="BF1" s="17" t="str">
+        <f t="shared" si="6"/>
+        <v>P4*Fex</v>
+      </c>
+      <c r="BG1" s="17" t="str">
+        <f t="shared" si="6"/>
+        <v>P5*Fex</v>
+      </c>
+      <c r="BH1" s="17" t="str">
+        <f t="shared" si="6"/>
+        <v>P6*Fex</v>
+      </c>
+      <c r="BI1" s="17" t="str">
+        <f t="shared" si="6"/>
+        <v>P7*Fex</v>
+      </c>
+      <c r="BJ1" s="17" t="str">
+        <f t="shared" si="6"/>
+        <v>Total*Fex</v>
+      </c>
+    </row>
+    <row r="2" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>224</v>
+      </c>
+      <c r="D2">
+        <v>68</v>
+      </c>
+      <c r="E2">
+        <v>187</v>
+      </c>
+      <c r="F2">
+        <v>36</v>
+      </c>
+      <c r="G2">
+        <v>64</v>
+      </c>
+      <c r="H2" s="5">
+        <v>36</v>
+      </c>
+      <c r="I2">
+        <f>SUM(C2:H2)</f>
+        <v>615</v>
+      </c>
+      <c r="J2">
+        <f>1/(1/3)</f>
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <f>IF($B2=1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <f>IF($B2=2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <f>IF($B2=3,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <f>C2*$K2</f>
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <f>D2*$K2</f>
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <f>E2*$K2</f>
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <f>F2*$K2</f>
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <f>G2*$K2</f>
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <f>I2*$K2</f>
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <f>I2*$K2</f>
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <f>N2*$J2</f>
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <f t="shared" ref="V2:AA11" si="7">O2*$J2</f>
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <f>C2*$L2</f>
+        <v>224</v>
+      </c>
+      <c r="AC2">
+        <f t="shared" ref="AC2:AH11" si="8">D2*$L2</f>
+        <v>68</v>
+      </c>
+      <c r="AD2">
+        <f t="shared" si="8"/>
+        <v>187</v>
+      </c>
+      <c r="AE2">
+        <f t="shared" si="8"/>
+        <v>36</v>
+      </c>
+      <c r="AF2">
+        <f t="shared" si="8"/>
+        <v>64</v>
+      </c>
+      <c r="AG2">
+        <f t="shared" si="8"/>
+        <v>36</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" si="8"/>
+        <v>615</v>
+      </c>
+      <c r="AI2">
+        <f>AB2*$J2</f>
+        <v>672</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" ref="AJ2:AO11" si="9">AC2*$J2</f>
+        <v>204</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="9"/>
+        <v>561</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="9"/>
+        <v>108</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="9"/>
+        <v>192</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="9"/>
+        <v>108</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="9"/>
+        <v>1845</v>
+      </c>
+      <c r="AP2">
+        <f>C2*$M2</f>
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" ref="AQ2:AV11" si="10">D2*$M2</f>
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <f>AP2*$J2</f>
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" ref="AX2:BC11" si="11">AQ2*$J2</f>
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BA2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BB2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BC2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BD2">
+        <f>C2*$J2</f>
+        <v>672</v>
+      </c>
+      <c r="BE2">
+        <f t="shared" ref="BE2:BJ11" si="12">D2*$J2</f>
+        <v>204</v>
+      </c>
+      <c r="BF2">
+        <f t="shared" si="12"/>
+        <v>561</v>
+      </c>
+      <c r="BG2">
+        <f t="shared" si="12"/>
+        <v>108</v>
+      </c>
+      <c r="BH2">
+        <f t="shared" si="12"/>
+        <v>192</v>
+      </c>
+      <c r="BI2">
+        <f t="shared" si="12"/>
+        <v>108</v>
+      </c>
+      <c r="BJ2">
+        <f t="shared" si="12"/>
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="3" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>112</v>
+      </c>
+      <c r="D3">
+        <v>42</v>
+      </c>
+      <c r="E3">
+        <v>126</v>
+      </c>
+      <c r="F3">
+        <v>78</v>
+      </c>
+      <c r="G3">
+        <v>207</v>
+      </c>
+      <c r="H3" s="5">
+        <v>63</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I11" si="13">SUM(C3:H3)</f>
+        <v>628</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J11" si="14">1/(1/3)</f>
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K11" si="15">IF($B3=1,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <f t="shared" ref="L3:L11" si="16">IF($B3=2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <f t="shared" ref="M3:M11" si="17">IF($B3=3,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <f t="shared" ref="N3:T11" si="18">C3*$K3</f>
+        <v>112</v>
+      </c>
+      <c r="O3">
+        <f t="shared" si="18"/>
+        <v>42</v>
+      </c>
+      <c r="P3">
+        <f t="shared" si="18"/>
+        <v>126</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" si="18"/>
+        <v>78</v>
+      </c>
+      <c r="R3">
+        <f t="shared" si="18"/>
+        <v>207</v>
+      </c>
+      <c r="S3">
+        <f t="shared" si="18"/>
+        <v>63</v>
+      </c>
+      <c r="T3">
+        <f t="shared" si="18"/>
+        <v>628</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="19">N3*$J3</f>
+        <v>336</v>
+      </c>
+      <c r="V3">
+        <f t="shared" si="7"/>
+        <v>126</v>
+      </c>
+      <c r="W3">
+        <f t="shared" si="7"/>
+        <v>378</v>
+      </c>
+      <c r="X3">
+        <f t="shared" si="7"/>
+        <v>234</v>
+      </c>
+      <c r="Y3">
+        <f t="shared" si="7"/>
+        <v>621</v>
+      </c>
+      <c r="Z3">
+        <f t="shared" si="7"/>
+        <v>189</v>
+      </c>
+      <c r="AA3">
+        <f t="shared" si="7"/>
+        <v>1884</v>
+      </c>
+      <c r="AB3">
+        <f t="shared" ref="AB3:AB11" si="20">C3*$L3</f>
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" ref="AI3:AI11" si="21">AB3*$J3</f>
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" ref="AP3:AP11" si="22">C3*$M3</f>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" ref="AW3:AW11" si="23">AP3*$J3</f>
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <f t="shared" ref="BD3:BD11" si="24">C3*$J3</f>
+        <v>336</v>
+      </c>
+      <c r="BE3">
+        <f t="shared" si="12"/>
+        <v>126</v>
+      </c>
+      <c r="BF3">
+        <f t="shared" si="12"/>
+        <v>378</v>
+      </c>
+      <c r="BG3">
+        <f t="shared" si="12"/>
+        <v>234</v>
+      </c>
+      <c r="BH3">
+        <f t="shared" si="12"/>
+        <v>621</v>
+      </c>
+      <c r="BI3">
+        <f t="shared" si="12"/>
+        <v>189</v>
+      </c>
+      <c r="BJ3">
+        <f t="shared" si="12"/>
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="4" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>227</v>
+      </c>
+      <c r="D4">
+        <v>154</v>
+      </c>
+      <c r="E4">
+        <v>78</v>
+      </c>
+      <c r="F4">
+        <v>155</v>
+      </c>
+      <c r="G4">
+        <v>169</v>
+      </c>
+      <c r="H4" s="5">
+        <v>57</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="13"/>
+        <v>840</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="14"/>
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="22"/>
+        <v>227</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="10"/>
+        <v>154</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="10"/>
+        <v>78</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="10"/>
+        <v>155</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="10"/>
+        <v>169</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="10"/>
+        <v>57</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="10"/>
+        <v>840</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="23"/>
+        <v>681</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="11"/>
+        <v>462</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="11"/>
+        <v>234</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="11"/>
+        <v>465</v>
+      </c>
+      <c r="BA4">
+        <f t="shared" si="11"/>
+        <v>507</v>
+      </c>
+      <c r="BB4">
+        <f t="shared" si="11"/>
+        <v>171</v>
+      </c>
+      <c r="BC4">
+        <f t="shared" si="11"/>
+        <v>2520</v>
+      </c>
+      <c r="BD4">
+        <f t="shared" si="24"/>
+        <v>681</v>
+      </c>
+      <c r="BE4">
+        <f t="shared" si="12"/>
+        <v>462</v>
+      </c>
+      <c r="BF4">
+        <f t="shared" si="12"/>
+        <v>234</v>
+      </c>
+      <c r="BG4">
+        <f t="shared" si="12"/>
+        <v>465</v>
+      </c>
+      <c r="BH4">
+        <f t="shared" si="12"/>
+        <v>507</v>
+      </c>
+      <c r="BI4">
+        <f t="shared" si="12"/>
+        <v>171</v>
+      </c>
+      <c r="BJ4">
+        <f t="shared" si="12"/>
+        <v>2520</v>
+      </c>
+    </row>
+    <row r="5" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>166</v>
+      </c>
+      <c r="D5">
+        <v>143</v>
+      </c>
+      <c r="E5">
+        <v>205</v>
+      </c>
+      <c r="F5">
+        <v>67</v>
+      </c>
+      <c r="G5">
+        <v>18</v>
+      </c>
+      <c r="H5" s="5">
+        <v>181</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="13"/>
+        <v>780</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="14"/>
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="18"/>
+        <v>166</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="18"/>
+        <v>143</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="18"/>
+        <v>205</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="18"/>
+        <v>67</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="18"/>
+        <v>18</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="18"/>
+        <v>181</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="18"/>
+        <v>780</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="19"/>
+        <v>498</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="7"/>
+        <v>429</v>
+      </c>
+      <c r="W5">
+        <f t="shared" si="7"/>
+        <v>615</v>
+      </c>
+      <c r="X5">
+        <f t="shared" si="7"/>
+        <v>201</v>
+      </c>
+      <c r="Y5">
+        <f t="shared" si="7"/>
+        <v>54</v>
+      </c>
+      <c r="Z5">
+        <f t="shared" si="7"/>
+        <v>543</v>
+      </c>
+      <c r="AA5">
+        <f t="shared" si="7"/>
+        <v>2340</v>
+      </c>
+      <c r="AB5">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <f t="shared" si="24"/>
+        <v>498</v>
+      </c>
+      <c r="BE5">
+        <f t="shared" si="12"/>
+        <v>429</v>
+      </c>
+      <c r="BF5">
+        <f t="shared" si="12"/>
+        <v>615</v>
+      </c>
+      <c r="BG5">
+        <f t="shared" si="12"/>
+        <v>201</v>
+      </c>
+      <c r="BH5">
+        <f t="shared" si="12"/>
+        <v>54</v>
+      </c>
+      <c r="BI5">
+        <f t="shared" si="12"/>
+        <v>543</v>
+      </c>
+      <c r="BJ5">
+        <f t="shared" si="12"/>
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="6" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>134</v>
+      </c>
+      <c r="D6">
+        <v>149</v>
+      </c>
+      <c r="E6">
+        <v>162</v>
+      </c>
+      <c r="F6">
+        <v>231</v>
+      </c>
+      <c r="G6">
+        <v>44</v>
+      </c>
+      <c r="H6" s="5">
+        <v>72</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="13"/>
+        <v>792</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="14"/>
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="22"/>
+        <v>134</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="10"/>
+        <v>149</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="10"/>
+        <v>162</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="10"/>
+        <v>231</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="10"/>
+        <v>44</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="10"/>
+        <v>72</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="10"/>
+        <v>792</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="23"/>
+        <v>402</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="11"/>
+        <v>447</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="11"/>
+        <v>486</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="11"/>
+        <v>693</v>
+      </c>
+      <c r="BA6">
+        <f t="shared" si="11"/>
+        <v>132</v>
+      </c>
+      <c r="BB6">
+        <f t="shared" si="11"/>
+        <v>216</v>
+      </c>
+      <c r="BC6">
+        <f t="shared" si="11"/>
+        <v>2376</v>
+      </c>
+      <c r="BD6">
+        <f t="shared" si="24"/>
+        <v>402</v>
+      </c>
+      <c r="BE6">
+        <f t="shared" si="12"/>
+        <v>447</v>
+      </c>
+      <c r="BF6">
+        <f t="shared" si="12"/>
+        <v>486</v>
+      </c>
+      <c r="BG6">
+        <f t="shared" si="12"/>
+        <v>693</v>
+      </c>
+      <c r="BH6">
+        <f t="shared" si="12"/>
+        <v>132</v>
+      </c>
+      <c r="BI6">
+        <f t="shared" si="12"/>
+        <v>216</v>
+      </c>
+      <c r="BJ6">
+        <f t="shared" si="12"/>
+        <v>2376</v>
+      </c>
+    </row>
+    <row r="7" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>109</v>
+      </c>
+      <c r="D7">
+        <v>224</v>
+      </c>
+      <c r="E7">
+        <v>138</v>
+      </c>
+      <c r="F7">
+        <v>31</v>
+      </c>
+      <c r="G7">
+        <v>73</v>
+      </c>
+      <c r="H7" s="5">
+        <v>65</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="13"/>
+        <v>640</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="14"/>
+        <v>3</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <f t="shared" si="20"/>
+        <v>109</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="8"/>
+        <v>224</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="8"/>
+        <v>138</v>
+      </c>
+      <c r="AE7">
+        <f t="shared" si="8"/>
+        <v>31</v>
+      </c>
+      <c r="AF7">
+        <f t="shared" si="8"/>
+        <v>73</v>
+      </c>
+      <c r="AG7">
+        <f t="shared" si="8"/>
+        <v>65</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="8"/>
+        <v>640</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="21"/>
+        <v>327</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="9"/>
+        <v>672</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="9"/>
+        <v>414</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="9"/>
+        <v>93</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="9"/>
+        <v>219</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="9"/>
+        <v>195</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="9"/>
+        <v>1920</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <f t="shared" si="24"/>
+        <v>327</v>
+      </c>
+      <c r="BE7">
+        <f t="shared" si="12"/>
+        <v>672</v>
+      </c>
+      <c r="BF7">
+        <f t="shared" si="12"/>
+        <v>414</v>
+      </c>
+      <c r="BG7">
+        <f t="shared" si="12"/>
+        <v>93</v>
+      </c>
+      <c r="BH7">
+        <f t="shared" si="12"/>
+        <v>219</v>
+      </c>
+      <c r="BI7">
+        <f t="shared" si="12"/>
+        <v>195</v>
+      </c>
+      <c r="BJ7">
+        <f t="shared" si="12"/>
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="8" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>154</v>
+      </c>
+      <c r="D8">
+        <v>126</v>
+      </c>
+      <c r="E8">
+        <v>50</v>
+      </c>
+      <c r="F8">
+        <v>115</v>
+      </c>
+      <c r="G8">
+        <v>43</v>
+      </c>
+      <c r="H8" s="5">
+        <v>242</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="13"/>
+        <v>730</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="14"/>
+        <v>3</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <f t="shared" si="20"/>
+        <v>154</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="8"/>
+        <v>126</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="8"/>
+        <v>50</v>
+      </c>
+      <c r="AE8">
+        <f t="shared" si="8"/>
+        <v>115</v>
+      </c>
+      <c r="AF8">
+        <f t="shared" si="8"/>
+        <v>43</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="8"/>
+        <v>242</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="8"/>
+        <v>730</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="21"/>
+        <v>462</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="9"/>
+        <v>378</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="9"/>
+        <v>150</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="9"/>
+        <v>345</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="9"/>
+        <v>129</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="9"/>
+        <v>726</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="9"/>
+        <v>2190</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <f t="shared" si="24"/>
+        <v>462</v>
+      </c>
+      <c r="BE8">
+        <f t="shared" si="12"/>
+        <v>378</v>
+      </c>
+      <c r="BF8">
+        <f t="shared" si="12"/>
+        <v>150</v>
+      </c>
+      <c r="BG8">
+        <f t="shared" si="12"/>
+        <v>345</v>
+      </c>
+      <c r="BH8">
+        <f t="shared" si="12"/>
+        <v>129</v>
+      </c>
+      <c r="BI8">
+        <f t="shared" si="12"/>
+        <v>726</v>
+      </c>
+      <c r="BJ8">
+        <f t="shared" si="12"/>
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="9" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>190</v>
+      </c>
+      <c r="D9">
+        <v>161</v>
+      </c>
+      <c r="E9">
+        <v>158</v>
+      </c>
+      <c r="F9">
+        <v>172</v>
+      </c>
+      <c r="G9">
+        <v>83</v>
+      </c>
+      <c r="H9" s="5">
+        <v>32</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="13"/>
+        <v>796</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="14"/>
+        <v>3</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <f t="shared" si="22"/>
+        <v>190</v>
+      </c>
+      <c r="AQ9">
+        <f t="shared" si="10"/>
+        <v>161</v>
+      </c>
+      <c r="AR9">
+        <f t="shared" si="10"/>
+        <v>158</v>
+      </c>
+      <c r="AS9">
+        <f t="shared" si="10"/>
+        <v>172</v>
+      </c>
+      <c r="AT9">
+        <f t="shared" si="10"/>
+        <v>83</v>
+      </c>
+      <c r="AU9">
+        <f t="shared" si="10"/>
+        <v>32</v>
+      </c>
+      <c r="AV9">
+        <f t="shared" si="10"/>
+        <v>796</v>
+      </c>
+      <c r="AW9">
+        <f t="shared" si="23"/>
+        <v>570</v>
+      </c>
+      <c r="AX9">
+        <f t="shared" si="11"/>
+        <v>483</v>
+      </c>
+      <c r="AY9">
+        <f t="shared" si="11"/>
+        <v>474</v>
+      </c>
+      <c r="AZ9">
+        <f t="shared" si="11"/>
+        <v>516</v>
+      </c>
+      <c r="BA9">
+        <f t="shared" si="11"/>
+        <v>249</v>
+      </c>
+      <c r="BB9">
+        <f t="shared" si="11"/>
+        <v>96</v>
+      </c>
+      <c r="BC9">
+        <f t="shared" si="11"/>
+        <v>2388</v>
+      </c>
+      <c r="BD9">
+        <f t="shared" si="24"/>
+        <v>570</v>
+      </c>
+      <c r="BE9">
+        <f t="shared" si="12"/>
+        <v>483</v>
+      </c>
+      <c r="BF9">
+        <f t="shared" si="12"/>
+        <v>474</v>
+      </c>
+      <c r="BG9">
+        <f t="shared" si="12"/>
+        <v>516</v>
+      </c>
+      <c r="BH9">
+        <f t="shared" si="12"/>
+        <v>249</v>
+      </c>
+      <c r="BI9">
+        <f t="shared" si="12"/>
+        <v>96</v>
+      </c>
+      <c r="BJ9">
+        <f t="shared" si="12"/>
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="10" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>33</v>
+      </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10">
+        <v>10</v>
+      </c>
+      <c r="F10">
+        <v>232</v>
+      </c>
+      <c r="G10">
+        <v>97</v>
+      </c>
+      <c r="H10" s="5">
+        <v>23</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="13"/>
+        <v>399</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="14"/>
+        <v>3</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <f t="shared" si="22"/>
+        <v>33</v>
+      </c>
+      <c r="AQ10">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="AR10">
+        <f t="shared" si="10"/>
+        <v>10</v>
+      </c>
+      <c r="AS10">
+        <f t="shared" si="10"/>
+        <v>232</v>
+      </c>
+      <c r="AT10">
+        <f t="shared" si="10"/>
+        <v>97</v>
+      </c>
+      <c r="AU10">
+        <f t="shared" si="10"/>
+        <v>23</v>
+      </c>
+      <c r="AV10">
+        <f t="shared" si="10"/>
+        <v>399</v>
+      </c>
+      <c r="AW10">
+        <f t="shared" si="23"/>
+        <v>99</v>
+      </c>
+      <c r="AX10">
+        <f t="shared" si="11"/>
+        <v>12</v>
+      </c>
+      <c r="AY10">
+        <f t="shared" si="11"/>
+        <v>30</v>
+      </c>
+      <c r="AZ10">
+        <f t="shared" si="11"/>
+        <v>696</v>
+      </c>
+      <c r="BA10">
+        <f t="shared" si="11"/>
+        <v>291</v>
+      </c>
+      <c r="BB10">
+        <f t="shared" si="11"/>
+        <v>69</v>
+      </c>
+      <c r="BC10">
+        <f t="shared" si="11"/>
+        <v>1197</v>
+      </c>
+      <c r="BD10">
+        <f t="shared" si="24"/>
+        <v>99</v>
+      </c>
+      <c r="BE10">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="BF10">
+        <f t="shared" si="12"/>
+        <v>30</v>
+      </c>
+      <c r="BG10">
+        <f t="shared" si="12"/>
+        <v>696</v>
+      </c>
+      <c r="BH10">
+        <f t="shared" si="12"/>
+        <v>291</v>
+      </c>
+      <c r="BI10">
+        <f t="shared" si="12"/>
+        <v>69</v>
+      </c>
+      <c r="BJ10">
+        <f t="shared" si="12"/>
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="11" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="6">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7">
+        <v>3</v>
+      </c>
+      <c r="C11" s="7">
+        <v>244</v>
+      </c>
+      <c r="D11" s="7">
+        <v>81</v>
+      </c>
+      <c r="E11" s="7">
+        <v>153</v>
+      </c>
+      <c r="F11" s="7">
+        <v>126</v>
+      </c>
+      <c r="G11" s="7">
+        <v>175</v>
+      </c>
+      <c r="H11" s="8">
+        <v>61</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="13"/>
+        <v>840</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="14"/>
+        <v>3</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <f t="shared" si="22"/>
+        <v>244</v>
+      </c>
+      <c r="AQ11">
+        <f t="shared" si="10"/>
+        <v>81</v>
+      </c>
+      <c r="AR11">
+        <f t="shared" si="10"/>
+        <v>153</v>
+      </c>
+      <c r="AS11">
+        <f t="shared" si="10"/>
+        <v>126</v>
+      </c>
+      <c r="AT11">
+        <f t="shared" si="10"/>
+        <v>175</v>
+      </c>
+      <c r="AU11">
+        <f t="shared" si="10"/>
+        <v>61</v>
+      </c>
+      <c r="AV11">
+        <f t="shared" si="10"/>
+        <v>840</v>
+      </c>
+      <c r="AW11">
+        <f t="shared" si="23"/>
+        <v>732</v>
+      </c>
+      <c r="AX11">
+        <f t="shared" si="11"/>
+        <v>243</v>
+      </c>
+      <c r="AY11">
+        <f t="shared" si="11"/>
+        <v>459</v>
+      </c>
+      <c r="AZ11">
+        <f t="shared" si="11"/>
+        <v>378</v>
+      </c>
+      <c r="BA11">
+        <f t="shared" si="11"/>
+        <v>525</v>
+      </c>
+      <c r="BB11">
+        <f t="shared" si="11"/>
+        <v>183</v>
+      </c>
+      <c r="BC11">
+        <f t="shared" si="11"/>
+        <v>2520</v>
+      </c>
+      <c r="BD11">
+        <f t="shared" si="24"/>
+        <v>732</v>
+      </c>
+      <c r="BE11">
+        <f t="shared" si="12"/>
+        <v>243</v>
+      </c>
+      <c r="BF11">
+        <f t="shared" si="12"/>
+        <v>459</v>
+      </c>
+      <c r="BG11">
+        <f t="shared" si="12"/>
+        <v>378</v>
+      </c>
+      <c r="BH11">
+        <f t="shared" si="12"/>
+        <v>525</v>
+      </c>
+      <c r="BI11">
+        <f t="shared" si="12"/>
+        <v>183</v>
+      </c>
+      <c r="BJ11">
+        <f t="shared" si="12"/>
+        <v>2520</v>
+      </c>
+    </row>
+    <row r="12" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="M12" t="s">
+        <v>30</v>
+      </c>
+      <c r="U12">
+        <f>SUM(U2:U11)</f>
+        <v>834</v>
+      </c>
+      <c r="V12">
+        <f t="shared" ref="V12:AA12" si="25">SUM(V1:V11)</f>
+        <v>555</v>
+      </c>
+      <c r="W12">
+        <f t="shared" si="25"/>
+        <v>993</v>
+      </c>
+      <c r="X12">
+        <f t="shared" si="25"/>
+        <v>435</v>
+      </c>
+      <c r="Y12">
+        <f t="shared" si="25"/>
+        <v>675</v>
+      </c>
+      <c r="Z12">
+        <f t="shared" si="25"/>
+        <v>732</v>
+      </c>
+      <c r="AA12" s="15">
+        <f t="shared" si="25"/>
+        <v>4224</v>
+      </c>
+      <c r="AI12" s="15">
+        <f>SUM(AI1:AI11)</f>
+        <v>1461</v>
+      </c>
+      <c r="AJ12">
+        <f t="shared" ref="AJ12:AO12" si="26">SUM(AJ1:AJ11)</f>
+        <v>1254</v>
+      </c>
+      <c r="AK12">
+        <f t="shared" si="26"/>
+        <v>1125</v>
+      </c>
+      <c r="AL12">
+        <f t="shared" si="26"/>
+        <v>546</v>
+      </c>
+      <c r="AM12">
+        <f t="shared" si="26"/>
+        <v>540</v>
+      </c>
+      <c r="AN12">
+        <f t="shared" si="26"/>
+        <v>1029</v>
+      </c>
+      <c r="AO12" s="15">
+        <f t="shared" si="26"/>
+        <v>5955</v>
+      </c>
+      <c r="AW12">
+        <f>SUM(AW1:AW11)</f>
+        <v>2484</v>
+      </c>
+      <c r="AX12">
+        <f t="shared" ref="AX12:BJ12" si="27">SUM(AX1:AX11)</f>
+        <v>1647</v>
+      </c>
+      <c r="AY12">
+        <f t="shared" si="27"/>
+        <v>1683</v>
+      </c>
+      <c r="AZ12">
+        <f t="shared" si="27"/>
+        <v>2748</v>
+      </c>
+      <c r="BA12">
+        <f t="shared" si="27"/>
+        <v>1704</v>
+      </c>
+      <c r="BB12">
+        <f t="shared" si="27"/>
+        <v>735</v>
+      </c>
+      <c r="BC12" s="15">
+        <f t="shared" si="27"/>
+        <v>11001</v>
+      </c>
+      <c r="BD12">
+        <f t="shared" si="27"/>
+        <v>4779</v>
+      </c>
+      <c r="BE12">
+        <f t="shared" si="27"/>
+        <v>3456</v>
+      </c>
+      <c r="BF12">
+        <f t="shared" si="27"/>
+        <v>3801</v>
+      </c>
+      <c r="BG12">
+        <f t="shared" si="27"/>
+        <v>3729</v>
+      </c>
+      <c r="BH12">
+        <f t="shared" si="27"/>
+        <v>2919</v>
+      </c>
+      <c r="BI12">
+        <f t="shared" si="27"/>
+        <v>2496</v>
+      </c>
+      <c r="BJ12" s="15">
+        <f t="shared" si="27"/>
+        <v>21180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="B13" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13">
+        <f>SUMSQ(C1:C11)</f>
+        <v>292083</v>
+      </c>
+      <c r="D13">
+        <f t="shared" ref="D13:I13" si="28">SUMSQ(D1:D11)</f>
+        <v>171304</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="28"/>
+        <v>195215</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="28"/>
+        <v>202725</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="28"/>
+        <v>131867</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="28"/>
+        <v>114522</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="28"/>
+        <v>5154790</v>
+      </c>
+      <c r="M13" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="N13">
+        <f>SUMSQ(N1:N11)</f>
+        <v>40100</v>
+      </c>
+      <c r="O13">
+        <f t="shared" ref="O13:T13" si="29">SUMSQ(O1:O11)</f>
+        <v>22213</v>
+      </c>
+      <c r="P13">
+        <f t="shared" si="29"/>
+        <v>57901</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="29"/>
+        <v>10573</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="29"/>
+        <v>43173</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="29"/>
+        <v>36730</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="29"/>
+        <v>1002784</v>
+      </c>
+      <c r="AB13">
+        <f>SUMSQ(AB1:AB11)</f>
+        <v>85773</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" ref="AC13:AH13" si="30">SUMSQ(AC1:AC11)</f>
+        <v>70676</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" si="30"/>
+        <v>56513</v>
+      </c>
+      <c r="AE13">
+        <f t="shared" si="30"/>
+        <v>15482</v>
+      </c>
+      <c r="AF13">
+        <f t="shared" si="30"/>
+        <v>11274</v>
+      </c>
+      <c r="AG13">
+        <f t="shared" si="30"/>
+        <v>64085</v>
+      </c>
+      <c r="AH13">
+        <f t="shared" si="30"/>
+        <v>1320725</v>
+      </c>
+      <c r="AP13">
+        <f>SUMSQ(AP1:AP11)</f>
+        <v>166210</v>
+      </c>
+      <c r="AQ13">
+        <f t="shared" ref="AQ13:AV13" si="31">SUMSQ(AQ1:AQ11)</f>
+        <v>78415</v>
+      </c>
+      <c r="AR13">
+        <f t="shared" si="31"/>
+        <v>80801</v>
+      </c>
+      <c r="AS13">
+        <f t="shared" si="31"/>
+        <v>176670</v>
+      </c>
+      <c r="AT13">
+        <f t="shared" si="31"/>
+        <v>77420</v>
+      </c>
+      <c r="AU13">
+        <f t="shared" si="31"/>
+        <v>13707</v>
+      </c>
+      <c r="AV13">
+        <f t="shared" si="31"/>
+        <v>2831281</v>
+      </c>
+    </row>
+    <row r="14" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="B14" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="18">
+        <f>$M$15*C13</f>
+        <v>1752498</v>
+      </c>
+      <c r="D14" s="18">
+        <f t="shared" ref="D14:I14" si="32">$M$15*D13</f>
+        <v>1027824</v>
+      </c>
+      <c r="E14" s="18">
+        <f t="shared" si="32"/>
+        <v>1171290</v>
+      </c>
+      <c r="F14" s="18">
+        <f t="shared" si="32"/>
+        <v>1216350</v>
+      </c>
+      <c r="G14" s="18">
+        <f t="shared" si="32"/>
+        <v>791202</v>
+      </c>
+      <c r="H14" s="18">
+        <f t="shared" si="32"/>
+        <v>687132</v>
+      </c>
+      <c r="I14" s="18">
+        <f t="shared" si="32"/>
+        <v>30928740</v>
+      </c>
+      <c r="M14" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="N14">
+        <f>$M$15*N13</f>
+        <v>240600</v>
+      </c>
+      <c r="O14">
+        <f t="shared" ref="O14:T14" si="33">$M$15*O13</f>
+        <v>133278</v>
+      </c>
+      <c r="P14">
+        <f t="shared" si="33"/>
+        <v>347406</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="33"/>
+        <v>63438</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="33"/>
+        <v>259038</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="33"/>
+        <v>220380</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="33"/>
+        <v>6016704</v>
+      </c>
+      <c r="AB14">
+        <f>$M$15*AB13</f>
+        <v>514638</v>
+      </c>
+      <c r="AC14">
+        <f t="shared" ref="AC14:AH14" si="34">$M$15*AC13</f>
+        <v>424056</v>
+      </c>
+      <c r="AD14">
+        <f t="shared" si="34"/>
+        <v>339078</v>
+      </c>
+      <c r="AE14">
+        <f t="shared" si="34"/>
+        <v>92892</v>
+      </c>
+      <c r="AF14">
+        <f t="shared" si="34"/>
+        <v>67644</v>
+      </c>
+      <c r="AG14">
+        <f t="shared" si="34"/>
+        <v>384510</v>
+      </c>
+      <c r="AH14">
+        <f t="shared" si="34"/>
+        <v>7924350</v>
+      </c>
+      <c r="AP14">
+        <f>$M$15*AP13</f>
+        <v>997260</v>
+      </c>
+      <c r="AQ14">
+        <f t="shared" ref="AQ14:AV14" si="35">$M$15*AQ13</f>
+        <v>470490</v>
+      </c>
+      <c r="AR14">
+        <f t="shared" si="35"/>
+        <v>484806</v>
+      </c>
+      <c r="AS14">
+        <f t="shared" si="35"/>
+        <v>1060020</v>
+      </c>
+      <c r="AT14">
+        <f t="shared" si="35"/>
+        <v>464520</v>
+      </c>
+      <c r="AU14">
+        <f t="shared" si="35"/>
+        <v>82242</v>
+      </c>
+      <c r="AV14">
+        <f t="shared" si="35"/>
+        <v>16987686</v>
+      </c>
+    </row>
+    <row r="15" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="B15" s="19"/>
+      <c r="L15" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15" s="15">
+        <f>1/(1/3)*(1/(1/3)-1)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="B16" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="16">
+        <f>SQRT(C14)/BD12</f>
+        <v>0.27700763216103425</v>
+      </c>
+      <c r="D16" s="16">
+        <f t="shared" ref="D16:I16" si="36">SQRT(D14)/BE12</f>
+        <v>0.29334969660097615</v>
+      </c>
+      <c r="E16" s="16">
+        <f t="shared" si="36"/>
+        <v>0.2847307343002361</v>
+      </c>
+      <c r="F16" s="16">
+        <f t="shared" si="36"/>
+        <v>0.29575826942319866</v>
+      </c>
+      <c r="G16" s="16">
+        <f t="shared" si="36"/>
+        <v>0.30472605774277117</v>
+      </c>
+      <c r="H16" s="16">
+        <f t="shared" si="36"/>
+        <v>0.33210507032667597</v>
+      </c>
+      <c r="I16" s="16">
+        <f t="shared" si="36"/>
+        <v>0.26257607857089182</v>
+      </c>
+      <c r="M16" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="N16" s="16">
+        <f>SQRT(N14)/U12</f>
+        <v>0.5881414133539915</v>
+      </c>
+      <c r="O16" s="16">
+        <f t="shared" ref="O16:T16" si="37">SQRT(O14)/V12</f>
+        <v>0.65778846039711325</v>
+      </c>
+      <c r="P16" s="16">
+        <f t="shared" si="37"/>
+        <v>0.59356653673279336</v>
+      </c>
+      <c r="Q16" s="16">
+        <f t="shared" si="37"/>
+        <v>0.57900922661264764</v>
+      </c>
+      <c r="R16" s="16">
+        <f t="shared" si="37"/>
+        <v>0.75401149416526358</v>
+      </c>
+      <c r="S16" s="16">
+        <f t="shared" si="37"/>
+        <v>0.64132033138364408</v>
+      </c>
+      <c r="T16" s="16">
+        <f t="shared" si="37"/>
+        <v>0.58070479703095779</v>
+      </c>
+      <c r="AB16" s="16">
+        <f>SQRT(AB14)/AI12</f>
+        <v>0.49102172692123114</v>
+      </c>
+      <c r="AC16" s="16">
+        <f t="shared" ref="AC16:AH16" si="38">SQRT(AC14)/AJ12</f>
+        <v>0.51929491473877776</v>
+      </c>
+      <c r="AD16" s="16">
+        <f t="shared" si="38"/>
+        <v>0.51760359492712327</v>
+      </c>
+      <c r="AE16" s="16">
+        <f t="shared" si="38"/>
+        <v>0.55820858832549736</v>
+      </c>
+      <c r="AF16" s="16">
+        <f t="shared" si="38"/>
+        <v>0.48163815114873881</v>
+      </c>
+      <c r="AG16" s="16">
+        <f t="shared" si="38"/>
+        <v>0.6026129284081938</v>
+      </c>
+      <c r="AH16" s="16">
+        <f t="shared" si="38"/>
+        <v>0.47271573507961734</v>
+      </c>
+      <c r="AP16" s="16">
+        <f>SQRT(AP14)/AW12</f>
+        <v>0.40202458142597325</v>
+      </c>
+      <c r="AQ16" s="16">
+        <f t="shared" ref="AQ16:AU16" si="39">SQRT(AQ14)/AX12</f>
+        <v>0.41646796367558525</v>
+      </c>
+      <c r="AR16" s="16">
+        <f t="shared" si="39"/>
+        <v>0.41371367560621475</v>
+      </c>
+      <c r="AS16" s="16">
+        <f t="shared" si="39"/>
+        <v>0.37466256437827827</v>
+      </c>
+      <c r="AT16" s="16">
+        <f t="shared" si="39"/>
+        <v>0.39997478926040658</v>
+      </c>
+      <c r="AU16" s="16">
+        <f t="shared" si="39"/>
+        <v>0.39017504801899677</v>
+      </c>
+      <c r="AV16" s="16">
+        <f>SQRT(AV14)/BC12</f>
+        <v>0.37465794593752783</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{143030CD-14A3-469B-BEF8-66DF235BC03B}">
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="15"/>
+      <c r="B2" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2" s="20"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="15"/>
+      <c r="B3" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4">
+        <v>973</v>
+      </c>
+      <c r="C4" s="16">
+        <v>0.57656996378352732</v>
+      </c>
+      <c r="D4">
+        <v>1704.5</v>
+      </c>
+      <c r="E4" s="16">
+        <v>0.45569892635228015</v>
+      </c>
+      <c r="F4">
+        <v>2898</v>
+      </c>
+      <c r="G4" s="16">
+        <v>0.33622040922029806</v>
+      </c>
+      <c r="H4">
+        <v>5575.5</v>
+      </c>
+      <c r="I4" s="16">
+        <v>0.10947146621487054</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5">
+        <v>647.5</v>
+      </c>
+      <c r="C5" s="16">
+        <v>0.66010370033529941</v>
+      </c>
+      <c r="D5">
+        <v>1463</v>
+      </c>
+      <c r="E5" s="16">
+        <v>0.49159669615942952</v>
+      </c>
+      <c r="F5">
+        <v>1921.5</v>
+      </c>
+      <c r="G5" s="16">
+        <v>0.35653574271736921</v>
+      </c>
+      <c r="H5">
+        <v>4032</v>
+      </c>
+      <c r="I5" s="16">
+        <v>0.15192172886539346</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6">
+        <v>1158.5</v>
+      </c>
+      <c r="C6" s="16">
+        <v>0.58315089003649156</v>
+      </c>
+      <c r="D6">
+        <v>1312.5</v>
+      </c>
+      <c r="E6" s="16">
+        <v>0.48946863172853905</v>
+      </c>
+      <c r="F6">
+        <v>1963.5</v>
+      </c>
+      <c r="G6" s="16">
+        <v>0.35269766277888442</v>
+      </c>
+      <c r="H6">
+        <v>4434.5</v>
+      </c>
+      <c r="I6" s="16">
+        <v>0.13095311951267588</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7">
+        <v>507.5</v>
+      </c>
+      <c r="C7" s="16">
+        <v>0.56545916638805438</v>
+      </c>
+      <c r="D7">
+        <v>637</v>
+      </c>
+      <c r="E7" s="16">
+        <v>0.53998474561090493</v>
+      </c>
+      <c r="F7">
+        <v>3206</v>
+      </c>
+      <c r="G7" s="16">
+        <v>0.29621696215186122</v>
+      </c>
+      <c r="H7">
+        <v>4350.5</v>
+      </c>
+      <c r="I7" s="16">
+        <v>0.15738293936075731</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8">
+        <v>787.5</v>
+      </c>
+      <c r="C8" s="16">
+        <v>0.77295557275972693</v>
+      </c>
+      <c r="D8">
+        <v>630</v>
+      </c>
+      <c r="E8" s="16">
+        <v>0.44361695453573219</v>
+      </c>
+      <c r="F8">
+        <v>1988</v>
+      </c>
+      <c r="G8" s="16">
+        <v>0.33329731718027883</v>
+      </c>
+      <c r="H8">
+        <v>3405.5</v>
+      </c>
+      <c r="I8" s="16">
+        <v>0.17657894363220863</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9">
+        <v>854</v>
+      </c>
+      <c r="C9" s="16">
+        <v>0.6405216445353632</v>
+      </c>
+      <c r="D9">
+        <v>1200.5</v>
+      </c>
+      <c r="E9" s="16">
+        <v>0.59409362218949024</v>
+      </c>
+      <c r="F9">
+        <v>857.5</v>
+      </c>
+      <c r="G9" s="16">
+        <v>0.31916912487545152</v>
+      </c>
+      <c r="H9">
+        <v>2912</v>
+      </c>
+      <c r="I9" s="16">
+        <v>0.22789698766793456</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10">
+        <v>4928</v>
+      </c>
+      <c r="C10" s="16">
+        <v>0.56752532419697355</v>
+      </c>
+      <c r="D10">
+        <v>6947.5</v>
+      </c>
+      <c r="E10" s="16">
+        <v>0.43204042404176263</v>
+      </c>
+      <c r="F10">
+        <v>12834.5</v>
+      </c>
+      <c r="G10" s="16">
+        <v>0.29621000792443913</v>
+      </c>
+      <c r="H10">
+        <v>24710</v>
+      </c>
+      <c r="I10" s="16">
+        <v>5.2093441354391638E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F14D51-A9CF-426A-ABB5-19C0E1B98BBB}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="11.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="18">
+        <f>MAS!I14</f>
+        <v>1656958.3333333335</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="18">
+        <f>BER!I14</f>
+        <v>30928740</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B4" s="18">
+        <f>B2/B1</f>
+        <v>18.665973294440111</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26724C6A-726E-4F3E-ACED-21AE035328E5}">
   <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/data/EjemploDominios.xlsx
+++ b/data/EjemploDominios.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giova\Documents\GB\MisCursos\Muestreo2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8729624E-DB31-44DA-98A0-768ABEE15F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE288466-B0ED-4787-B29C-0C44D0454C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{42CC5FC2-8CC7-43C2-B7FE-203DEB835DFD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{42CC5FC2-8CC7-43C2-B7FE-203DEB835DFD}"/>
   </bookViews>
   <sheets>
     <sheet name="MAS" sheetId="1" r:id="rId1"/>
     <sheet name="BER" sheetId="3" r:id="rId2"/>
-    <sheet name="Cuadro" sheetId="4" r:id="rId3"/>
-    <sheet name="Deff" sheetId="5" r:id="rId4"/>
-    <sheet name="Diccionario" sheetId="2" r:id="rId5"/>
+    <sheet name="MCR" sheetId="6" r:id="rId3"/>
+    <sheet name="Cuadro" sheetId="4" r:id="rId4"/>
+    <sheet name="Deff" sheetId="5" r:id="rId5"/>
+    <sheet name="Diccionario" sheetId="2" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,8 +43,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="52">
   <si>
     <t>ID</t>
   </si>
@@ -193,6 +216,15 @@
   <si>
     <t>VAR BER</t>
   </si>
+  <si>
+    <t>pk =</t>
+  </si>
+  <si>
+    <t>m =</t>
+  </si>
+  <si>
+    <t>Sum_(ykd/pk-t_ymcr,d)^2</t>
+  </si>
 </sst>
 </file>
 
@@ -201,7 +233,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -240,6 +272,15 @@
       <b/>
       <i/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -389,7 +430,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -413,6 +454,9 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3817,7 +3861,7 @@
         <v>0.22789698766793456</v>
       </c>
       <c r="I16" s="16">
-        <f t="shared" si="91"/>
+        <f>SQRT(I14)/BJ12</f>
         <v>5.2093441354391638E-2</v>
       </c>
       <c r="M16" s="19" t="s">
@@ -7086,6 +7130,3191 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DECAB487-B3C8-4CF4-A9FC-A3E99C031A3C}">
+  <dimension ref="A1:BJ19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="4.7265625" customWidth="1"/>
+    <col min="2" max="2" width="8.453125" customWidth="1"/>
+    <col min="3" max="8" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.7265625" customWidth="1"/>
+    <col min="11" max="11" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.36328125" customWidth="1"/>
+    <col min="13" max="13" width="6.26953125" customWidth="1"/>
+    <col min="14" max="14" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="19" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1" s="12" t="str">
+        <f t="shared" ref="N1" si="0">C1&amp;"*D1"</f>
+        <v>P2*D1</v>
+      </c>
+      <c r="O1" s="12" t="str">
+        <f>D1&amp;"*D1"</f>
+        <v>P3*D1</v>
+      </c>
+      <c r="P1" s="12" t="str">
+        <f>E1&amp;"*D1"</f>
+        <v>P4*D1</v>
+      </c>
+      <c r="Q1" s="12" t="str">
+        <f>F1&amp;"*D1"</f>
+        <v>P5*D1</v>
+      </c>
+      <c r="R1" s="12" t="str">
+        <f>G1&amp;"*D1"</f>
+        <v>P6*D1</v>
+      </c>
+      <c r="S1" s="12" t="str">
+        <f>H1&amp;"*D1"</f>
+        <v>P7*D1</v>
+      </c>
+      <c r="T1" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="U1" s="11" t="str">
+        <f>N1&amp;"*Fex"</f>
+        <v>P2*D1*Fex</v>
+      </c>
+      <c r="V1" s="11" t="str">
+        <f t="shared" ref="V1:AA1" si="1">O1&amp;"*Fex"</f>
+        <v>P3*D1*Fex</v>
+      </c>
+      <c r="W1" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>P4*D1*Fex</v>
+      </c>
+      <c r="X1" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>P5*D1*Fex</v>
+      </c>
+      <c r="Y1" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>P6*D1*Fex</v>
+      </c>
+      <c r="Z1" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>P7*D1*Fex</v>
+      </c>
+      <c r="AA1" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>Total*D1*Fex</v>
+      </c>
+      <c r="AB1" s="12" t="str">
+        <f>C1&amp;"*D2"</f>
+        <v>P2*D2</v>
+      </c>
+      <c r="AC1" s="12" t="str">
+        <f>D1&amp;"*D2"</f>
+        <v>P3*D2</v>
+      </c>
+      <c r="AD1" s="12" t="str">
+        <f>E1&amp;"*D2"</f>
+        <v>P4*D2</v>
+      </c>
+      <c r="AE1" s="12" t="str">
+        <f>F1&amp;"*D2"</f>
+        <v>P5*D2</v>
+      </c>
+      <c r="AF1" s="12" t="str">
+        <f>G1&amp;"*D2"</f>
+        <v>P6*D2</v>
+      </c>
+      <c r="AG1" s="12" t="str">
+        <f>H1&amp;"*D2"</f>
+        <v>P7*D2</v>
+      </c>
+      <c r="AH1" s="12" t="str">
+        <f>I1&amp;"*D2"</f>
+        <v>Total*D2</v>
+      </c>
+      <c r="AI1" s="13" t="str">
+        <f>AB1&amp;"*Fex"</f>
+        <v>P2*D2*Fex</v>
+      </c>
+      <c r="AJ1" s="13" t="str">
+        <f t="shared" ref="AJ1:AO1" si="2">AC1&amp;"*Fex"</f>
+        <v>P3*D2*Fex</v>
+      </c>
+      <c r="AK1" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>P4*D2*Fex</v>
+      </c>
+      <c r="AL1" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>P5*D2*Fex</v>
+      </c>
+      <c r="AM1" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>P6*D2*Fex</v>
+      </c>
+      <c r="AN1" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>P7*D2*Fex</v>
+      </c>
+      <c r="AO1" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v>Total*D2*Fex</v>
+      </c>
+      <c r="AP1" s="14" t="str">
+        <f>C1&amp;"*D3"</f>
+        <v>P2*D3</v>
+      </c>
+      <c r="AQ1" s="14" t="str">
+        <f>D1&amp;"*D3"</f>
+        <v>P3*D3</v>
+      </c>
+      <c r="AR1" s="14" t="str">
+        <f>E1&amp;"*D3"</f>
+        <v>P4*D3</v>
+      </c>
+      <c r="AS1" s="14" t="str">
+        <f>F1&amp;"*D3"</f>
+        <v>P5*D3</v>
+      </c>
+      <c r="AT1" s="14" t="str">
+        <f>G1&amp;"*D3"</f>
+        <v>P6*D3</v>
+      </c>
+      <c r="AU1" s="14" t="str">
+        <f>H1&amp;"*D3"</f>
+        <v>P7*D3</v>
+      </c>
+      <c r="AV1" s="14" t="str">
+        <f>I1&amp;"*D3"</f>
+        <v>Total*D3</v>
+      </c>
+      <c r="AW1" s="13" t="str">
+        <f>AP1&amp;"*Fex"</f>
+        <v>P2*D3*Fex</v>
+      </c>
+      <c r="AX1" s="13" t="str">
+        <f t="shared" ref="AX1:BC1" si="3">AQ1&amp;"*Fex"</f>
+        <v>P3*D3*Fex</v>
+      </c>
+      <c r="AY1" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>P4*D3*Fex</v>
+      </c>
+      <c r="AZ1" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>P5*D3*Fex</v>
+      </c>
+      <c r="BA1" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>P6*D3*Fex</v>
+      </c>
+      <c r="BB1" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>P7*D3*Fex</v>
+      </c>
+      <c r="BC1" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>Total*D3*Fex</v>
+      </c>
+      <c r="BD1" s="17" t="str">
+        <f>C1&amp;"*Fex"</f>
+        <v>P2*Fex</v>
+      </c>
+      <c r="BE1" s="17" t="str">
+        <f>D1&amp;"*Fex"</f>
+        <v>P3*Fex</v>
+      </c>
+      <c r="BF1" s="17" t="str">
+        <f>E1&amp;"*Fex"</f>
+        <v>P4*Fex</v>
+      </c>
+      <c r="BG1" s="17" t="str">
+        <f>F1&amp;"*Fex"</f>
+        <v>P5*Fex</v>
+      </c>
+      <c r="BH1" s="17" t="str">
+        <f>G1&amp;"*Fex"</f>
+        <v>P6*Fex</v>
+      </c>
+      <c r="BI1" s="17" t="str">
+        <f>H1&amp;"*Fex"</f>
+        <v>P7*Fex</v>
+      </c>
+      <c r="BJ1" s="17" t="str">
+        <f>I1&amp;"*Fex"</f>
+        <v>Total*Fex</v>
+      </c>
+    </row>
+    <row r="2" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>224</v>
+      </c>
+      <c r="D2">
+        <v>68</v>
+      </c>
+      <c r="E2">
+        <v>187</v>
+      </c>
+      <c r="F2">
+        <v>36</v>
+      </c>
+      <c r="G2">
+        <v>64</v>
+      </c>
+      <c r="H2" s="5">
+        <v>36</v>
+      </c>
+      <c r="I2">
+        <f>SUM(C2:H2)</f>
+        <v>615</v>
+      </c>
+      <c r="J2">
+        <f>1/($B$19*$B$18)</f>
+        <v>3.5</v>
+      </c>
+      <c r="K2">
+        <f>IF($B2=1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <f>IF($B2=2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <f>IF($B2=3,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <f>C2*$K2</f>
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <f>D2*$K2</f>
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <f>E2*$K2</f>
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <f>F2*$K2</f>
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <f>G2*$K2</f>
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <f>I2*$K2</f>
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <f>I2*$K2</f>
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <f>N2*$J2</f>
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <f t="shared" ref="V2:AA11" si="4">O2*$J2</f>
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <f>C2*$L2</f>
+        <v>224</v>
+      </c>
+      <c r="AC2">
+        <f>D2*$L2</f>
+        <v>68</v>
+      </c>
+      <c r="AD2">
+        <f>E2*$L2</f>
+        <v>187</v>
+      </c>
+      <c r="AE2">
+        <f>F2*$L2</f>
+        <v>36</v>
+      </c>
+      <c r="AF2">
+        <f>G2*$L2</f>
+        <v>64</v>
+      </c>
+      <c r="AG2">
+        <f>H2*$L2</f>
+        <v>36</v>
+      </c>
+      <c r="AH2">
+        <f>I2*$L2</f>
+        <v>615</v>
+      </c>
+      <c r="AI2">
+        <f>AB2*$J2</f>
+        <v>784</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" ref="AJ2:AO11" si="5">AC2*$J2</f>
+        <v>238</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="5"/>
+        <v>654.5</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="5"/>
+        <v>126</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="5"/>
+        <v>224</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="5"/>
+        <v>126</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="5"/>
+        <v>2152.5</v>
+      </c>
+      <c r="AP2">
+        <f>C2*$M2</f>
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <f>D2*$M2</f>
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <f>E2*$M2</f>
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <f>F2*$M2</f>
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <f>G2*$M2</f>
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <f>H2*$M2</f>
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <f>I2*$M2</f>
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <f>AP2*$J2</f>
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" ref="AX2:BC11" si="6">AQ2*$J2</f>
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BA2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BC2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BD2">
+        <f>C2*$J2</f>
+        <v>784</v>
+      </c>
+      <c r="BE2">
+        <f>D2*$J2</f>
+        <v>238</v>
+      </c>
+      <c r="BF2">
+        <f>E2*$J2</f>
+        <v>654.5</v>
+      </c>
+      <c r="BG2">
+        <f>F2*$J2</f>
+        <v>126</v>
+      </c>
+      <c r="BH2">
+        <f>G2*$J2</f>
+        <v>224</v>
+      </c>
+      <c r="BI2">
+        <f>H2*$J2</f>
+        <v>126</v>
+      </c>
+      <c r="BJ2">
+        <f>I2*$J2</f>
+        <v>2152.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>112</v>
+      </c>
+      <c r="D3">
+        <v>42</v>
+      </c>
+      <c r="E3">
+        <v>126</v>
+      </c>
+      <c r="F3">
+        <v>78</v>
+      </c>
+      <c r="G3">
+        <v>207</v>
+      </c>
+      <c r="H3" s="5">
+        <v>63</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I11" si="7">SUM(C3:H3)</f>
+        <v>628</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J11" si="8">1/($B$19*$B$18)</f>
+        <v>3.5</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K11" si="9">IF($B3=1,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <f t="shared" ref="L3:L11" si="10">IF($B3=2,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <f t="shared" ref="M3:M11" si="11">IF($B3=3,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <f t="shared" ref="N3:N11" si="12">C3*$K3</f>
+        <v>112</v>
+      </c>
+      <c r="O3">
+        <f>D3*$K3</f>
+        <v>42</v>
+      </c>
+      <c r="P3">
+        <f>E3*$K3</f>
+        <v>126</v>
+      </c>
+      <c r="Q3">
+        <f>F3*$K3</f>
+        <v>78</v>
+      </c>
+      <c r="R3">
+        <f>G3*$K3</f>
+        <v>207</v>
+      </c>
+      <c r="S3">
+        <f>H3*$K3</f>
+        <v>63</v>
+      </c>
+      <c r="T3">
+        <f>I3*$K3</f>
+        <v>628</v>
+      </c>
+      <c r="U3">
+        <f>N3*$J3</f>
+        <v>392</v>
+      </c>
+      <c r="V3">
+        <f t="shared" si="4"/>
+        <v>147</v>
+      </c>
+      <c r="W3">
+        <f t="shared" si="4"/>
+        <v>441</v>
+      </c>
+      <c r="X3">
+        <f t="shared" si="4"/>
+        <v>273</v>
+      </c>
+      <c r="Y3">
+        <f t="shared" si="4"/>
+        <v>724.5</v>
+      </c>
+      <c r="Z3">
+        <f t="shared" si="4"/>
+        <v>220.5</v>
+      </c>
+      <c r="AA3">
+        <f t="shared" si="4"/>
+        <v>2198</v>
+      </c>
+      <c r="AB3">
+        <f>C3*$L3</f>
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <f>D3*$L3</f>
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <f>E3*$L3</f>
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <f>F3*$L3</f>
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <f>G3*$L3</f>
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <f>H3*$L3</f>
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <f>I3*$L3</f>
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" ref="AI3:AI11" si="13">AB3*$J3</f>
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <f>C3*$M3</f>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <f>D3*$M3</f>
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <f>E3*$M3</f>
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <f>F3*$M3</f>
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <f>G3*$M3</f>
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <f>H3*$M3</f>
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <f>I3*$M3</f>
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" ref="AW3:AW11" si="14">AP3*$J3</f>
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <f>C3*$J3</f>
+        <v>392</v>
+      </c>
+      <c r="BE3">
+        <f>D3*$J3</f>
+        <v>147</v>
+      </c>
+      <c r="BF3">
+        <f>E3*$J3</f>
+        <v>441</v>
+      </c>
+      <c r="BG3">
+        <f>F3*$J3</f>
+        <v>273</v>
+      </c>
+      <c r="BH3">
+        <f>G3*$J3</f>
+        <v>724.5</v>
+      </c>
+      <c r="BI3">
+        <f>H3*$J3</f>
+        <v>220.5</v>
+      </c>
+      <c r="BJ3">
+        <f>I3*$J3</f>
+        <v>2198</v>
+      </c>
+    </row>
+    <row r="4" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>227</v>
+      </c>
+      <c r="D4">
+        <v>154</v>
+      </c>
+      <c r="E4">
+        <v>78</v>
+      </c>
+      <c r="F4">
+        <v>155</v>
+      </c>
+      <c r="G4">
+        <v>169</v>
+      </c>
+      <c r="H4" s="5">
+        <v>57</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="7"/>
+        <v>840</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="8"/>
+        <v>3.5</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <f>D4*$K4</f>
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <f>E4*$K4</f>
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <f>F4*$K4</f>
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <f>G4*$K4</f>
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <f>H4*$K4</f>
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <f>I4*$K4</f>
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <f>N4*$J4</f>
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <f>C4*$L4</f>
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <f>D4*$L4</f>
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <f>E4*$L4</f>
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <f>F4*$L4</f>
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <f>G4*$L4</f>
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <f>H4*$L4</f>
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <f>I4*$L4</f>
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <f>C4*$M4</f>
+        <v>227</v>
+      </c>
+      <c r="AQ4">
+        <f>D4*$M4</f>
+        <v>154</v>
+      </c>
+      <c r="AR4">
+        <f>E4*$M4</f>
+        <v>78</v>
+      </c>
+      <c r="AS4">
+        <f>F4*$M4</f>
+        <v>155</v>
+      </c>
+      <c r="AT4">
+        <f>G4*$M4</f>
+        <v>169</v>
+      </c>
+      <c r="AU4">
+        <f>H4*$M4</f>
+        <v>57</v>
+      </c>
+      <c r="AV4">
+        <f>I4*$M4</f>
+        <v>840</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="14"/>
+        <v>794.5</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="6"/>
+        <v>539</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="6"/>
+        <v>273</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="6"/>
+        <v>542.5</v>
+      </c>
+      <c r="BA4">
+        <f t="shared" si="6"/>
+        <v>591.5</v>
+      </c>
+      <c r="BB4">
+        <f t="shared" si="6"/>
+        <v>199.5</v>
+      </c>
+      <c r="BC4">
+        <f t="shared" si="6"/>
+        <v>2940</v>
+      </c>
+      <c r="BD4">
+        <f>C4*$J4</f>
+        <v>794.5</v>
+      </c>
+      <c r="BE4">
+        <f>D4*$J4</f>
+        <v>539</v>
+      </c>
+      <c r="BF4">
+        <f>E4*$J4</f>
+        <v>273</v>
+      </c>
+      <c r="BG4">
+        <f>F4*$J4</f>
+        <v>542.5</v>
+      </c>
+      <c r="BH4">
+        <f>G4*$J4</f>
+        <v>591.5</v>
+      </c>
+      <c r="BI4">
+        <f>H4*$J4</f>
+        <v>199.5</v>
+      </c>
+      <c r="BJ4">
+        <f>I4*$J4</f>
+        <v>2940</v>
+      </c>
+    </row>
+    <row r="5" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>166</v>
+      </c>
+      <c r="D5">
+        <v>143</v>
+      </c>
+      <c r="E5">
+        <v>205</v>
+      </c>
+      <c r="F5">
+        <v>67</v>
+      </c>
+      <c r="G5">
+        <v>18</v>
+      </c>
+      <c r="H5" s="5">
+        <v>181</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="7"/>
+        <v>780</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="8"/>
+        <v>3.5</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="12"/>
+        <v>166</v>
+      </c>
+      <c r="O5">
+        <f>D5*$K5</f>
+        <v>143</v>
+      </c>
+      <c r="P5">
+        <f>E5*$K5</f>
+        <v>205</v>
+      </c>
+      <c r="Q5">
+        <f>F5*$K5</f>
+        <v>67</v>
+      </c>
+      <c r="R5">
+        <f>G5*$K5</f>
+        <v>18</v>
+      </c>
+      <c r="S5">
+        <f>H5*$K5</f>
+        <v>181</v>
+      </c>
+      <c r="T5">
+        <f>I5*$K5</f>
+        <v>780</v>
+      </c>
+      <c r="U5">
+        <f>N5*$J5</f>
+        <v>581</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="4"/>
+        <v>500.5</v>
+      </c>
+      <c r="W5">
+        <f t="shared" si="4"/>
+        <v>717.5</v>
+      </c>
+      <c r="X5">
+        <f t="shared" si="4"/>
+        <v>234.5</v>
+      </c>
+      <c r="Y5">
+        <f t="shared" si="4"/>
+        <v>63</v>
+      </c>
+      <c r="Z5">
+        <f t="shared" si="4"/>
+        <v>633.5</v>
+      </c>
+      <c r="AA5">
+        <f t="shared" si="4"/>
+        <v>2730</v>
+      </c>
+      <c r="AB5">
+        <f>C5*$L5</f>
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <f>D5*$L5</f>
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <f>E5*$L5</f>
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <f>F5*$L5</f>
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <f>G5*$L5</f>
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <f>H5*$L5</f>
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <f>I5*$L5</f>
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <f>C5*$M5</f>
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <f>D5*$M5</f>
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <f>E5*$M5</f>
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <f>F5*$M5</f>
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <f>G5*$M5</f>
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <f>H5*$M5</f>
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <f>I5*$M5</f>
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <f>C5*$J5</f>
+        <v>581</v>
+      </c>
+      <c r="BE5">
+        <f>D5*$J5</f>
+        <v>500.5</v>
+      </c>
+      <c r="BF5">
+        <f>E5*$J5</f>
+        <v>717.5</v>
+      </c>
+      <c r="BG5">
+        <f>F5*$J5</f>
+        <v>234.5</v>
+      </c>
+      <c r="BH5">
+        <f>G5*$J5</f>
+        <v>63</v>
+      </c>
+      <c r="BI5">
+        <f>H5*$J5</f>
+        <v>633.5</v>
+      </c>
+      <c r="BJ5">
+        <f>I5*$J5</f>
+        <v>2730</v>
+      </c>
+    </row>
+    <row r="6" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>134</v>
+      </c>
+      <c r="D6">
+        <v>149</v>
+      </c>
+      <c r="E6">
+        <v>162</v>
+      </c>
+      <c r="F6">
+        <v>231</v>
+      </c>
+      <c r="G6">
+        <v>44</v>
+      </c>
+      <c r="H6" s="5">
+        <v>72</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="7"/>
+        <v>792</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="8"/>
+        <v>3.5</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <f>D6*$K6</f>
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <f>E6*$K6</f>
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <f>F6*$K6</f>
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <f>G6*$K6</f>
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <f>H6*$K6</f>
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <f>I6*$K6</f>
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <f>N6*$J6</f>
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <f>C6*$L6</f>
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <f>D6*$L6</f>
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <f>E6*$L6</f>
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <f>F6*$L6</f>
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <f>G6*$L6</f>
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <f>H6*$L6</f>
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <f>I6*$L6</f>
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f>C6*$M6</f>
+        <v>134</v>
+      </c>
+      <c r="AQ6">
+        <f>D6*$M6</f>
+        <v>149</v>
+      </c>
+      <c r="AR6">
+        <f>E6*$M6</f>
+        <v>162</v>
+      </c>
+      <c r="AS6">
+        <f>F6*$M6</f>
+        <v>231</v>
+      </c>
+      <c r="AT6">
+        <f>G6*$M6</f>
+        <v>44</v>
+      </c>
+      <c r="AU6">
+        <f>H6*$M6</f>
+        <v>72</v>
+      </c>
+      <c r="AV6">
+        <f>I6*$M6</f>
+        <v>792</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="14"/>
+        <v>469</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="6"/>
+        <v>521.5</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="6"/>
+        <v>567</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="6"/>
+        <v>808.5</v>
+      </c>
+      <c r="BA6">
+        <f t="shared" si="6"/>
+        <v>154</v>
+      </c>
+      <c r="BB6">
+        <f t="shared" si="6"/>
+        <v>252</v>
+      </c>
+      <c r="BC6">
+        <f t="shared" si="6"/>
+        <v>2772</v>
+      </c>
+      <c r="BD6">
+        <f>C6*$J6</f>
+        <v>469</v>
+      </c>
+      <c r="BE6">
+        <f>D6*$J6</f>
+        <v>521.5</v>
+      </c>
+      <c r="BF6">
+        <f>E6*$J6</f>
+        <v>567</v>
+      </c>
+      <c r="BG6">
+        <f>F6*$J6</f>
+        <v>808.5</v>
+      </c>
+      <c r="BH6">
+        <f>G6*$J6</f>
+        <v>154</v>
+      </c>
+      <c r="BI6">
+        <f>H6*$J6</f>
+        <v>252</v>
+      </c>
+      <c r="BJ6">
+        <f>I6*$J6</f>
+        <v>2772</v>
+      </c>
+    </row>
+    <row r="7" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>109</v>
+      </c>
+      <c r="D7">
+        <v>224</v>
+      </c>
+      <c r="E7">
+        <v>138</v>
+      </c>
+      <c r="F7">
+        <v>31</v>
+      </c>
+      <c r="G7">
+        <v>73</v>
+      </c>
+      <c r="H7" s="5">
+        <v>65</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="7"/>
+        <v>640</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="8"/>
+        <v>3.5</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <f>D7*$K7</f>
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <f>E7*$K7</f>
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <f>F7*$K7</f>
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <f>G7*$K7</f>
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <f>H7*$K7</f>
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <f>I7*$K7</f>
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <f>N7*$J7</f>
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <f>C7*$L7</f>
+        <v>109</v>
+      </c>
+      <c r="AC7">
+        <f>D7*$L7</f>
+        <v>224</v>
+      </c>
+      <c r="AD7">
+        <f>E7*$L7</f>
+        <v>138</v>
+      </c>
+      <c r="AE7">
+        <f>F7*$L7</f>
+        <v>31</v>
+      </c>
+      <c r="AF7">
+        <f>G7*$L7</f>
+        <v>73</v>
+      </c>
+      <c r="AG7">
+        <f>H7*$L7</f>
+        <v>65</v>
+      </c>
+      <c r="AH7">
+        <f>I7*$L7</f>
+        <v>640</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="13"/>
+        <v>381.5</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="5"/>
+        <v>784</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="5"/>
+        <v>483</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="5"/>
+        <v>108.5</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="5"/>
+        <v>255.5</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="5"/>
+        <v>227.5</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="5"/>
+        <v>2240</v>
+      </c>
+      <c r="AP7">
+        <f>C7*$M7</f>
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <f>D7*$M7</f>
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <f>E7*$M7</f>
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <f>F7*$M7</f>
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <f>G7*$M7</f>
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <f>H7*$M7</f>
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <f>I7*$M7</f>
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <f>C7*$J7</f>
+        <v>381.5</v>
+      </c>
+      <c r="BE7">
+        <f>D7*$J7</f>
+        <v>784</v>
+      </c>
+      <c r="BF7">
+        <f>E7*$J7</f>
+        <v>483</v>
+      </c>
+      <c r="BG7">
+        <f>F7*$J7</f>
+        <v>108.5</v>
+      </c>
+      <c r="BH7">
+        <f>G7*$J7</f>
+        <v>255.5</v>
+      </c>
+      <c r="BI7">
+        <f>H7*$J7</f>
+        <v>227.5</v>
+      </c>
+      <c r="BJ7">
+        <f>I7*$J7</f>
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="8" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>154</v>
+      </c>
+      <c r="D8">
+        <v>126</v>
+      </c>
+      <c r="E8">
+        <v>50</v>
+      </c>
+      <c r="F8">
+        <v>115</v>
+      </c>
+      <c r="G8">
+        <v>43</v>
+      </c>
+      <c r="H8" s="5">
+        <v>242</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="7"/>
+        <v>730</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="8"/>
+        <v>3.5</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <f>D8*$K8</f>
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <f>E8*$K8</f>
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <f>F8*$K8</f>
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <f>G8*$K8</f>
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <f>H8*$K8</f>
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <f>I8*$K8</f>
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <f>N8*$J8</f>
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <f>C8*$L8</f>
+        <v>154</v>
+      </c>
+      <c r="AC8">
+        <f>D8*$L8</f>
+        <v>126</v>
+      </c>
+      <c r="AD8">
+        <f>E8*$L8</f>
+        <v>50</v>
+      </c>
+      <c r="AE8">
+        <f>F8*$L8</f>
+        <v>115</v>
+      </c>
+      <c r="AF8">
+        <f>G8*$L8</f>
+        <v>43</v>
+      </c>
+      <c r="AG8">
+        <f>H8*$L8</f>
+        <v>242</v>
+      </c>
+      <c r="AH8">
+        <f>I8*$L8</f>
+        <v>730</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="13"/>
+        <v>539</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="5"/>
+        <v>441</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="5"/>
+        <v>175</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="5"/>
+        <v>402.5</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="5"/>
+        <v>150.5</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="5"/>
+        <v>847</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="5"/>
+        <v>2555</v>
+      </c>
+      <c r="AP8">
+        <f>C8*$M8</f>
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <f>D8*$M8</f>
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <f>E8*$M8</f>
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <f>F8*$M8</f>
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <f>G8*$M8</f>
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <f>H8*$M8</f>
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <f>I8*$M8</f>
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <f>C8*$J8</f>
+        <v>539</v>
+      </c>
+      <c r="BE8">
+        <f>D8*$J8</f>
+        <v>441</v>
+      </c>
+      <c r="BF8">
+        <f>E8*$J8</f>
+        <v>175</v>
+      </c>
+      <c r="BG8">
+        <f>F8*$J8</f>
+        <v>402.5</v>
+      </c>
+      <c r="BH8">
+        <f>G8*$J8</f>
+        <v>150.5</v>
+      </c>
+      <c r="BI8">
+        <f>H8*$J8</f>
+        <v>847</v>
+      </c>
+      <c r="BJ8">
+        <f>I8*$J8</f>
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="9" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>190</v>
+      </c>
+      <c r="D9">
+        <v>161</v>
+      </c>
+      <c r="E9">
+        <v>158</v>
+      </c>
+      <c r="F9">
+        <v>172</v>
+      </c>
+      <c r="G9">
+        <v>83</v>
+      </c>
+      <c r="H9" s="5">
+        <v>32</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="7"/>
+        <v>796</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="8"/>
+        <v>3.5</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <f>D9*$K9</f>
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <f>E9*$K9</f>
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <f>F9*$K9</f>
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <f>G9*$K9</f>
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <f>H9*$K9</f>
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <f>I9*$K9</f>
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <f>N9*$J9</f>
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <f>C9*$L9</f>
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <f>D9*$L9</f>
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <f>E9*$L9</f>
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <f>F9*$L9</f>
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <f>G9*$L9</f>
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <f>H9*$L9</f>
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <f>I9*$L9</f>
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <f>C9*$M9</f>
+        <v>190</v>
+      </c>
+      <c r="AQ9">
+        <f>D9*$M9</f>
+        <v>161</v>
+      </c>
+      <c r="AR9">
+        <f>E9*$M9</f>
+        <v>158</v>
+      </c>
+      <c r="AS9">
+        <f>F9*$M9</f>
+        <v>172</v>
+      </c>
+      <c r="AT9">
+        <f>G9*$M9</f>
+        <v>83</v>
+      </c>
+      <c r="AU9">
+        <f>H9*$M9</f>
+        <v>32</v>
+      </c>
+      <c r="AV9">
+        <f>I9*$M9</f>
+        <v>796</v>
+      </c>
+      <c r="AW9">
+        <f t="shared" si="14"/>
+        <v>665</v>
+      </c>
+      <c r="AX9">
+        <f t="shared" si="6"/>
+        <v>563.5</v>
+      </c>
+      <c r="AY9">
+        <f t="shared" si="6"/>
+        <v>553</v>
+      </c>
+      <c r="AZ9">
+        <f t="shared" si="6"/>
+        <v>602</v>
+      </c>
+      <c r="BA9">
+        <f t="shared" si="6"/>
+        <v>290.5</v>
+      </c>
+      <c r="BB9">
+        <f t="shared" si="6"/>
+        <v>112</v>
+      </c>
+      <c r="BC9">
+        <f t="shared" si="6"/>
+        <v>2786</v>
+      </c>
+      <c r="BD9">
+        <f>C9*$J9</f>
+        <v>665</v>
+      </c>
+      <c r="BE9">
+        <f>D9*$J9</f>
+        <v>563.5</v>
+      </c>
+      <c r="BF9">
+        <f>E9*$J9</f>
+        <v>553</v>
+      </c>
+      <c r="BG9">
+        <f>F9*$J9</f>
+        <v>602</v>
+      </c>
+      <c r="BH9">
+        <f>G9*$J9</f>
+        <v>290.5</v>
+      </c>
+      <c r="BI9">
+        <f>H9*$J9</f>
+        <v>112</v>
+      </c>
+      <c r="BJ9">
+        <f>I9*$J9</f>
+        <v>2786</v>
+      </c>
+    </row>
+    <row r="10" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>33</v>
+      </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10">
+        <v>10</v>
+      </c>
+      <c r="F10">
+        <v>232</v>
+      </c>
+      <c r="G10">
+        <v>97</v>
+      </c>
+      <c r="H10" s="5">
+        <v>23</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="7"/>
+        <v>399</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="8"/>
+        <v>3.5</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <f>D10*$K10</f>
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <f>E10*$K10</f>
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <f>F10*$K10</f>
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <f>G10*$K10</f>
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <f>H10*$K10</f>
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <f>I10*$K10</f>
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <f>N10*$J10</f>
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <f>C10*$L10</f>
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <f>D10*$L10</f>
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <f>E10*$L10</f>
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <f>F10*$L10</f>
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <f>G10*$L10</f>
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <f>H10*$L10</f>
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <f>I10*$L10</f>
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <f>C10*$M10</f>
+        <v>33</v>
+      </c>
+      <c r="AQ10">
+        <f>D10*$M10</f>
+        <v>4</v>
+      </c>
+      <c r="AR10">
+        <f>E10*$M10</f>
+        <v>10</v>
+      </c>
+      <c r="AS10">
+        <f>F10*$M10</f>
+        <v>232</v>
+      </c>
+      <c r="AT10">
+        <f>G10*$M10</f>
+        <v>97</v>
+      </c>
+      <c r="AU10">
+        <f>H10*$M10</f>
+        <v>23</v>
+      </c>
+      <c r="AV10">
+        <f>I10*$M10</f>
+        <v>399</v>
+      </c>
+      <c r="AW10">
+        <f t="shared" si="14"/>
+        <v>115.5</v>
+      </c>
+      <c r="AX10">
+        <f t="shared" si="6"/>
+        <v>14</v>
+      </c>
+      <c r="AY10">
+        <f t="shared" si="6"/>
+        <v>35</v>
+      </c>
+      <c r="AZ10">
+        <f t="shared" si="6"/>
+        <v>812</v>
+      </c>
+      <c r="BA10">
+        <f t="shared" si="6"/>
+        <v>339.5</v>
+      </c>
+      <c r="BB10">
+        <f t="shared" si="6"/>
+        <v>80.5</v>
+      </c>
+      <c r="BC10">
+        <f t="shared" si="6"/>
+        <v>1396.5</v>
+      </c>
+      <c r="BD10">
+        <f>C10*$J10</f>
+        <v>115.5</v>
+      </c>
+      <c r="BE10">
+        <f>D10*$J10</f>
+        <v>14</v>
+      </c>
+      <c r="BF10">
+        <f>E10*$J10</f>
+        <v>35</v>
+      </c>
+      <c r="BG10">
+        <f>F10*$J10</f>
+        <v>812</v>
+      </c>
+      <c r="BH10">
+        <f>G10*$J10</f>
+        <v>339.5</v>
+      </c>
+      <c r="BI10">
+        <f>H10*$J10</f>
+        <v>80.5</v>
+      </c>
+      <c r="BJ10">
+        <f>I10*$J10</f>
+        <v>1396.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="6">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7">
+        <v>3</v>
+      </c>
+      <c r="C11" s="7">
+        <v>244</v>
+      </c>
+      <c r="D11" s="7">
+        <v>81</v>
+      </c>
+      <c r="E11" s="7">
+        <v>153</v>
+      </c>
+      <c r="F11" s="7">
+        <v>126</v>
+      </c>
+      <c r="G11" s="7">
+        <v>175</v>
+      </c>
+      <c r="H11" s="8">
+        <v>61</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="7"/>
+        <v>840</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="8"/>
+        <v>3.5</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <f>D11*$K11</f>
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <f>E11*$K11</f>
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <f>F11*$K11</f>
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <f>G11*$K11</f>
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <f>H11*$K11</f>
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <f>I11*$K11</f>
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <f>N11*$J11</f>
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <f>C11*$L11</f>
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <f>D11*$L11</f>
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <f>E11*$L11</f>
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <f>F11*$L11</f>
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <f>G11*$L11</f>
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <f>H11*$L11</f>
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <f>I11*$L11</f>
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <f>C11*$M11</f>
+        <v>244</v>
+      </c>
+      <c r="AQ11">
+        <f>D11*$M11</f>
+        <v>81</v>
+      </c>
+      <c r="AR11">
+        <f>E11*$M11</f>
+        <v>153</v>
+      </c>
+      <c r="AS11">
+        <f>F11*$M11</f>
+        <v>126</v>
+      </c>
+      <c r="AT11">
+        <f>G11*$M11</f>
+        <v>175</v>
+      </c>
+      <c r="AU11">
+        <f>H11*$M11</f>
+        <v>61</v>
+      </c>
+      <c r="AV11">
+        <f>I11*$M11</f>
+        <v>840</v>
+      </c>
+      <c r="AW11">
+        <f t="shared" si="14"/>
+        <v>854</v>
+      </c>
+      <c r="AX11">
+        <f t="shared" si="6"/>
+        <v>283.5</v>
+      </c>
+      <c r="AY11">
+        <f t="shared" si="6"/>
+        <v>535.5</v>
+      </c>
+      <c r="AZ11">
+        <f t="shared" si="6"/>
+        <v>441</v>
+      </c>
+      <c r="BA11">
+        <f t="shared" si="6"/>
+        <v>612.5</v>
+      </c>
+      <c r="BB11">
+        <f t="shared" si="6"/>
+        <v>213.5</v>
+      </c>
+      <c r="BC11">
+        <f t="shared" si="6"/>
+        <v>2940</v>
+      </c>
+      <c r="BD11">
+        <f>C11*$J11</f>
+        <v>854</v>
+      </c>
+      <c r="BE11">
+        <f>D11*$J11</f>
+        <v>283.5</v>
+      </c>
+      <c r="BF11">
+        <f>E11*$J11</f>
+        <v>535.5</v>
+      </c>
+      <c r="BG11">
+        <f>F11*$J11</f>
+        <v>441</v>
+      </c>
+      <c r="BH11">
+        <f>G11*$J11</f>
+        <v>612.5</v>
+      </c>
+      <c r="BI11">
+        <f>H11*$J11</f>
+        <v>213.5</v>
+      </c>
+      <c r="BJ11">
+        <f>I11*$J11</f>
+        <v>2940</v>
+      </c>
+    </row>
+    <row r="12" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="U12">
+        <f>SUM(U2:U11)</f>
+        <v>973</v>
+      </c>
+      <c r="V12">
+        <f t="shared" ref="V12:AA12" si="15">SUM(V1:V11)</f>
+        <v>647.5</v>
+      </c>
+      <c r="W12">
+        <f t="shared" si="15"/>
+        <v>1158.5</v>
+      </c>
+      <c r="X12">
+        <f t="shared" si="15"/>
+        <v>507.5</v>
+      </c>
+      <c r="Y12">
+        <f t="shared" si="15"/>
+        <v>787.5</v>
+      </c>
+      <c r="Z12">
+        <f t="shared" si="15"/>
+        <v>854</v>
+      </c>
+      <c r="AA12" s="15">
+        <f t="shared" si="15"/>
+        <v>4928</v>
+      </c>
+      <c r="AI12" s="15">
+        <f>SUM(AI1:AI11)</f>
+        <v>1704.5</v>
+      </c>
+      <c r="AJ12">
+        <f t="shared" ref="AJ12:AO12" si="16">SUM(AJ1:AJ11)</f>
+        <v>1463</v>
+      </c>
+      <c r="AK12">
+        <f t="shared" si="16"/>
+        <v>1312.5</v>
+      </c>
+      <c r="AL12">
+        <f t="shared" si="16"/>
+        <v>637</v>
+      </c>
+      <c r="AM12">
+        <f t="shared" si="16"/>
+        <v>630</v>
+      </c>
+      <c r="AN12">
+        <f t="shared" si="16"/>
+        <v>1200.5</v>
+      </c>
+      <c r="AO12" s="15">
+        <f t="shared" si="16"/>
+        <v>6947.5</v>
+      </c>
+      <c r="AW12">
+        <f>SUM(AW1:AW11)</f>
+        <v>2898</v>
+      </c>
+      <c r="AX12">
+        <f t="shared" ref="AX12:BJ12" si="17">SUM(AX1:AX11)</f>
+        <v>1921.5</v>
+      </c>
+      <c r="AY12">
+        <f t="shared" si="17"/>
+        <v>1963.5</v>
+      </c>
+      <c r="AZ12">
+        <f t="shared" si="17"/>
+        <v>3206</v>
+      </c>
+      <c r="BA12">
+        <f t="shared" si="17"/>
+        <v>1988</v>
+      </c>
+      <c r="BB12">
+        <f t="shared" si="17"/>
+        <v>857.5</v>
+      </c>
+      <c r="BC12" s="15">
+        <f t="shared" si="17"/>
+        <v>12834.5</v>
+      </c>
+      <c r="BD12">
+        <f t="shared" si="17"/>
+        <v>5575.5</v>
+      </c>
+      <c r="BE12">
+        <f t="shared" si="17"/>
+        <v>4032</v>
+      </c>
+      <c r="BF12">
+        <f t="shared" si="17"/>
+        <v>4434.5</v>
+      </c>
+      <c r="BG12">
+        <f t="shared" si="17"/>
+        <v>4350.5</v>
+      </c>
+      <c r="BH12">
+        <f t="shared" si="17"/>
+        <v>3405.5</v>
+      </c>
+      <c r="BI12">
+        <f t="shared" si="17"/>
+        <v>2912</v>
+      </c>
+      <c r="BJ12" s="15">
+        <f t="shared" si="17"/>
+        <v>24710</v>
+      </c>
+    </row>
+    <row r="13" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="B13" s="19"/>
+      <c r="C13" cm="1">
+        <f t="array" ref="C13">SUMPRODUCT((C2:C11/$B$18-$BD$12)^2)</f>
+        <v>46939672.5</v>
+      </c>
+      <c r="D13" cm="1">
+        <f t="array" ref="D13">SUMPRODUCT((D2:D11/$B$18-$BD$12)^2)</f>
+        <v>71101082.5</v>
+      </c>
+      <c r="E13" cm="1">
+        <f t="array" ref="E13">SUMPRODUCT((E2:E11/$B$18-$BD$12)^2)</f>
+        <v>55509282.5</v>
+      </c>
+      <c r="F13" cm="1">
+        <f t="array" ref="F13">SUMPRODUCT((F2:F11/$B$18-$BD$12)^2)</f>
+        <v>74075872.5</v>
+      </c>
+      <c r="G13" cm="1">
+        <f t="array" ref="G13">SUMPRODUCT((G2:G11/$B$18-$BD$12)^2)</f>
+        <v>92651772.5</v>
+      </c>
+      <c r="H13" cm="1">
+        <f t="array" ref="H13">SUMPRODUCT((H2:H11/$B$18-$BD$12)^2)</f>
+        <v>126434332.5</v>
+      </c>
+      <c r="I13" cm="1">
+        <f t="array" ref="I13">SUMPRODUCT((I2:I11/$B$18-$BD$12)^2)</f>
+        <v>3870067652.5</v>
+      </c>
+      <c r="J13" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="21"/>
+      <c r="N13" cm="1">
+        <f t="array" ref="N13">SUMPRODUCT((N2:N11/$B$18-$U$12)^2)</f>
+        <v>39655210</v>
+      </c>
+      <c r="O13" cm="1">
+        <f t="array" ref="O13">SUMPRODUCT((O2:O11/$B$18-$U$12)^2)</f>
+        <v>24077865</v>
+      </c>
+      <c r="P13" cm="1">
+        <f t="array" ref="P13">SUMPRODUCT((P2:P11/$B$18-$U$12)^2)</f>
+        <v>57851605</v>
+      </c>
+      <c r="Q13" cm="1">
+        <f t="array" ref="Q13">SUMPRODUCT((Q2:Q11/$B$18-$U$12)^2)</f>
+        <v>12543265</v>
+      </c>
+      <c r="R13" cm="1">
+        <f t="array" ref="R13">SUMPRODUCT((R2:R11/$B$18-$U$12)^2)</f>
+        <v>47029465</v>
+      </c>
+      <c r="S13" cm="1">
+        <f t="array" ref="S13">SUMPRODUCT((S2:S11/$B$18-$U$12)^2)</f>
+        <v>37842700</v>
+      </c>
+      <c r="T13" cm="1">
+        <f t="array" ref="T13">SUMPRODUCT((T2:T11/$B$18-$U$12)^2)</f>
+        <v>1141978810</v>
+      </c>
+      <c r="AB13" cm="1">
+        <f t="array" ref="AB13">SUMPRODUCT((AB2:AB11/$B$18-$U$12)^2)</f>
+        <v>81369645</v>
+      </c>
+      <c r="AC13" cm="1">
+        <f t="array" ref="AC13">SUMPRODUCT((AC2:AC11/$B$18-$U$12)^2)</f>
+        <v>67575410</v>
+      </c>
+      <c r="AD13" cm="1">
+        <f t="array" ref="AD13">SUMPRODUCT((AD2:AD11/$B$18-$U$12)^2)</f>
+        <v>53154465</v>
+      </c>
+      <c r="AE13" cm="1">
+        <f t="array" ref="AE13">SUMPRODUCT((AE2:AE11/$B$18-$U$12)^2)</f>
+        <v>16036720</v>
+      </c>
+      <c r="AF13" cm="1">
+        <f t="array" ref="AF13">SUMPRODUCT((AF2:AF11/$B$18-$U$12)^2)</f>
+        <v>11018140</v>
+      </c>
+      <c r="AG13" cm="1">
+        <f t="array" ref="AG13">SUMPRODUCT((AG2:AG11/$B$18-$U$12)^2)</f>
+        <v>64609685</v>
+      </c>
+      <c r="AH13" cm="1">
+        <f t="array" ref="AH13">SUMPRODUCT((AH2:AH11/$B$18-$U$12)^2)</f>
+        <v>1492157065</v>
+      </c>
+      <c r="AP13" cm="1">
+        <f t="array" ref="AP13">SUMPRODUCT((AP2:AP11/$B$18-$U$12)^2)</f>
+        <v>156679460</v>
+      </c>
+      <c r="AQ13" cm="1">
+        <f t="array" ref="AQ13">SUMPRODUCT((AQ2:AQ11/$B$18-$U$12)^2)</f>
+        <v>68133275</v>
+      </c>
+      <c r="AR13" cm="1">
+        <f t="array" ref="AR13">SUMPRODUCT((AR2:AR11/$B$18-$U$12)^2)</f>
+        <v>70238805</v>
+      </c>
+      <c r="AS13" cm="1">
+        <f t="array" ref="AS13">SUMPRODUCT((AS2:AS11/$B$18-$U$12)^2)</f>
+        <v>163499280</v>
+      </c>
+      <c r="AT13" cm="1">
+        <f t="array" ref="AT13">SUMPRODUCT((AT2:AT11/$B$18-$U$12)^2)</f>
+        <v>65620310</v>
+      </c>
+      <c r="AU13" cm="1">
+        <f t="array" ref="AU13">SUMPRODUCT((AU2:AU11/$B$18-$U$12)^2)</f>
+        <v>9571415</v>
+      </c>
+      <c r="AV13" cm="1">
+        <f t="array" ref="AV13">SUMPRODUCT((AV2:AV11/$B$18-$U$12)^2)</f>
+        <v>3228027145</v>
+      </c>
+    </row>
+    <row r="14" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="B14" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14">
+        <f>1/($B$19*($B$19-1))*C13</f>
+        <v>521551.91666666669</v>
+      </c>
+      <c r="D14">
+        <f t="shared" ref="D14:I14" si="18">1/($B$19*($B$19-1))*D13</f>
+        <v>790012.02777777775</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="18"/>
+        <v>616769.80555555562</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="18"/>
+        <v>823065.25</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="18"/>
+        <v>1029464.1388888889</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="18"/>
+        <v>1404825.9166666667</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="18"/>
+        <v>43000751.694444448</v>
+      </c>
+      <c r="M14" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="N14">
+        <f>1/($B$19*($B$19-1))*N13</f>
+        <v>440613.44444444444</v>
+      </c>
+      <c r="O14">
+        <f t="shared" ref="O14:T14" si="19">1/($B$19*($B$19-1))*O13</f>
+        <v>267531.83333333337</v>
+      </c>
+      <c r="P14">
+        <f t="shared" si="19"/>
+        <v>642795.61111111112</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="19"/>
+        <v>139369.61111111112</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="19"/>
+        <v>522549.61111111112</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="19"/>
+        <v>420474.44444444444</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="19"/>
+        <v>12688653.444444444</v>
+      </c>
+      <c r="AB14">
+        <f>1/($B$19*($B$19-1))*AB13</f>
+        <v>904107.16666666674</v>
+      </c>
+      <c r="AC14">
+        <f t="shared" ref="AC14" si="20">1/($B$19*($B$19-1))*AC13</f>
+        <v>750837.88888888888</v>
+      </c>
+      <c r="AD14">
+        <f t="shared" ref="AD14" si="21">1/($B$19*($B$19-1))*AD13</f>
+        <v>590605.16666666674</v>
+      </c>
+      <c r="AE14">
+        <f t="shared" ref="AE14" si="22">1/($B$19*($B$19-1))*AE13</f>
+        <v>178185.77777777778</v>
+      </c>
+      <c r="AF14">
+        <f t="shared" ref="AF14" si="23">1/($B$19*($B$19-1))*AF13</f>
+        <v>122423.77777777778</v>
+      </c>
+      <c r="AG14">
+        <f t="shared" ref="AG14" si="24">1/($B$19*($B$19-1))*AG13</f>
+        <v>717885.38888888888</v>
+      </c>
+      <c r="AH14">
+        <f t="shared" ref="AH14" si="25">1/($B$19*($B$19-1))*AH13</f>
+        <v>16579522.944444446</v>
+      </c>
+      <c r="AP14">
+        <f>1/($B$19*($B$19-1))*AP13</f>
+        <v>1740882.888888889</v>
+      </c>
+      <c r="AQ14">
+        <f t="shared" ref="AQ14" si="26">1/($B$19*($B$19-1))*AQ13</f>
+        <v>757036.38888888888</v>
+      </c>
+      <c r="AR14">
+        <f t="shared" ref="AR14" si="27">1/($B$19*($B$19-1))*AR13</f>
+        <v>780431.16666666674</v>
+      </c>
+      <c r="AS14">
+        <f t="shared" ref="AS14" si="28">1/($B$19*($B$19-1))*AS13</f>
+        <v>1816658.6666666667</v>
+      </c>
+      <c r="AT14">
+        <f t="shared" ref="AT14" si="29">1/($B$19*($B$19-1))*AT13</f>
+        <v>729114.55555555562</v>
+      </c>
+      <c r="AU14">
+        <f t="shared" ref="AU14" si="30">1/($B$19*($B$19-1))*AU13</f>
+        <v>106349.05555555556</v>
+      </c>
+      <c r="AV14">
+        <f t="shared" ref="AV14" si="31">1/($B$19*($B$19-1))*AV13</f>
+        <v>35866968.277777776</v>
+      </c>
+    </row>
+    <row r="15" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="B15" s="19"/>
+      <c r="L15" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15" s="15">
+        <f>(35^2)/10*(1-(10/35))</f>
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:62" x14ac:dyDescent="0.35">
+      <c r="B16" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="16">
+        <f>SQRT(C14)/BD12</f>
+        <v>0.12952838562001365</v>
+      </c>
+      <c r="D16" s="16">
+        <f>SQRT(D14)/BE12</f>
+        <v>0.22044300790164478</v>
+      </c>
+      <c r="E16" s="16">
+        <f>SQRT(E14)/BF12</f>
+        <v>0.17709931970771733</v>
+      </c>
+      <c r="F16" s="16">
+        <f>SQRT(F14)/BG12</f>
+        <v>0.20853452160690281</v>
+      </c>
+      <c r="G16" s="16">
+        <f>SQRT(G14)/BH12</f>
+        <v>0.29793719640072686</v>
+      </c>
+      <c r="H16" s="16">
+        <f>SQRT(H14)/BI12</f>
+        <v>0.40702387507420751</v>
+      </c>
+      <c r="I16" s="16">
+        <f>SQRT(I14)/BJ12</f>
+        <v>0.26537822097189662</v>
+      </c>
+      <c r="M16" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="N16" s="16">
+        <f>SQRT(N14)/U12</f>
+        <v>0.68220678125644085</v>
+      </c>
+      <c r="O16" s="16">
+        <f t="shared" ref="O16:T16" si="32">SQRT(O14)/V12</f>
+        <v>0.79881821647694529</v>
+      </c>
+      <c r="P16" s="16">
+        <f t="shared" si="32"/>
+        <v>0.69205468539808956</v>
+      </c>
+      <c r="Q16" s="16">
+        <f t="shared" si="32"/>
+        <v>0.73561063186819975</v>
+      </c>
+      <c r="R16" s="16">
+        <f t="shared" si="32"/>
+        <v>0.91793768971253575</v>
+      </c>
+      <c r="S16" s="16">
+        <f t="shared" si="32"/>
+        <v>0.75929743367909708</v>
+      </c>
+      <c r="T16" s="16">
+        <f t="shared" si="32"/>
+        <v>0.72283149764055676</v>
+      </c>
+      <c r="AB16" s="16">
+        <f>SQRT(AB14)/AI12</f>
+        <v>0.55784423640049385</v>
+      </c>
+      <c r="AC16" s="16">
+        <f t="shared" ref="AC16:AH16" si="33">SQRT(AC14)/AJ12</f>
+        <v>0.59228231314034474</v>
+      </c>
+      <c r="AD16" s="16">
+        <f t="shared" si="33"/>
+        <v>0.58553021239696046</v>
+      </c>
+      <c r="AE16" s="16">
+        <f t="shared" si="33"/>
+        <v>0.66266965864879757</v>
+      </c>
+      <c r="AF16" s="16">
+        <f t="shared" si="33"/>
+        <v>0.55538268915486944</v>
+      </c>
+      <c r="AG16" s="16">
+        <f t="shared" si="33"/>
+        <v>0.70577357320602552</v>
+      </c>
+      <c r="AH16" s="16">
+        <f t="shared" si="33"/>
+        <v>0.58608075339892041</v>
+      </c>
+      <c r="AP16" s="16">
+        <f>SQRT(AP14)/AW12</f>
+        <v>0.45528820274524928</v>
+      </c>
+      <c r="AQ16" s="16">
+        <f t="shared" ref="AQ16:AU16" si="34">SQRT(AQ14)/AX12</f>
+        <v>0.45281206395426382</v>
+      </c>
+      <c r="AR16" s="16">
+        <f t="shared" si="34"/>
+        <v>0.44992113723764243</v>
+      </c>
+      <c r="AS16" s="16">
+        <f t="shared" si="34"/>
+        <v>0.42041010820053454</v>
+      </c>
+      <c r="AT16" s="16">
+        <f t="shared" si="34"/>
+        <v>0.429518133874496</v>
+      </c>
+      <c r="AU16" s="16">
+        <f t="shared" si="34"/>
+        <v>0.38030557335138415</v>
+      </c>
+      <c r="AV16" s="16">
+        <f>SQRT(AV14)/BC12</f>
+        <v>0.4666254051663713</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="18">
+        <f>1/35</f>
+        <v>2.8571428571428571E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="J13:M13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{143030CD-14A3-469B-BEF8-66DF235BC03B}">
   <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -7366,7 +10595,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F14D51-A9CF-426A-ABB5-19C0E1B98BBB}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -7403,7 +10632,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26724C6A-726E-4F3E-ACED-21AE035328E5}">
   <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/data/EjemploDominios.xlsx
+++ b/data/EjemploDominios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giova\Documents\GB\MisCursos\Muestreo2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE288466-B0ED-4787-B29C-0C44D0454C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{309B51FB-4D5E-45FE-BDE0-D9BBB6E64168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{42CC5FC2-8CC7-43C2-B7FE-203DEB835DFD}"/>
   </bookViews>
@@ -453,10 +453,10 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3841,7 +3841,7 @@
         <v>0.10947146621487054</v>
       </c>
       <c r="D16" s="16">
-        <f t="shared" ref="D16:I16" si="91">SQRT(D14)/BE12</f>
+        <f t="shared" ref="D16:H16" si="91">SQRT(D14)/BE12</f>
         <v>0.15192172886539346</v>
       </c>
       <c r="E16" s="16">
@@ -7136,15 +7136,17 @@
   <cols>
     <col min="1" max="1" width="4.7265625" customWidth="1"/>
     <col min="2" max="2" width="8.453125" customWidth="1"/>
-    <col min="3" max="8" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.08984375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="4.7265625" customWidth="1"/>
-    <col min="11" max="11" width="3.08984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.1796875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="4.36328125" customWidth="1"/>
     <col min="13" max="13" width="6.26953125" customWidth="1"/>
-    <col min="14" max="14" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="19" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.08984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="8.90625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7243,31 +7245,31 @@
         <v>Total*D1*Fex</v>
       </c>
       <c r="AB1" s="12" t="str">
-        <f>C1&amp;"*D2"</f>
+        <f t="shared" ref="AB1:AH1" si="2">C1&amp;"*D2"</f>
         <v>P2*D2</v>
       </c>
       <c r="AC1" s="12" t="str">
-        <f>D1&amp;"*D2"</f>
+        <f t="shared" si="2"/>
         <v>P3*D2</v>
       </c>
       <c r="AD1" s="12" t="str">
-        <f>E1&amp;"*D2"</f>
+        <f t="shared" si="2"/>
         <v>P4*D2</v>
       </c>
       <c r="AE1" s="12" t="str">
-        <f>F1&amp;"*D2"</f>
+        <f t="shared" si="2"/>
         <v>P5*D2</v>
       </c>
       <c r="AF1" s="12" t="str">
-        <f>G1&amp;"*D2"</f>
+        <f t="shared" si="2"/>
         <v>P6*D2</v>
       </c>
       <c r="AG1" s="12" t="str">
-        <f>H1&amp;"*D2"</f>
+        <f t="shared" si="2"/>
         <v>P7*D2</v>
       </c>
       <c r="AH1" s="12" t="str">
-        <f>I1&amp;"*D2"</f>
+        <f t="shared" si="2"/>
         <v>Total*D2</v>
       </c>
       <c r="AI1" s="13" t="str">
@@ -7275,55 +7277,55 @@
         <v>P2*D2*Fex</v>
       </c>
       <c r="AJ1" s="13" t="str">
-        <f t="shared" ref="AJ1:AO1" si="2">AC1&amp;"*Fex"</f>
+        <f t="shared" ref="AJ1:AO1" si="3">AC1&amp;"*Fex"</f>
         <v>P3*D2*Fex</v>
       </c>
       <c r="AK1" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>P4*D2*Fex</v>
       </c>
       <c r="AL1" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>P5*D2*Fex</v>
       </c>
       <c r="AM1" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>P6*D2*Fex</v>
       </c>
       <c r="AN1" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>P7*D2*Fex</v>
       </c>
       <c r="AO1" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Total*D2*Fex</v>
       </c>
       <c r="AP1" s="14" t="str">
-        <f>C1&amp;"*D3"</f>
+        <f t="shared" ref="AP1:AV1" si="4">C1&amp;"*D3"</f>
         <v>P2*D3</v>
       </c>
       <c r="AQ1" s="14" t="str">
-        <f>D1&amp;"*D3"</f>
+        <f t="shared" si="4"/>
         <v>P3*D3</v>
       </c>
       <c r="AR1" s="14" t="str">
-        <f>E1&amp;"*D3"</f>
+        <f t="shared" si="4"/>
         <v>P4*D3</v>
       </c>
       <c r="AS1" s="14" t="str">
-        <f>F1&amp;"*D3"</f>
+        <f t="shared" si="4"/>
         <v>P5*D3</v>
       </c>
       <c r="AT1" s="14" t="str">
-        <f>G1&amp;"*D3"</f>
+        <f t="shared" si="4"/>
         <v>P6*D3</v>
       </c>
       <c r="AU1" s="14" t="str">
-        <f>H1&amp;"*D3"</f>
+        <f t="shared" si="4"/>
         <v>P7*D3</v>
       </c>
       <c r="AV1" s="14" t="str">
-        <f>I1&amp;"*D3"</f>
+        <f t="shared" si="4"/>
         <v>Total*D3</v>
       </c>
       <c r="AW1" s="13" t="str">
@@ -7331,55 +7333,55 @@
         <v>P2*D3*Fex</v>
       </c>
       <c r="AX1" s="13" t="str">
-        <f t="shared" ref="AX1:BC1" si="3">AQ1&amp;"*Fex"</f>
+        <f t="shared" ref="AX1:BC1" si="5">AQ1&amp;"*Fex"</f>
         <v>P3*D3*Fex</v>
       </c>
       <c r="AY1" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>P4*D3*Fex</v>
       </c>
       <c r="AZ1" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>P5*D3*Fex</v>
       </c>
       <c r="BA1" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>P6*D3*Fex</v>
       </c>
       <c r="BB1" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>P7*D3*Fex</v>
       </c>
       <c r="BC1" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Total*D3*Fex</v>
       </c>
       <c r="BD1" s="17" t="str">
-        <f>C1&amp;"*Fex"</f>
+        <f t="shared" ref="BD1:BJ1" si="6">C1&amp;"*Fex"</f>
         <v>P2*Fex</v>
       </c>
       <c r="BE1" s="17" t="str">
-        <f>D1&amp;"*Fex"</f>
+        <f t="shared" si="6"/>
         <v>P3*Fex</v>
       </c>
       <c r="BF1" s="17" t="str">
-        <f>E1&amp;"*Fex"</f>
+        <f t="shared" si="6"/>
         <v>P4*Fex</v>
       </c>
       <c r="BG1" s="17" t="str">
-        <f>F1&amp;"*Fex"</f>
+        <f t="shared" si="6"/>
         <v>P5*Fex</v>
       </c>
       <c r="BH1" s="17" t="str">
-        <f>G1&amp;"*Fex"</f>
+        <f t="shared" si="6"/>
         <v>P6*Fex</v>
       </c>
       <c r="BI1" s="17" t="str">
-        <f>H1&amp;"*Fex"</f>
+        <f t="shared" si="6"/>
         <v>P7*Fex</v>
       </c>
       <c r="BJ1" s="17" t="str">
-        <f>I1&amp;"*Fex"</f>
+        <f t="shared" si="6"/>
         <v>Total*Fex</v>
       </c>
     </row>
@@ -7453,63 +7455,63 @@
         <v>0</v>
       </c>
       <c r="T2">
-        <f>I2*$K2</f>
+        <f t="shared" ref="T2:T11" si="7">I2*$K2</f>
         <v>0</v>
       </c>
       <c r="U2">
-        <f>N2*$J2</f>
+        <f t="shared" ref="U2:U11" si="8">N2*$J2</f>
         <v>0</v>
       </c>
       <c r="V2">
-        <f t="shared" ref="V2:AA11" si="4">O2*$J2</f>
+        <f t="shared" ref="V2:AA11" si="9">O2*$J2</f>
         <v>0</v>
       </c>
       <c r="W2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="X2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Y2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AA2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AB2">
-        <f>C2*$L2</f>
+        <f t="shared" ref="AB2:AB11" si="10">C2*$L2</f>
         <v>224</v>
       </c>
       <c r="AC2">
-        <f>D2*$L2</f>
+        <f t="shared" ref="AC2:AC11" si="11">D2*$L2</f>
         <v>68</v>
       </c>
       <c r="AD2">
-        <f>E2*$L2</f>
+        <f t="shared" ref="AD2:AD11" si="12">E2*$L2</f>
         <v>187</v>
       </c>
       <c r="AE2">
-        <f>F2*$L2</f>
+        <f t="shared" ref="AE2:AE11" si="13">F2*$L2</f>
         <v>36</v>
       </c>
       <c r="AF2">
-        <f>G2*$L2</f>
+        <f t="shared" ref="AF2:AF11" si="14">G2*$L2</f>
         <v>64</v>
       </c>
       <c r="AG2">
-        <f>H2*$L2</f>
+        <f t="shared" ref="AG2:AG11" si="15">H2*$L2</f>
         <v>36</v>
       </c>
       <c r="AH2">
-        <f>I2*$L2</f>
+        <f t="shared" ref="AH2:AH11" si="16">I2*$L2</f>
         <v>615</v>
       </c>
       <c r="AI2">
@@ -7517,55 +7519,55 @@
         <v>784</v>
       </c>
       <c r="AJ2">
-        <f t="shared" ref="AJ2:AO11" si="5">AC2*$J2</f>
+        <f t="shared" ref="AJ2:AO11" si="17">AC2*$J2</f>
         <v>238</v>
       </c>
       <c r="AK2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>654.5</v>
       </c>
       <c r="AL2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>126</v>
       </c>
       <c r="AM2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>224</v>
       </c>
       <c r="AN2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>126</v>
       </c>
       <c r="AO2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>2152.5</v>
       </c>
       <c r="AP2">
-        <f>C2*$M2</f>
+        <f t="shared" ref="AP2:AP11" si="18">C2*$M2</f>
         <v>0</v>
       </c>
       <c r="AQ2">
-        <f>D2*$M2</f>
+        <f t="shared" ref="AQ2:AQ11" si="19">D2*$M2</f>
         <v>0</v>
       </c>
       <c r="AR2">
-        <f>E2*$M2</f>
+        <f t="shared" ref="AR2:AR11" si="20">E2*$M2</f>
         <v>0</v>
       </c>
       <c r="AS2">
-        <f>F2*$M2</f>
+        <f t="shared" ref="AS2:AS11" si="21">F2*$M2</f>
         <v>0</v>
       </c>
       <c r="AT2">
-        <f>G2*$M2</f>
+        <f t="shared" ref="AT2:AT11" si="22">G2*$M2</f>
         <v>0</v>
       </c>
       <c r="AU2">
-        <f>H2*$M2</f>
+        <f t="shared" ref="AU2:AU11" si="23">H2*$M2</f>
         <v>0</v>
       </c>
       <c r="AV2">
-        <f>I2*$M2</f>
+        <f t="shared" ref="AV2:AV11" si="24">I2*$M2</f>
         <v>0</v>
       </c>
       <c r="AW2">
@@ -7573,55 +7575,55 @@
         <v>0</v>
       </c>
       <c r="AX2">
-        <f t="shared" ref="AX2:BC11" si="6">AQ2*$J2</f>
+        <f t="shared" ref="AX2:BC11" si="25">AQ2*$J2</f>
         <v>0</v>
       </c>
       <c r="AY2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AZ2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BA2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BB2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BC2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BD2">
-        <f>C2*$J2</f>
+        <f t="shared" ref="BD2:BD11" si="26">C2*$J2</f>
         <v>784</v>
       </c>
       <c r="BE2">
-        <f>D2*$J2</f>
+        <f t="shared" ref="BE2:BE11" si="27">D2*$J2</f>
         <v>238</v>
       </c>
       <c r="BF2">
-        <f>E2*$J2</f>
+        <f t="shared" ref="BF2:BF11" si="28">E2*$J2</f>
         <v>654.5</v>
       </c>
       <c r="BG2">
-        <f>F2*$J2</f>
+        <f t="shared" ref="BG2:BG11" si="29">F2*$J2</f>
         <v>126</v>
       </c>
       <c r="BH2">
-        <f>G2*$J2</f>
+        <f t="shared" ref="BH2:BH11" si="30">G2*$J2</f>
         <v>224</v>
       </c>
       <c r="BI2">
-        <f>H2*$J2</f>
+        <f t="shared" ref="BI2:BI11" si="31">H2*$J2</f>
         <v>126</v>
       </c>
       <c r="BJ2">
-        <f>I2*$J2</f>
+        <f t="shared" ref="BJ2:BJ11" si="32">I2*$J2</f>
         <v>2152.5</v>
       </c>
     </row>
@@ -7651,219 +7653,219 @@
         <v>63</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I11" si="7">SUM(C3:H3)</f>
+        <f t="shared" ref="I3:I11" si="33">SUM(C3:H3)</f>
         <v>628</v>
       </c>
       <c r="J3">
-        <f t="shared" ref="J3:J11" si="8">1/($B$19*$B$18)</f>
+        <f t="shared" ref="J3:J11" si="34">1/($B$19*$B$18)</f>
         <v>3.5</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K11" si="9">IF($B3=1,1,0)</f>
+        <f t="shared" ref="K3:K11" si="35">IF($B3=1,1,0)</f>
         <v>1</v>
       </c>
       <c r="L3">
-        <f t="shared" ref="L3:L11" si="10">IF($B3=2,1,0)</f>
+        <f t="shared" ref="L3:L11" si="36">IF($B3=2,1,0)</f>
         <v>0</v>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:M11" si="11">IF($B3=3,1,0)</f>
+        <f t="shared" ref="M3:M11" si="37">IF($B3=3,1,0)</f>
         <v>0</v>
       </c>
       <c r="N3">
-        <f t="shared" ref="N3:N11" si="12">C3*$K3</f>
+        <f t="shared" ref="N3:N11" si="38">C3*$K3</f>
         <v>112</v>
       </c>
       <c r="O3">
-        <f>D3*$K3</f>
+        <f t="shared" ref="O3:O11" si="39">D3*$K3</f>
         <v>42</v>
       </c>
       <c r="P3">
-        <f>E3*$K3</f>
+        <f t="shared" ref="P3:P11" si="40">E3*$K3</f>
         <v>126</v>
       </c>
       <c r="Q3">
-        <f>F3*$K3</f>
+        <f t="shared" ref="Q3:Q11" si="41">F3*$K3</f>
         <v>78</v>
       </c>
       <c r="R3">
-        <f>G3*$K3</f>
+        <f t="shared" ref="R3:R11" si="42">G3*$K3</f>
         <v>207</v>
       </c>
       <c r="S3">
-        <f>H3*$K3</f>
+        <f t="shared" ref="S3:S11" si="43">H3*$K3</f>
         <v>63</v>
       </c>
       <c r="T3">
-        <f>I3*$K3</f>
+        <f t="shared" si="7"/>
         <v>628</v>
       </c>
       <c r="U3">
-        <f>N3*$J3</f>
+        <f t="shared" si="8"/>
         <v>392</v>
       </c>
       <c r="V3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>147</v>
       </c>
       <c r="W3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>441</v>
       </c>
       <c r="X3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>273</v>
       </c>
       <c r="Y3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>724.5</v>
       </c>
       <c r="Z3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>220.5</v>
       </c>
       <c r="AA3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>2198</v>
       </c>
       <c r="AB3">
-        <f>C3*$L3</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AC3">
-        <f>D3*$L3</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AD3">
-        <f>E3*$L3</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AE3">
-        <f>F3*$L3</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AF3">
-        <f>G3*$L3</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AG3">
-        <f>H3*$L3</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AH3">
-        <f>I3*$L3</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AI3">
-        <f t="shared" ref="AI3:AI11" si="13">AB3*$J3</f>
+        <f t="shared" ref="AI3:AI11" si="44">AB3*$J3</f>
         <v>0</v>
       </c>
       <c r="AJ3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AL3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AM3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AN3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AO3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AP3">
-        <f>C3*$M3</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AQ3">
-        <f>D3*$M3</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AR3">
-        <f>E3*$M3</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AS3">
-        <f>F3*$M3</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AT3">
-        <f>G3*$M3</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AU3">
-        <f>H3*$M3</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AV3">
-        <f>I3*$M3</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AW3">
-        <f t="shared" ref="AW3:AW11" si="14">AP3*$J3</f>
+        <f t="shared" ref="AW3:AW11" si="45">AP3*$J3</f>
         <v>0</v>
       </c>
       <c r="AX3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AZ3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BA3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BB3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BC3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BD3">
-        <f>C3*$J3</f>
+        <f t="shared" si="26"/>
         <v>392</v>
       </c>
       <c r="BE3">
-        <f>D3*$J3</f>
+        <f t="shared" si="27"/>
         <v>147</v>
       </c>
       <c r="BF3">
-        <f>E3*$J3</f>
+        <f t="shared" si="28"/>
         <v>441</v>
       </c>
       <c r="BG3">
-        <f>F3*$J3</f>
+        <f t="shared" si="29"/>
         <v>273</v>
       </c>
       <c r="BH3">
-        <f>G3*$J3</f>
+        <f t="shared" si="30"/>
         <v>724.5</v>
       </c>
       <c r="BI3">
-        <f>H3*$J3</f>
+        <f t="shared" si="31"/>
         <v>220.5</v>
       </c>
       <c r="BJ3">
-        <f>I3*$J3</f>
+        <f t="shared" si="32"/>
         <v>2198</v>
       </c>
     </row>
@@ -7893,219 +7895,219 @@
         <v>57</v>
       </c>
       <c r="I4">
+        <f t="shared" si="33"/>
+        <v>840</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="34"/>
+        <v>3.5</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="37"/>
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T4">
         <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="18"/>
+        <v>227</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="19"/>
+        <v>154</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="20"/>
+        <v>78</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="21"/>
+        <v>155</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="22"/>
+        <v>169</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="23"/>
+        <v>57</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="24"/>
         <v>840</v>
       </c>
-      <c r="J4">
-        <f t="shared" si="8"/>
-        <v>3.5</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="N4">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <f>D4*$K4</f>
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <f>E4*$K4</f>
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <f>F4*$K4</f>
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <f>G4*$K4</f>
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <f>H4*$K4</f>
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <f>I4*$K4</f>
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <f>N4*$J4</f>
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <f>C4*$L4</f>
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <f>D4*$L4</f>
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <f>E4*$L4</f>
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <f>F4*$L4</f>
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <f>G4*$L4</f>
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <f>H4*$L4</f>
-        <v>0</v>
-      </c>
-      <c r="AH4">
-        <f>I4*$L4</f>
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AK4">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AL4">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AO4">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <f>C4*$M4</f>
-        <v>227</v>
-      </c>
-      <c r="AQ4">
-        <f>D4*$M4</f>
-        <v>154</v>
-      </c>
-      <c r="AR4">
-        <f>E4*$M4</f>
-        <v>78</v>
-      </c>
-      <c r="AS4">
-        <f>F4*$M4</f>
-        <v>155</v>
-      </c>
-      <c r="AT4">
-        <f>G4*$M4</f>
-        <v>169</v>
-      </c>
-      <c r="AU4">
-        <f>H4*$M4</f>
-        <v>57</v>
-      </c>
-      <c r="AV4">
-        <f>I4*$M4</f>
-        <v>840</v>
-      </c>
       <c r="AW4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="45"/>
         <v>794.5</v>
       </c>
       <c r="AX4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>539</v>
       </c>
       <c r="AY4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>273</v>
       </c>
       <c r="AZ4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>542.5</v>
       </c>
       <c r="BA4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>591.5</v>
       </c>
       <c r="BB4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>199.5</v>
       </c>
       <c r="BC4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>2940</v>
       </c>
       <c r="BD4">
-        <f>C4*$J4</f>
+        <f t="shared" si="26"/>
         <v>794.5</v>
       </c>
       <c r="BE4">
-        <f>D4*$J4</f>
+        <f t="shared" si="27"/>
         <v>539</v>
       </c>
       <c r="BF4">
-        <f>E4*$J4</f>
+        <f t="shared" si="28"/>
         <v>273</v>
       </c>
       <c r="BG4">
-        <f>F4*$J4</f>
+        <f t="shared" si="29"/>
         <v>542.5</v>
       </c>
       <c r="BH4">
-        <f>G4*$J4</f>
+        <f t="shared" si="30"/>
         <v>591.5</v>
       </c>
       <c r="BI4">
-        <f>H4*$J4</f>
+        <f t="shared" si="31"/>
         <v>199.5</v>
       </c>
       <c r="BJ4">
-        <f>I4*$J4</f>
+        <f t="shared" si="32"/>
         <v>2940</v>
       </c>
     </row>
@@ -8135,219 +8137,219 @@
         <v>181</v>
       </c>
       <c r="I5">
+        <f t="shared" si="33"/>
+        <v>780</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="34"/>
+        <v>3.5</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="35"/>
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="38"/>
+        <v>166</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="39"/>
+        <v>143</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="40"/>
+        <v>205</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="41"/>
+        <v>67</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="42"/>
+        <v>18</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="43"/>
+        <v>181</v>
+      </c>
+      <c r="T5">
         <f t="shared" si="7"/>
         <v>780</v>
       </c>
-      <c r="J5">
+      <c r="U5">
         <f t="shared" si="8"/>
-        <v>3.5</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="L5">
+        <v>581</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="9"/>
+        <v>500.5</v>
+      </c>
+      <c r="W5">
+        <f t="shared" si="9"/>
+        <v>717.5</v>
+      </c>
+      <c r="X5">
+        <f t="shared" si="9"/>
+        <v>234.5</v>
+      </c>
+      <c r="Y5">
+        <f t="shared" si="9"/>
+        <v>63</v>
+      </c>
+      <c r="Z5">
+        <f t="shared" si="9"/>
+        <v>633.5</v>
+      </c>
+      <c r="AA5">
+        <f t="shared" si="9"/>
+        <v>2730</v>
+      </c>
+      <c r="AB5">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="M5">
+      <c r="AC5">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="N5">
-        <f t="shared" si="12"/>
-        <v>166</v>
-      </c>
-      <c r="O5">
-        <f>D5*$K5</f>
-        <v>143</v>
-      </c>
-      <c r="P5">
-        <f>E5*$K5</f>
-        <v>205</v>
-      </c>
-      <c r="Q5">
-        <f>F5*$K5</f>
-        <v>67</v>
-      </c>
-      <c r="R5">
-        <f>G5*$K5</f>
-        <v>18</v>
-      </c>
-      <c r="S5">
-        <f>H5*$K5</f>
-        <v>181</v>
-      </c>
-      <c r="T5">
-        <f>I5*$K5</f>
-        <v>780</v>
-      </c>
-      <c r="U5">
-        <f>N5*$J5</f>
+      <c r="AD5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <f t="shared" si="26"/>
         <v>581</v>
       </c>
-      <c r="V5">
-        <f t="shared" si="4"/>
+      <c r="BE5">
+        <f t="shared" si="27"/>
         <v>500.5</v>
       </c>
-      <c r="W5">
-        <f t="shared" si="4"/>
+      <c r="BF5">
+        <f t="shared" si="28"/>
         <v>717.5</v>
       </c>
-      <c r="X5">
-        <f t="shared" si="4"/>
+      <c r="BG5">
+        <f t="shared" si="29"/>
         <v>234.5</v>
       </c>
-      <c r="Y5">
-        <f t="shared" si="4"/>
+      <c r="BH5">
+        <f t="shared" si="30"/>
         <v>63</v>
       </c>
-      <c r="Z5">
-        <f t="shared" si="4"/>
+      <c r="BI5">
+        <f t="shared" si="31"/>
         <v>633.5</v>
       </c>
-      <c r="AA5">
-        <f t="shared" si="4"/>
-        <v>2730</v>
-      </c>
-      <c r="AB5">
-        <f>C5*$L5</f>
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <f>D5*$L5</f>
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <f>E5*$L5</f>
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <f>F5*$L5</f>
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <f>G5*$L5</f>
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <f>H5*$L5</f>
-        <v>0</v>
-      </c>
-      <c r="AH5">
-        <f>I5*$L5</f>
-        <v>0</v>
-      </c>
-      <c r="AI5">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AJ5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AK5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AL5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AO5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AP5">
-        <f>C5*$M5</f>
-        <v>0</v>
-      </c>
-      <c r="AQ5">
-        <f>D5*$M5</f>
-        <v>0</v>
-      </c>
-      <c r="AR5">
-        <f>E5*$M5</f>
-        <v>0</v>
-      </c>
-      <c r="AS5">
-        <f>F5*$M5</f>
-        <v>0</v>
-      </c>
-      <c r="AT5">
-        <f>G5*$M5</f>
-        <v>0</v>
-      </c>
-      <c r="AU5">
-        <f>H5*$M5</f>
-        <v>0</v>
-      </c>
-      <c r="AV5">
-        <f>I5*$M5</f>
-        <v>0</v>
-      </c>
-      <c r="AW5">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AX5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AY5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AZ5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BD5">
-        <f>C5*$J5</f>
-        <v>581</v>
-      </c>
-      <c r="BE5">
-        <f>D5*$J5</f>
-        <v>500.5</v>
-      </c>
-      <c r="BF5">
-        <f>E5*$J5</f>
-        <v>717.5</v>
-      </c>
-      <c r="BG5">
-        <f>F5*$J5</f>
-        <v>234.5</v>
-      </c>
-      <c r="BH5">
-        <f>G5*$J5</f>
-        <v>63</v>
-      </c>
-      <c r="BI5">
-        <f>H5*$J5</f>
-        <v>633.5</v>
-      </c>
       <c r="BJ5">
-        <f>I5*$J5</f>
+        <f t="shared" si="32"/>
         <v>2730</v>
       </c>
     </row>
@@ -8377,219 +8379,219 @@
         <v>72</v>
       </c>
       <c r="I6">
+        <f t="shared" si="33"/>
+        <v>792</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="34"/>
+        <v>3.5</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="37"/>
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T6">
         <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="18"/>
+        <v>134</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="19"/>
+        <v>149</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="20"/>
+        <v>162</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="21"/>
+        <v>231</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="22"/>
+        <v>44</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="23"/>
+        <v>72</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="24"/>
         <v>792</v>
       </c>
-      <c r="J6">
-        <f t="shared" si="8"/>
-        <v>3.5</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="N6">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <f>D6*$K6</f>
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <f>E6*$K6</f>
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <f>F6*$K6</f>
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <f>G6*$K6</f>
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <f>H6*$K6</f>
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <f>I6*$K6</f>
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <f>N6*$J6</f>
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Y6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Z6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <f>C6*$L6</f>
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <f>D6*$L6</f>
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <f>E6*$L6</f>
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <f>F6*$L6</f>
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <f>G6*$L6</f>
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <f>H6*$L6</f>
-        <v>0</v>
-      </c>
-      <c r="AH6">
-        <f>I6*$L6</f>
-        <v>0</v>
-      </c>
-      <c r="AI6">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AJ6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AK6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AL6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AO6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AP6">
-        <f>C6*$M6</f>
-        <v>134</v>
-      </c>
-      <c r="AQ6">
-        <f>D6*$M6</f>
-        <v>149</v>
-      </c>
-      <c r="AR6">
-        <f>E6*$M6</f>
-        <v>162</v>
-      </c>
-      <c r="AS6">
-        <f>F6*$M6</f>
-        <v>231</v>
-      </c>
-      <c r="AT6">
-        <f>G6*$M6</f>
-        <v>44</v>
-      </c>
-      <c r="AU6">
-        <f>H6*$M6</f>
-        <v>72</v>
-      </c>
-      <c r="AV6">
-        <f>I6*$M6</f>
-        <v>792</v>
-      </c>
       <c r="AW6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="45"/>
         <v>469</v>
       </c>
       <c r="AX6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>521.5</v>
       </c>
       <c r="AY6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>567</v>
       </c>
       <c r="AZ6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>808.5</v>
       </c>
       <c r="BA6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>154</v>
       </c>
       <c r="BB6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>252</v>
       </c>
       <c r="BC6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>2772</v>
       </c>
       <c r="BD6">
-        <f>C6*$J6</f>
+        <f t="shared" si="26"/>
         <v>469</v>
       </c>
       <c r="BE6">
-        <f>D6*$J6</f>
+        <f t="shared" si="27"/>
         <v>521.5</v>
       </c>
       <c r="BF6">
-        <f>E6*$J6</f>
+        <f t="shared" si="28"/>
         <v>567</v>
       </c>
       <c r="BG6">
-        <f>F6*$J6</f>
+        <f t="shared" si="29"/>
         <v>808.5</v>
       </c>
       <c r="BH6">
-        <f>G6*$J6</f>
+        <f t="shared" si="30"/>
         <v>154</v>
       </c>
       <c r="BI6">
-        <f>H6*$J6</f>
+        <f t="shared" si="31"/>
         <v>252</v>
       </c>
       <c r="BJ6">
-        <f>I6*$J6</f>
+        <f t="shared" si="32"/>
         <v>2772</v>
       </c>
     </row>
@@ -8619,219 +8621,219 @@
         <v>65</v>
       </c>
       <c r="I7">
+        <f t="shared" si="33"/>
+        <v>640</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="34"/>
+        <v>3.5</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="36"/>
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T7">
         <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <f t="shared" si="10"/>
+        <v>109</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="11"/>
+        <v>224</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="12"/>
+        <v>138</v>
+      </c>
+      <c r="AE7">
+        <f t="shared" si="13"/>
+        <v>31</v>
+      </c>
+      <c r="AF7">
+        <f t="shared" si="14"/>
+        <v>73</v>
+      </c>
+      <c r="AG7">
+        <f t="shared" si="15"/>
+        <v>65</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="16"/>
         <v>640</v>
       </c>
-      <c r="J7">
-        <f t="shared" si="8"/>
-        <v>3.5</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <f>D7*$K7</f>
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <f>E7*$K7</f>
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <f>F7*$K7</f>
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <f>G7*$K7</f>
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <f>H7*$K7</f>
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <f>I7*$K7</f>
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <f>N7*$J7</f>
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <f>C7*$L7</f>
-        <v>109</v>
-      </c>
-      <c r="AC7">
-        <f>D7*$L7</f>
-        <v>224</v>
-      </c>
-      <c r="AD7">
-        <f>E7*$L7</f>
-        <v>138</v>
-      </c>
-      <c r="AE7">
-        <f>F7*$L7</f>
-        <v>31</v>
-      </c>
-      <c r="AF7">
-        <f>G7*$L7</f>
-        <v>73</v>
-      </c>
-      <c r="AG7">
-        <f>H7*$L7</f>
-        <v>65</v>
-      </c>
-      <c r="AH7">
-        <f>I7*$L7</f>
-        <v>640</v>
-      </c>
       <c r="AI7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="44"/>
         <v>381.5</v>
       </c>
       <c r="AJ7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>784</v>
       </c>
       <c r="AK7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>483</v>
       </c>
       <c r="AL7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>108.5</v>
       </c>
       <c r="AM7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>255.5</v>
       </c>
       <c r="AN7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>227.5</v>
       </c>
       <c r="AO7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>2240</v>
       </c>
       <c r="AP7">
-        <f>C7*$M7</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AQ7">
-        <f>D7*$M7</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AR7">
-        <f>E7*$M7</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AS7">
-        <f>F7*$M7</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AT7">
-        <f>G7*$M7</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AU7">
-        <f>H7*$M7</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AV7">
-        <f>I7*$M7</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AW7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AX7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AZ7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BA7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BB7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BC7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BD7">
-        <f>C7*$J7</f>
+        <f t="shared" si="26"/>
         <v>381.5</v>
       </c>
       <c r="BE7">
-        <f>D7*$J7</f>
+        <f t="shared" si="27"/>
         <v>784</v>
       </c>
       <c r="BF7">
-        <f>E7*$J7</f>
+        <f t="shared" si="28"/>
         <v>483</v>
       </c>
       <c r="BG7">
-        <f>F7*$J7</f>
+        <f t="shared" si="29"/>
         <v>108.5</v>
       </c>
       <c r="BH7">
-        <f>G7*$J7</f>
+        <f t="shared" si="30"/>
         <v>255.5</v>
       </c>
       <c r="BI7">
-        <f>H7*$J7</f>
+        <f t="shared" si="31"/>
         <v>227.5</v>
       </c>
       <c r="BJ7">
-        <f>I7*$J7</f>
+        <f t="shared" si="32"/>
         <v>2240</v>
       </c>
     </row>
@@ -8861,219 +8863,219 @@
         <v>242</v>
       </c>
       <c r="I8">
+        <f t="shared" si="33"/>
+        <v>730</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="34"/>
+        <v>3.5</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="36"/>
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T8">
         <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <f t="shared" si="10"/>
+        <v>154</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="11"/>
+        <v>126</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="12"/>
+        <v>50</v>
+      </c>
+      <c r="AE8">
+        <f t="shared" si="13"/>
+        <v>115</v>
+      </c>
+      <c r="AF8">
+        <f t="shared" si="14"/>
+        <v>43</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="15"/>
+        <v>242</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="16"/>
         <v>730</v>
       </c>
-      <c r="J8">
-        <f t="shared" si="8"/>
-        <v>3.5</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-      <c r="M8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <f>D8*$K8</f>
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <f>E8*$K8</f>
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <f>F8*$K8</f>
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <f>G8*$K8</f>
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <f>H8*$K8</f>
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <f>I8*$K8</f>
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <f>N8*$J8</f>
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Z8">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AA8">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <f>C8*$L8</f>
-        <v>154</v>
-      </c>
-      <c r="AC8">
-        <f>D8*$L8</f>
-        <v>126</v>
-      </c>
-      <c r="AD8">
-        <f>E8*$L8</f>
-        <v>50</v>
-      </c>
-      <c r="AE8">
-        <f>F8*$L8</f>
-        <v>115</v>
-      </c>
-      <c r="AF8">
-        <f>G8*$L8</f>
-        <v>43</v>
-      </c>
-      <c r="AG8">
-        <f>H8*$L8</f>
-        <v>242</v>
-      </c>
-      <c r="AH8">
-        <f>I8*$L8</f>
-        <v>730</v>
-      </c>
       <c r="AI8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="44"/>
         <v>539</v>
       </c>
       <c r="AJ8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>441</v>
       </c>
       <c r="AK8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>175</v>
       </c>
       <c r="AL8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>402.5</v>
       </c>
       <c r="AM8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>150.5</v>
       </c>
       <c r="AN8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>847</v>
       </c>
       <c r="AO8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="17"/>
         <v>2555</v>
       </c>
       <c r="AP8">
-        <f>C8*$M8</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AQ8">
-        <f>D8*$M8</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AR8">
-        <f>E8*$M8</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AS8">
-        <f>F8*$M8</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AT8">
-        <f>G8*$M8</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AU8">
-        <f>H8*$M8</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AV8">
-        <f>I8*$M8</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AW8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AX8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AY8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AZ8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BA8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BB8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BC8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BD8">
-        <f>C8*$J8</f>
+        <f t="shared" si="26"/>
         <v>539</v>
       </c>
       <c r="BE8">
-        <f>D8*$J8</f>
+        <f t="shared" si="27"/>
         <v>441</v>
       </c>
       <c r="BF8">
-        <f>E8*$J8</f>
+        <f t="shared" si="28"/>
         <v>175</v>
       </c>
       <c r="BG8">
-        <f>F8*$J8</f>
+        <f t="shared" si="29"/>
         <v>402.5</v>
       </c>
       <c r="BH8">
-        <f>G8*$J8</f>
+        <f t="shared" si="30"/>
         <v>150.5</v>
       </c>
       <c r="BI8">
-        <f>H8*$J8</f>
+        <f t="shared" si="31"/>
         <v>847</v>
       </c>
       <c r="BJ8">
-        <f>I8*$J8</f>
+        <f t="shared" si="32"/>
         <v>2555</v>
       </c>
     </row>
@@ -9103,219 +9105,219 @@
         <v>32</v>
       </c>
       <c r="I9">
+        <f t="shared" si="33"/>
+        <v>796</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="34"/>
+        <v>3.5</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="37"/>
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T9">
         <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <f t="shared" si="18"/>
+        <v>190</v>
+      </c>
+      <c r="AQ9">
+        <f t="shared" si="19"/>
+        <v>161</v>
+      </c>
+      <c r="AR9">
+        <f t="shared" si="20"/>
+        <v>158</v>
+      </c>
+      <c r="AS9">
+        <f t="shared" si="21"/>
+        <v>172</v>
+      </c>
+      <c r="AT9">
+        <f t="shared" si="22"/>
+        <v>83</v>
+      </c>
+      <c r="AU9">
+        <f t="shared" si="23"/>
+        <v>32</v>
+      </c>
+      <c r="AV9">
+        <f t="shared" si="24"/>
         <v>796</v>
       </c>
-      <c r="J9">
-        <f t="shared" si="8"/>
-        <v>3.5</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="N9">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <f>D9*$K9</f>
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <f>E9*$K9</f>
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <f>F9*$K9</f>
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <f>G9*$K9</f>
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <f>H9*$K9</f>
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <f>I9*$K9</f>
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <f>N9*$J9</f>
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Y9">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Z9">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AA9">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <f>C9*$L9</f>
-        <v>0</v>
-      </c>
-      <c r="AC9">
-        <f>D9*$L9</f>
-        <v>0</v>
-      </c>
-      <c r="AD9">
-        <f>E9*$L9</f>
-        <v>0</v>
-      </c>
-      <c r="AE9">
-        <f>F9*$L9</f>
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <f>G9*$L9</f>
-        <v>0</v>
-      </c>
-      <c r="AG9">
-        <f>H9*$L9</f>
-        <v>0</v>
-      </c>
-      <c r="AH9">
-        <f>I9*$L9</f>
-        <v>0</v>
-      </c>
-      <c r="AI9">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AJ9">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AK9">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AL9">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AN9">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AO9">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AP9">
-        <f>C9*$M9</f>
-        <v>190</v>
-      </c>
-      <c r="AQ9">
-        <f>D9*$M9</f>
-        <v>161</v>
-      </c>
-      <c r="AR9">
-        <f>E9*$M9</f>
-        <v>158</v>
-      </c>
-      <c r="AS9">
-        <f>F9*$M9</f>
-        <v>172</v>
-      </c>
-      <c r="AT9">
-        <f>G9*$M9</f>
-        <v>83</v>
-      </c>
-      <c r="AU9">
-        <f>H9*$M9</f>
-        <v>32</v>
-      </c>
-      <c r="AV9">
-        <f>I9*$M9</f>
-        <v>796</v>
-      </c>
       <c r="AW9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="45"/>
         <v>665</v>
       </c>
       <c r="AX9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>563.5</v>
       </c>
       <c r="AY9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>553</v>
       </c>
       <c r="AZ9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>602</v>
       </c>
       <c r="BA9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>290.5</v>
       </c>
       <c r="BB9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>112</v>
       </c>
       <c r="BC9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>2786</v>
       </c>
       <c r="BD9">
-        <f>C9*$J9</f>
+        <f t="shared" si="26"/>
         <v>665</v>
       </c>
       <c r="BE9">
-        <f>D9*$J9</f>
+        <f t="shared" si="27"/>
         <v>563.5</v>
       </c>
       <c r="BF9">
-        <f>E9*$J9</f>
+        <f t="shared" si="28"/>
         <v>553</v>
       </c>
       <c r="BG9">
-        <f>F9*$J9</f>
+        <f t="shared" si="29"/>
         <v>602</v>
       </c>
       <c r="BH9">
-        <f>G9*$J9</f>
+        <f t="shared" si="30"/>
         <v>290.5</v>
       </c>
       <c r="BI9">
-        <f>H9*$J9</f>
+        <f t="shared" si="31"/>
         <v>112</v>
       </c>
       <c r="BJ9">
-        <f>I9*$J9</f>
+        <f t="shared" si="32"/>
         <v>2786</v>
       </c>
     </row>
@@ -9345,219 +9347,219 @@
         <v>23</v>
       </c>
       <c r="I10">
+        <f t="shared" si="33"/>
+        <v>399</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="34"/>
+        <v>3.5</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="37"/>
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T10">
         <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <f t="shared" si="18"/>
+        <v>33</v>
+      </c>
+      <c r="AQ10">
+        <f t="shared" si="19"/>
+        <v>4</v>
+      </c>
+      <c r="AR10">
+        <f t="shared" si="20"/>
+        <v>10</v>
+      </c>
+      <c r="AS10">
+        <f t="shared" si="21"/>
+        <v>232</v>
+      </c>
+      <c r="AT10">
+        <f t="shared" si="22"/>
+        <v>97</v>
+      </c>
+      <c r="AU10">
+        <f t="shared" si="23"/>
+        <v>23</v>
+      </c>
+      <c r="AV10">
+        <f t="shared" si="24"/>
         <v>399</v>
       </c>
-      <c r="J10">
-        <f t="shared" si="8"/>
-        <v>3.5</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="N10">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <f>D10*$K10</f>
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <f>E10*$K10</f>
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <f>F10*$K10</f>
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <f>G10*$K10</f>
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <f>H10*$K10</f>
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <f>I10*$K10</f>
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <f>N10*$J10</f>
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Y10">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Z10">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AA10">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <f>C10*$L10</f>
-        <v>0</v>
-      </c>
-      <c r="AC10">
-        <f>D10*$L10</f>
-        <v>0</v>
-      </c>
-      <c r="AD10">
-        <f>E10*$L10</f>
-        <v>0</v>
-      </c>
-      <c r="AE10">
-        <f>F10*$L10</f>
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <f>G10*$L10</f>
-        <v>0</v>
-      </c>
-      <c r="AG10">
-        <f>H10*$L10</f>
-        <v>0</v>
-      </c>
-      <c r="AH10">
-        <f>I10*$L10</f>
-        <v>0</v>
-      </c>
-      <c r="AI10">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AJ10">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AK10">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AL10">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AM10">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AN10">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AO10">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AP10">
-        <f>C10*$M10</f>
-        <v>33</v>
-      </c>
-      <c r="AQ10">
-        <f>D10*$M10</f>
-        <v>4</v>
-      </c>
-      <c r="AR10">
-        <f>E10*$M10</f>
-        <v>10</v>
-      </c>
-      <c r="AS10">
-        <f>F10*$M10</f>
-        <v>232</v>
-      </c>
-      <c r="AT10">
-        <f>G10*$M10</f>
-        <v>97</v>
-      </c>
-      <c r="AU10">
-        <f>H10*$M10</f>
-        <v>23</v>
-      </c>
-      <c r="AV10">
-        <f>I10*$M10</f>
-        <v>399</v>
-      </c>
       <c r="AW10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="45"/>
         <v>115.5</v>
       </c>
       <c r="AX10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>14</v>
       </c>
       <c r="AY10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>35</v>
       </c>
       <c r="AZ10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>812</v>
       </c>
       <c r="BA10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>339.5</v>
       </c>
       <c r="BB10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>80.5</v>
       </c>
       <c r="BC10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>1396.5</v>
       </c>
       <c r="BD10">
-        <f>C10*$J10</f>
+        <f t="shared" si="26"/>
         <v>115.5</v>
       </c>
       <c r="BE10">
-        <f>D10*$J10</f>
+        <f t="shared" si="27"/>
         <v>14</v>
       </c>
       <c r="BF10">
-        <f>E10*$J10</f>
+        <f t="shared" si="28"/>
         <v>35</v>
       </c>
       <c r="BG10">
-        <f>F10*$J10</f>
+        <f t="shared" si="29"/>
         <v>812</v>
       </c>
       <c r="BH10">
-        <f>G10*$J10</f>
+        <f t="shared" si="30"/>
         <v>339.5</v>
       </c>
       <c r="BI10">
-        <f>H10*$J10</f>
+        <f t="shared" si="31"/>
         <v>80.5</v>
       </c>
       <c r="BJ10">
-        <f>I10*$J10</f>
+        <f t="shared" si="32"/>
         <v>1396.5</v>
       </c>
     </row>
@@ -9587,219 +9589,219 @@
         <v>61</v>
       </c>
       <c r="I11">
+        <f t="shared" si="33"/>
+        <v>840</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="34"/>
+        <v>3.5</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="37"/>
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="T11">
         <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <f t="shared" si="18"/>
+        <v>244</v>
+      </c>
+      <c r="AQ11">
+        <f t="shared" si="19"/>
+        <v>81</v>
+      </c>
+      <c r="AR11">
+        <f t="shared" si="20"/>
+        <v>153</v>
+      </c>
+      <c r="AS11">
+        <f t="shared" si="21"/>
+        <v>126</v>
+      </c>
+      <c r="AT11">
+        <f t="shared" si="22"/>
+        <v>175</v>
+      </c>
+      <c r="AU11">
+        <f t="shared" si="23"/>
+        <v>61</v>
+      </c>
+      <c r="AV11">
+        <f t="shared" si="24"/>
         <v>840</v>
       </c>
-      <c r="J11">
-        <f t="shared" si="8"/>
-        <v>3.5</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="N11">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <f>D11*$K11</f>
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <f>E11*$K11</f>
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <f>F11*$K11</f>
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <f>G11*$K11</f>
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <f>H11*$K11</f>
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <f>I11*$K11</f>
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <f>N11*$J11</f>
-        <v>0</v>
-      </c>
-      <c r="V11">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="X11">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Y11">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Z11">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AA11">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <f>C11*$L11</f>
-        <v>0</v>
-      </c>
-      <c r="AC11">
-        <f>D11*$L11</f>
-        <v>0</v>
-      </c>
-      <c r="AD11">
-        <f>E11*$L11</f>
-        <v>0</v>
-      </c>
-      <c r="AE11">
-        <f>F11*$L11</f>
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <f>G11*$L11</f>
-        <v>0</v>
-      </c>
-      <c r="AG11">
-        <f>H11*$L11</f>
-        <v>0</v>
-      </c>
-      <c r="AH11">
-        <f>I11*$L11</f>
-        <v>0</v>
-      </c>
-      <c r="AI11">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AJ11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AK11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AL11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AN11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AO11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AP11">
-        <f>C11*$M11</f>
-        <v>244</v>
-      </c>
-      <c r="AQ11">
-        <f>D11*$M11</f>
-        <v>81</v>
-      </c>
-      <c r="AR11">
-        <f>E11*$M11</f>
-        <v>153</v>
-      </c>
-      <c r="AS11">
-        <f>F11*$M11</f>
-        <v>126</v>
-      </c>
-      <c r="AT11">
-        <f>G11*$M11</f>
-        <v>175</v>
-      </c>
-      <c r="AU11">
-        <f>H11*$M11</f>
-        <v>61</v>
-      </c>
-      <c r="AV11">
-        <f>I11*$M11</f>
-        <v>840</v>
-      </c>
       <c r="AW11">
-        <f t="shared" si="14"/>
+        <f t="shared" si="45"/>
         <v>854</v>
       </c>
       <c r="AX11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>283.5</v>
       </c>
       <c r="AY11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>535.5</v>
       </c>
       <c r="AZ11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>441</v>
       </c>
       <c r="BA11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>612.5</v>
       </c>
       <c r="BB11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>213.5</v>
       </c>
       <c r="BC11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="25"/>
         <v>2940</v>
       </c>
       <c r="BD11">
-        <f>C11*$J11</f>
+        <f t="shared" si="26"/>
         <v>854</v>
       </c>
       <c r="BE11">
-        <f>D11*$J11</f>
+        <f t="shared" si="27"/>
         <v>283.5</v>
       </c>
       <c r="BF11">
-        <f>E11*$J11</f>
+        <f t="shared" si="28"/>
         <v>535.5</v>
       </c>
       <c r="BG11">
-        <f>F11*$J11</f>
+        <f t="shared" si="29"/>
         <v>441</v>
       </c>
       <c r="BH11">
-        <f>G11*$J11</f>
+        <f t="shared" si="30"/>
         <v>612.5</v>
       </c>
       <c r="BI11">
-        <f>H11*$J11</f>
+        <f t="shared" si="31"/>
         <v>213.5</v>
       </c>
       <c r="BJ11">
-        <f>I11*$J11</f>
+        <f t="shared" si="32"/>
         <v>2940</v>
       </c>
     </row>
@@ -9809,27 +9811,27 @@
         <v>973</v>
       </c>
       <c r="V12">
-        <f t="shared" ref="V12:AA12" si="15">SUM(V1:V11)</f>
+        <f t="shared" ref="V12:AA12" si="46">SUM(V1:V11)</f>
         <v>647.5</v>
       </c>
       <c r="W12">
-        <f t="shared" si="15"/>
+        <f t="shared" si="46"/>
         <v>1158.5</v>
       </c>
       <c r="X12">
-        <f t="shared" si="15"/>
+        <f t="shared" si="46"/>
         <v>507.5</v>
       </c>
       <c r="Y12">
-        <f t="shared" si="15"/>
+        <f t="shared" si="46"/>
         <v>787.5</v>
       </c>
       <c r="Z12">
-        <f t="shared" si="15"/>
+        <f t="shared" si="46"/>
         <v>854</v>
       </c>
       <c r="AA12" s="15">
-        <f t="shared" si="15"/>
+        <f t="shared" si="46"/>
         <v>4928</v>
       </c>
       <c r="AI12" s="15">
@@ -9837,27 +9839,27 @@
         <v>1704.5</v>
       </c>
       <c r="AJ12">
-        <f t="shared" ref="AJ12:AO12" si="16">SUM(AJ1:AJ11)</f>
+        <f t="shared" ref="AJ12:AO12" si="47">SUM(AJ1:AJ11)</f>
         <v>1463</v>
       </c>
       <c r="AK12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="47"/>
         <v>1312.5</v>
       </c>
       <c r="AL12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="47"/>
         <v>637</v>
       </c>
       <c r="AM12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="47"/>
         <v>630</v>
       </c>
       <c r="AN12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="47"/>
         <v>1200.5</v>
       </c>
       <c r="AO12" s="15">
-        <f t="shared" si="16"/>
+        <f t="shared" si="47"/>
         <v>6947.5</v>
       </c>
       <c r="AW12">
@@ -9865,177 +9867,177 @@
         <v>2898</v>
       </c>
       <c r="AX12">
-        <f t="shared" ref="AX12:BJ12" si="17">SUM(AX1:AX11)</f>
+        <f t="shared" ref="AX12:BJ12" si="48">SUM(AX1:AX11)</f>
         <v>1921.5</v>
       </c>
       <c r="AY12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="48"/>
         <v>1963.5</v>
       </c>
       <c r="AZ12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="48"/>
         <v>3206</v>
       </c>
       <c r="BA12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="48"/>
         <v>1988</v>
       </c>
       <c r="BB12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="48"/>
         <v>857.5</v>
       </c>
       <c r="BC12" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="48"/>
         <v>12834.5</v>
       </c>
       <c r="BD12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="48"/>
         <v>5575.5</v>
       </c>
       <c r="BE12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="48"/>
         <v>4032</v>
       </c>
       <c r="BF12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="48"/>
         <v>4434.5</v>
       </c>
       <c r="BG12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="48"/>
         <v>4350.5</v>
       </c>
       <c r="BH12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="48"/>
         <v>3405.5</v>
       </c>
       <c r="BI12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="48"/>
         <v>2912</v>
       </c>
       <c r="BJ12" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="48"/>
         <v>24710</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.35">
       <c r="B13" s="19"/>
       <c r="C13" cm="1">
-        <f t="array" ref="C13">SUMPRODUCT((C2:C11/$B$18-$BD$12)^2)</f>
+        <f t="array" ref="C13">SUMPRODUCT((C2:C11/$B$18-BD$12)^2)</f>
         <v>46939672.5</v>
       </c>
       <c r="D13" cm="1">
-        <f t="array" ref="D13">SUMPRODUCT((D2:D11/$B$18-$BD$12)^2)</f>
-        <v>71101082.5</v>
+        <f t="array" ref="D13">SUMPRODUCT((D2:D11/$B$18-BE$12)^2)</f>
+        <v>47277160</v>
       </c>
       <c r="E13" cm="1">
-        <f t="array" ref="E13">SUMPRODUCT((E2:E11/$B$18-$BD$12)^2)</f>
-        <v>55509282.5</v>
+        <f t="array" ref="E13">SUMPRODUCT((E2:E11/$B$18-BF$12)^2)</f>
+        <v>42490472.5</v>
       </c>
       <c r="F13" cm="1">
-        <f t="array" ref="F13">SUMPRODUCT((F2:F11/$B$18-$BD$12)^2)</f>
-        <v>74075872.5</v>
+        <f t="array" ref="F13">SUMPRODUCT((F2:F11/$B$18-BG$12)^2)</f>
+        <v>59069622.5</v>
       </c>
       <c r="G13" cm="1">
-        <f t="array" ref="G13">SUMPRODUCT((G2:G11/$B$18-$BD$12)^2)</f>
-        <v>92651772.5</v>
+        <f t="array" ref="G13">SUMPRODUCT((G2:G11/$B$18-BH$12)^2)</f>
+        <v>45562772.5</v>
       </c>
       <c r="H13" cm="1">
-        <f t="array" ref="H13">SUMPRODUCT((H2:H11/$B$18-$BD$12)^2)</f>
-        <v>126434332.5</v>
+        <f t="array" ref="H13">SUMPRODUCT((H2:H11/$B$18-BI$12)^2)</f>
+        <v>55492010</v>
       </c>
       <c r="I13" cm="1">
-        <f t="array" ref="I13">SUMPRODUCT((I2:I11/$B$18-$BD$12)^2)</f>
-        <v>3870067652.5</v>
-      </c>
-      <c r="J13" s="21" t="s">
+        <f t="array" ref="I13">SUMPRODUCT((I2:I11/$B$18-BJ$12)^2)</f>
+        <v>208776750</v>
+      </c>
+      <c r="J13" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="21"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
       <c r="N13" cm="1">
-        <f t="array" ref="N13">SUMPRODUCT((N2:N11/$B$18-$U$12)^2)</f>
+        <f t="array" ref="N13">SUMPRODUCT((N2:N11/$B$18-U$12)^2)</f>
         <v>39655210</v>
       </c>
       <c r="O13" cm="1">
-        <f t="array" ref="O13">SUMPRODUCT((O2:O11/$B$18-$U$12)^2)</f>
-        <v>24077865</v>
+        <f t="array" ref="O13">SUMPRODUCT((O2:O11/$B$18-V$12)^2)</f>
+        <v>23018362.5</v>
       </c>
       <c r="P13" cm="1">
-        <f t="array" ref="P13">SUMPRODUCT((P2:P11/$B$18-$U$12)^2)</f>
-        <v>57851605</v>
+        <f t="array" ref="P13">SUMPRODUCT((P2:P11/$B$18-W$12)^2)</f>
+        <v>57507502.5</v>
       </c>
       <c r="Q13" cm="1">
-        <f t="array" ref="Q13">SUMPRODUCT((Q2:Q11/$B$18-$U$12)^2)</f>
-        <v>12543265</v>
+        <f t="array" ref="Q13">SUMPRODUCT((Q2:Q11/$B$18-X$12)^2)</f>
+        <v>10376362.5</v>
       </c>
       <c r="R13" cm="1">
-        <f t="array" ref="R13">SUMPRODUCT((R2:R11/$B$18-$U$12)^2)</f>
-        <v>47029465</v>
+        <f t="array" ref="R13">SUMPRODUCT((R2:R11/$B$18-Y$12)^2)</f>
+        <v>46685362.5</v>
       </c>
       <c r="S13" cm="1">
-        <f t="array" ref="S13">SUMPRODUCT((S2:S11/$B$18-$U$12)^2)</f>
-        <v>37842700</v>
+        <f t="array" ref="S13">SUMPRODUCT((S2:S11/$B$18-Z$12)^2)</f>
+        <v>37701090</v>
       </c>
       <c r="T13" cm="1">
-        <f t="array" ref="T13">SUMPRODUCT((T2:T11/$B$18-$U$12)^2)</f>
-        <v>1141978810</v>
+        <f t="array" ref="T13">SUMPRODUCT((T2:T11/$B$18-AA$12)^2)</f>
+        <v>985558560</v>
       </c>
       <c r="AB13" cm="1">
-        <f t="array" ref="AB13">SUMPRODUCT((AB2:AB11/$B$18-$U$12)^2)</f>
-        <v>81369645</v>
+        <f t="array" ref="AB13">SUMPRODUCT((AB2:AB11/$B$18-AI$12)^2)</f>
+        <v>76018722.5</v>
       </c>
       <c r="AC13" cm="1">
-        <f t="array" ref="AC13">SUMPRODUCT((AC2:AC11/$B$18-$U$12)^2)</f>
-        <v>67575410</v>
+        <f t="array" ref="AC13">SUMPRODUCT((AC2:AC11/$B$18-AJ$12)^2)</f>
+        <v>65174410</v>
       </c>
       <c r="AD13" cm="1">
-        <f t="array" ref="AD13">SUMPRODUCT((AD2:AD11/$B$18-$U$12)^2)</f>
-        <v>53154465</v>
+        <f t="array" ref="AD13">SUMPRODUCT((AD2:AD11/$B$18-AK$12)^2)</f>
+        <v>52001862.5</v>
       </c>
       <c r="AE13" cm="1">
-        <f t="array" ref="AE13">SUMPRODUCT((AE2:AE11/$B$18-$U$12)^2)</f>
-        <v>16036720</v>
+        <f t="array" ref="AE13">SUMPRODUCT((AE2:AE11/$B$18-AL$12)^2)</f>
+        <v>14907760</v>
       </c>
       <c r="AF13" cm="1">
-        <f t="array" ref="AF13">SUMPRODUCT((AF2:AF11/$B$18-$U$12)^2)</f>
-        <v>11018140</v>
+        <f t="array" ref="AF13">SUMPRODUCT((AF2:AF11/$B$18-AM$12)^2)</f>
+        <v>9841650</v>
       </c>
       <c r="AG13" cm="1">
-        <f t="array" ref="AG13">SUMPRODUCT((AG2:AG11/$B$18-$U$12)^2)</f>
-        <v>64609685</v>
+        <f t="array" ref="AG13">SUMPRODUCT((AG2:AG11/$B$18-AN$12)^2)</f>
+        <v>64092122.5</v>
       </c>
       <c r="AH13" cm="1">
-        <f t="array" ref="AH13">SUMPRODUCT((AH2:AH11/$B$18-$U$12)^2)</f>
-        <v>1492157065</v>
+        <f t="array" ref="AH13">SUMPRODUCT((AH2:AH11/$B$18-AO$12)^2)</f>
+        <v>1135210562.5</v>
       </c>
       <c r="AP13" cm="1">
-        <f t="array" ref="AP13">SUMPRODUCT((AP2:AP11/$B$18-$U$12)^2)</f>
-        <v>156679460</v>
+        <f t="array" ref="AP13">SUMPRODUCT((AP2:AP11/$B$18-AW$12)^2)</f>
+        <v>119623210</v>
       </c>
       <c r="AQ13" cm="1">
-        <f t="array" ref="AQ13">SUMPRODUCT((AQ2:AQ11/$B$18-$U$12)^2)</f>
-        <v>68133275</v>
+        <f t="array" ref="AQ13">SUMPRODUCT((AQ2:AQ11/$B$18-AX$12)^2)</f>
+        <v>59136752.5</v>
       </c>
       <c r="AR13" cm="1">
-        <f t="array" ref="AR13">SUMPRODUCT((AR2:AR11/$B$18-$U$12)^2)</f>
-        <v>70238805</v>
+        <f t="array" ref="AR13">SUMPRODUCT((AR2:AR11/$B$18-AY$12)^2)</f>
+        <v>60427902.5</v>
       </c>
       <c r="AS13" cm="1">
-        <f t="array" ref="AS13">SUMPRODUCT((AS2:AS11/$B$18-$U$12)^2)</f>
-        <v>163499280</v>
+        <f t="array" ref="AS13">SUMPRODUCT((AS2:AS11/$B$18-AZ$12)^2)</f>
+        <v>113636390</v>
       </c>
       <c r="AT13" cm="1">
-        <f t="array" ref="AT13">SUMPRODUCT((AT2:AT11/$B$18-$U$12)^2)</f>
-        <v>65620310</v>
+        <f t="array" ref="AT13">SUMPRODUCT((AT2:AT11/$B$18-BA$12)^2)</f>
+        <v>55318060</v>
       </c>
       <c r="AU13" cm="1">
-        <f t="array" ref="AU13">SUMPRODUCT((AU2:AU11/$B$18-$U$12)^2)</f>
-        <v>9571415</v>
+        <f t="array" ref="AU13">SUMPRODUCT((AU2:AU11/$B$18-BB$12)^2)</f>
+        <v>9438012.5</v>
       </c>
       <c r="AV13" cm="1">
-        <f t="array" ref="AV13">SUMPRODUCT((AV2:AV11/$B$18-$U$12)^2)</f>
-        <v>3228027145</v>
+        <f t="array" ref="AV13">SUMPRODUCT((AV2:AV11/$B$18-BC$12)^2)</f>
+        <v>1821075322.5</v>
       </c>
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.35">
@@ -10047,28 +10049,28 @@
         <v>521551.91666666669</v>
       </c>
       <c r="D14">
-        <f t="shared" ref="D14:I14" si="18">1/($B$19*($B$19-1))*D13</f>
-        <v>790012.02777777775</v>
+        <f t="shared" ref="D14:I14" si="49">1/($B$19*($B$19-1))*D13</f>
+        <v>525301.77777777775</v>
       </c>
       <c r="E14">
-        <f t="shared" si="18"/>
-        <v>616769.80555555562</v>
+        <f t="shared" si="49"/>
+        <v>472116.36111111112</v>
       </c>
       <c r="F14">
-        <f t="shared" si="18"/>
-        <v>823065.25</v>
+        <f t="shared" si="49"/>
+        <v>656329.13888888888</v>
       </c>
       <c r="G14">
-        <f t="shared" si="18"/>
-        <v>1029464.1388888889</v>
+        <f t="shared" si="49"/>
+        <v>506253.02777777781</v>
       </c>
       <c r="H14">
-        <f t="shared" si="18"/>
-        <v>1404825.9166666667</v>
+        <f t="shared" si="49"/>
+        <v>616577.88888888888</v>
       </c>
       <c r="I14">
-        <f t="shared" si="18"/>
-        <v>43000751.694444448</v>
+        <f t="shared" si="49"/>
+        <v>2319741.666666667</v>
       </c>
       <c r="M14" s="19" t="s">
         <v>33</v>
@@ -10078,84 +10080,84 @@
         <v>440613.44444444444</v>
       </c>
       <c r="O14">
-        <f t="shared" ref="O14:T14" si="19">1/($B$19*($B$19-1))*O13</f>
-        <v>267531.83333333337</v>
+        <f t="shared" ref="O14:T14" si="50">1/($B$19*($B$19-1))*O13</f>
+        <v>255759.58333333334</v>
       </c>
       <c r="P14">
-        <f t="shared" si="19"/>
-        <v>642795.61111111112</v>
+        <f t="shared" si="50"/>
+        <v>638972.25</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="19"/>
-        <v>139369.61111111112</v>
+        <f t="shared" si="50"/>
+        <v>115292.91666666667</v>
       </c>
       <c r="R14">
-        <f t="shared" si="19"/>
-        <v>522549.61111111112</v>
+        <f t="shared" si="50"/>
+        <v>518726.25</v>
       </c>
       <c r="S14">
-        <f t="shared" si="19"/>
-        <v>420474.44444444444</v>
+        <f t="shared" si="50"/>
+        <v>418901</v>
       </c>
       <c r="T14">
-        <f t="shared" si="19"/>
-        <v>12688653.444444444</v>
+        <f t="shared" si="50"/>
+        <v>10950650.666666668</v>
       </c>
       <c r="AB14">
         <f>1/($B$19*($B$19-1))*AB13</f>
-        <v>904107.16666666674</v>
+        <v>844652.47222222225</v>
       </c>
       <c r="AC14">
-        <f t="shared" ref="AC14" si="20">1/($B$19*($B$19-1))*AC13</f>
-        <v>750837.88888888888</v>
+        <f t="shared" ref="AC14" si="51">1/($B$19*($B$19-1))*AC13</f>
+        <v>724160.11111111112</v>
       </c>
       <c r="AD14">
-        <f t="shared" ref="AD14" si="21">1/($B$19*($B$19-1))*AD13</f>
-        <v>590605.16666666674</v>
+        <f t="shared" ref="AD14" si="52">1/($B$19*($B$19-1))*AD13</f>
+        <v>577798.47222222225</v>
       </c>
       <c r="AE14">
-        <f t="shared" ref="AE14" si="22">1/($B$19*($B$19-1))*AE13</f>
-        <v>178185.77777777778</v>
+        <f t="shared" ref="AE14" si="53">1/($B$19*($B$19-1))*AE13</f>
+        <v>165641.77777777778</v>
       </c>
       <c r="AF14">
-        <f t="shared" ref="AF14" si="23">1/($B$19*($B$19-1))*AF13</f>
-        <v>122423.77777777778</v>
+        <f t="shared" ref="AF14" si="54">1/($B$19*($B$19-1))*AF13</f>
+        <v>109351.66666666667</v>
       </c>
       <c r="AG14">
-        <f t="shared" ref="AG14" si="24">1/($B$19*($B$19-1))*AG13</f>
-        <v>717885.38888888888</v>
+        <f t="shared" ref="AG14" si="55">1/($B$19*($B$19-1))*AG13</f>
+        <v>712134.6944444445</v>
       </c>
       <c r="AH14">
-        <f t="shared" ref="AH14" si="25">1/($B$19*($B$19-1))*AH13</f>
-        <v>16579522.944444446</v>
+        <f t="shared" ref="AH14" si="56">1/($B$19*($B$19-1))*AH13</f>
+        <v>12613450.694444444</v>
       </c>
       <c r="AP14">
         <f>1/($B$19*($B$19-1))*AP13</f>
-        <v>1740882.888888889</v>
+        <v>1329146.7777777778</v>
       </c>
       <c r="AQ14">
-        <f t="shared" ref="AQ14" si="26">1/($B$19*($B$19-1))*AQ13</f>
-        <v>757036.38888888888</v>
+        <f t="shared" ref="AQ14" si="57">1/($B$19*($B$19-1))*AQ13</f>
+        <v>657075.02777777775</v>
       </c>
       <c r="AR14">
-        <f t="shared" ref="AR14" si="27">1/($B$19*($B$19-1))*AR13</f>
-        <v>780431.16666666674</v>
+        <f t="shared" ref="AR14" si="58">1/($B$19*($B$19-1))*AR13</f>
+        <v>671421.13888888888</v>
       </c>
       <c r="AS14">
-        <f t="shared" ref="AS14" si="28">1/($B$19*($B$19-1))*AS13</f>
-        <v>1816658.6666666667</v>
+        <f t="shared" ref="AS14" si="59">1/($B$19*($B$19-1))*AS13</f>
+        <v>1262626.5555555555</v>
       </c>
       <c r="AT14">
-        <f t="shared" ref="AT14" si="29">1/($B$19*($B$19-1))*AT13</f>
-        <v>729114.55555555562</v>
+        <f t="shared" ref="AT14" si="60">1/($B$19*($B$19-1))*AT13</f>
+        <v>614645.11111111112</v>
       </c>
       <c r="AU14">
-        <f t="shared" ref="AU14" si="30">1/($B$19*($B$19-1))*AU13</f>
-        <v>106349.05555555556</v>
+        <f t="shared" ref="AU14" si="61">1/($B$19*($B$19-1))*AU13</f>
+        <v>104866.80555555556</v>
       </c>
       <c r="AV14">
-        <f t="shared" ref="AV14" si="31">1/($B$19*($B$19-1))*AV13</f>
-        <v>35866968.277777776</v>
+        <f t="shared" ref="AV14" si="62">1/($B$19*($B$19-1))*AV13</f>
+        <v>20234170.25</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.35">
@@ -10173,32 +10175,32 @@
         <v>34</v>
       </c>
       <c r="C16" s="16">
-        <f>SQRT(C14)/BD12</f>
+        <f t="shared" ref="C16:I16" si="63">SQRT(C14)/BD12</f>
         <v>0.12952838562001365</v>
       </c>
       <c r="D16" s="16">
-        <f>SQRT(D14)/BE12</f>
-        <v>0.22044300790164478</v>
+        <f t="shared" si="63"/>
+        <v>0.17975621375081913</v>
       </c>
       <c r="E16" s="16">
-        <f>SQRT(E14)/BF12</f>
-        <v>0.17709931970771733</v>
+        <f t="shared" si="63"/>
+        <v>0.1549458205765539</v>
       </c>
       <c r="F16" s="16">
-        <f>SQRT(F14)/BG12</f>
-        <v>0.20853452160690281</v>
+        <f t="shared" si="63"/>
+        <v>0.18621800515139381</v>
       </c>
       <c r="G16" s="16">
-        <f>SQRT(G14)/BH12</f>
-        <v>0.29793719640072686</v>
+        <f t="shared" si="63"/>
+        <v>0.20893102370871922</v>
       </c>
       <c r="H16" s="16">
-        <f>SQRT(H14)/BI12</f>
-        <v>0.40702387507420751</v>
+        <f t="shared" si="63"/>
+        <v>0.26965135227431403</v>
       </c>
       <c r="I16" s="16">
-        <f>SQRT(I14)/BJ12</f>
-        <v>0.26537822097189662</v>
+        <f t="shared" si="63"/>
+        <v>6.1637791045760365E-2</v>
       </c>
       <c r="M16" s="19" t="s">
         <v>34</v>
@@ -10208,84 +10210,84 @@
         <v>0.68220678125644085</v>
       </c>
       <c r="O16" s="16">
-        <f t="shared" ref="O16:T16" si="32">SQRT(O14)/V12</f>
-        <v>0.79881821647694529</v>
+        <f t="shared" ref="O16:T16" si="64">SQRT(O14)/V12</f>
+        <v>0.78104523126058234</v>
       </c>
       <c r="P16" s="16">
-        <f t="shared" si="32"/>
-        <v>0.69205468539808956</v>
+        <f t="shared" si="64"/>
+        <v>0.68999343820828696</v>
       </c>
       <c r="Q16" s="16">
-        <f t="shared" si="32"/>
-        <v>0.73561063186819975</v>
+        <f t="shared" si="64"/>
+        <v>0.6690603084873461</v>
       </c>
       <c r="R16" s="16">
-        <f t="shared" si="32"/>
-        <v>0.91793768971253575</v>
+        <f t="shared" si="64"/>
+        <v>0.91457336744760098</v>
       </c>
       <c r="S16" s="16">
-        <f t="shared" si="32"/>
-        <v>0.75929743367909708</v>
+        <f t="shared" si="64"/>
+        <v>0.7578754303746762</v>
       </c>
       <c r="T16" s="16">
-        <f t="shared" si="32"/>
-        <v>0.72283149764055676</v>
+        <f t="shared" si="64"/>
+        <v>0.67150501937575413</v>
       </c>
       <c r="AB16" s="16">
         <f>SQRT(AB14)/AI12</f>
-        <v>0.55784423640049385</v>
+        <v>0.53919024107458502</v>
       </c>
       <c r="AC16" s="16">
-        <f t="shared" ref="AC16:AH16" si="33">SQRT(AC14)/AJ12</f>
-        <v>0.59228231314034474</v>
+        <f t="shared" ref="AC16:AH16" si="65">SQRT(AC14)/AJ12</f>
+        <v>0.58166505511747313</v>
       </c>
       <c r="AD16" s="16">
-        <f t="shared" si="33"/>
-        <v>0.58553021239696046</v>
+        <f t="shared" si="65"/>
+        <v>0.57914709532612818</v>
       </c>
       <c r="AE16" s="16">
-        <f t="shared" si="33"/>
-        <v>0.66266965864879757</v>
+        <f t="shared" si="65"/>
+        <v>0.63891856733817276</v>
       </c>
       <c r="AF16" s="16">
-        <f t="shared" si="33"/>
-        <v>0.55538268915486944</v>
+        <f t="shared" si="65"/>
+        <v>0.5248946592338134</v>
       </c>
       <c r="AG16" s="16">
-        <f t="shared" si="33"/>
-        <v>0.70577357320602552</v>
+        <f t="shared" si="65"/>
+        <v>0.70294105350073299</v>
       </c>
       <c r="AH16" s="16">
-        <f t="shared" si="33"/>
-        <v>0.58608075339892041</v>
+        <f t="shared" si="65"/>
+        <v>0.51119712363105152</v>
       </c>
       <c r="AP16" s="16">
         <f>SQRT(AP14)/AW12</f>
-        <v>0.45528820274524928</v>
+        <v>0.39782135313073702</v>
       </c>
       <c r="AQ16" s="16">
-        <f t="shared" ref="AQ16:AU16" si="34">SQRT(AQ14)/AX12</f>
-        <v>0.45281206395426382</v>
+        <f t="shared" ref="AQ16:AU16" si="66">SQRT(AQ14)/AX12</f>
+        <v>0.42185877988852677</v>
       </c>
       <c r="AR16" s="16">
-        <f t="shared" si="34"/>
-        <v>0.44992113723764243</v>
+        <f t="shared" si="66"/>
+        <v>0.4173175024625288</v>
       </c>
       <c r="AS16" s="16">
-        <f t="shared" si="34"/>
-        <v>0.42041010820053454</v>
+        <f t="shared" si="66"/>
+        <v>0.35048863623956206</v>
       </c>
       <c r="AT16" s="16">
-        <f t="shared" si="34"/>
-        <v>0.429518133874496</v>
+        <f t="shared" si="66"/>
+        <v>0.39436270398631762</v>
       </c>
       <c r="AU16" s="16">
-        <f t="shared" si="34"/>
-        <v>0.38030557335138415</v>
+        <f t="shared" si="66"/>
+        <v>0.3776460014130511</v>
       </c>
       <c r="AV16" s="16">
         <f>SQRT(AV14)/BC12</f>
-        <v>0.4666254051663713</v>
+        <v>0.35048040788671025</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
@@ -10337,22 +10339,22 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="15"/>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20" t="s">
+      <c r="C2" s="21"/>
+      <c r="D2" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20" t="s">
+      <c r="E2" s="21"/>
+      <c r="F2" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20" t="s">
+      <c r="G2" s="21"/>
+      <c r="H2" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="I2" s="20"/>
+      <c r="I2" s="21"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="15"/>
